--- a/Översikt ÖDESHÖG.xlsx
+++ b/Översikt ÖDESHÖG.xlsx
@@ -601,7 +601,7 @@
         <v>45805</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45723</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44698</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>44664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 35443-2022</t>
+          <t>A 56797-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1058,14 +1058,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44798</v>
+        <v>45244</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1118,149 +1118,149 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Jungfrulin
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 56797-2023 artfynd.xlsx", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 56797-2023 karta.png", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 56797-2023 georefererad karta.tif", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 56797-2023 FSC-klagomål.docx", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 56797-2023 FSC-klagomål mail.docx", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 56797-2023 tillsynsbegäran.docx", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 56797-2023 tillsynsbegäran mail.docx", "A 56797-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 35443-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44798</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Axveronika
 Bivråk</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 35443-2022 artfynd.xlsx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 35443-2022 karta.png", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 35443-2022 georefererad karta.tif", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 35443-2022 FSC-klagomål.docx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 35443-2022 FSC-klagomål mail.docx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 35443-2022 tillsynsbegäran.docx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 35443-2022 tillsynsbegäran mail.docx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/fåglar/A 35443-2022 prioriterade fågelarter.docx", "A 35443-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 56797-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45244</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 56797-2023 artfynd.xlsx", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 56797-2023 karta.png", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 56797-2023 georefererad karta.tif", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 56797-2023 FSC-klagomål.docx", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 56797-2023 FSC-klagomål mail.docx", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 56797-2023 tillsynsbegäran.docx", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 56797-2023 tillsynsbegäran mail.docx", "A 56797-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>44538</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 15437-2025</t>
+          <t>A 32776-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45747</v>
+        <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1503,16 +1503,11 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>11.9</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1545,370 +1540,370 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Smalsprötad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32776-2025 artfynd.xlsx", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32776-2025 karta.png", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32776-2025 georefererad karta.tif", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32776-2025 FSC-klagomål.docx", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32776-2025 FSC-klagomål mail.docx", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32776-2025 tillsynsbegäran.docx", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32776-2025 tillsynsbegäran mail.docx", "A 32776-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 58551-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45251</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58551-2023 artfynd.xlsx", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58551-2023 karta.png", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58551-2023 georefererad karta.tif", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58551-2023 FSC-klagomål.docx", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58551-2023 FSC-klagomål mail.docx", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58551-2023 tillsynsbegäran.docx", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58551-2023 tillsynsbegäran mail.docx", "A 58551-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 50774-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Mörk dunört</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 50774-2023 artfynd.xlsx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 50774-2023 karta.png", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 50774-2023 georefererad karta.tif", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 50774-2023 FSC-klagomål.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 50774-2023 FSC-klagomål mail.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 50774-2023 tillsynsbegäran.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 50774-2023 tillsynsbegäran mail.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 15437-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>Knärot</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 15437-2025 artfynd.xlsx", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 15437-2025 karta.png", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 15437-2025 georefererad karta.tif", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="Z10">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/knärot/A 15437-2025 karta knärot.png", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 15437-2025 FSC-klagomål.docx", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 15437-2025 FSC-klagomål mail.docx", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 15437-2025 tillsynsbegäran.docx", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 15437-2025 tillsynsbegäran mail.docx", "A 15437-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 4772-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44592</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 4772-2022 artfynd.xlsx", "A 4772-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 4772-2022 karta.png", "A 4772-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 4772-2022 georefererad karta.tif", "A 4772-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 4772-2022 FSC-klagomål.docx", "A 4772-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 4772-2022 FSC-klagomål mail.docx", "A 4772-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 4772-2022 tillsynsbegäran.docx", "A 4772-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 4772-2022 tillsynsbegäran mail.docx", "A 4772-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 32776-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45839</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Smalsprötad bastardsvärmare</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32776-2025 artfynd.xlsx", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32776-2025 karta.png", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32776-2025 georefererad karta.tif", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32776-2025 FSC-klagomål.docx", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32776-2025 FSC-klagomål mail.docx", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32776-2025 tillsynsbegäran.docx", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32776-2025 tillsynsbegäran mail.docx", "A 32776-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 58052-2021</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>44487</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Granbarkgnagare</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58052-2021 artfynd.xlsx", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58052-2021 karta.png", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58052-2021 georefererad karta.tif", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58052-2021 FSC-klagomål.docx", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58052-2021 FSC-klagomål mail.docx", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58052-2021 tillsynsbegäran.docx", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58052-2021 tillsynsbegäran mail.docx", "A 58052-2021")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 58551-2023</t>
+          <t>A 32713-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1918,14 +1913,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45251</v>
+        <v>45516</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1938,31 +1933,31 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>6.1</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1978,35 +1973,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kristinspindling</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58551-2023 artfynd.xlsx", "A 58551-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32713-2024 artfynd.xlsx", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58551-2023 karta.png", "A 58551-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32713-2024 karta.png", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58551-2023 georefererad karta.tif", "A 58551-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32713-2024 georefererad karta.tif", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58551-2023 FSC-klagomål.docx", "A 58551-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32713-2024 FSC-klagomål.docx", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58551-2023 FSC-klagomål mail.docx", "A 58551-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32713-2024 FSC-klagomål mail.docx", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58551-2023 tillsynsbegäran.docx", "A 58551-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32713-2024 tillsynsbegäran.docx", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58551-2023 tillsynsbegäran mail.docx", "A 58551-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32713-2024 tillsynsbegäran mail.docx", "A 32713-2024")</f>
         <v/>
       </c>
     </row>
@@ -2030,7 +2025,7 @@
         <v>45272</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2123,7 +2118,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 56637-2023</t>
+          <t>A 38720-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2133,14 +2128,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45243</v>
+        <v>45163</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2153,13 +2148,13 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -2168,7 +2163,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2177,10 +2172,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2189,151 +2184,151 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
+          <t>Hässleklocka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 38720-2023 artfynd.xlsx", "A 38720-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 38720-2023 karta.png", "A 38720-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 38720-2023 georefererad karta.tif", "A 38720-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 38720-2023 FSC-klagomål.docx", "A 38720-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 38720-2023 FSC-klagomål mail.docx", "A 38720-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 38720-2023 tillsynsbegäran.docx", "A 38720-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 38720-2023 tillsynsbegäran mail.docx", "A 38720-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 56637-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45243</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>Skogsalm</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 56637-2023 artfynd.xlsx", "A 56637-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 56637-2023 karta.png", "A 56637-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 56637-2023 georefererad karta.tif", "A 56637-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 56637-2023 FSC-klagomål.docx", "A 56637-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 56637-2023 FSC-klagomål mail.docx", "A 56637-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 56637-2023 tillsynsbegäran.docx", "A 56637-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 56637-2023 tillsynsbegäran mail.docx", "A 56637-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 50774-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Mörk dunört</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 50774-2023 artfynd.xlsx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 50774-2023 karta.png", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 50774-2023 georefererad karta.tif", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 50774-2023 FSC-klagomål.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 50774-2023 FSC-klagomål mail.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 50774-2023 tillsynsbegäran.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 50774-2023 tillsynsbegäran mail.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 38720-2023</t>
+          <t>A 58052-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2347,10 +2342,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45163</v>
+        <v>44487</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2362,8 +2357,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2403,42 +2403,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Hässleklocka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 38720-2023 artfynd.xlsx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58052-2021 artfynd.xlsx", "A 58052-2021")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 38720-2023 karta.png", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58052-2021 karta.png", "A 58052-2021")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 38720-2023 georefererad karta.tif", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58052-2021 georefererad karta.tif", "A 58052-2021")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 38720-2023 FSC-klagomål.docx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58052-2021 FSC-klagomål.docx", "A 58052-2021")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 38720-2023 FSC-klagomål mail.docx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58052-2021 FSC-klagomål mail.docx", "A 58052-2021")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 38720-2023 tillsynsbegäran.docx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58052-2021 tillsynsbegäran.docx", "A 58052-2021")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 38720-2023 tillsynsbegäran mail.docx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58052-2021 tillsynsbegäran mail.docx", "A 58052-2021")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32713-2024</t>
+          <t>A 4772-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45516</v>
+        <v>44592</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.1</v>
+        <v>1.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2483,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2508,35 +2508,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kristinspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32713-2024 artfynd.xlsx", "A 32713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 4772-2022 artfynd.xlsx", "A 4772-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32713-2024 karta.png", "A 32713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 4772-2022 karta.png", "A 4772-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32713-2024 georefererad karta.tif", "A 32713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 4772-2022 georefererad karta.tif", "A 4772-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32713-2024 FSC-klagomål.docx", "A 32713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 4772-2022 FSC-klagomål.docx", "A 4772-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32713-2024 FSC-klagomål mail.docx", "A 32713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 4772-2022 FSC-klagomål mail.docx", "A 4772-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32713-2024 tillsynsbegäran.docx", "A 32713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 4772-2022 tillsynsbegäran.docx", "A 4772-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32713-2024 tillsynsbegäran mail.docx", "A 32713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 4772-2022 tillsynsbegäran mail.docx", "A 4772-2022")</f>
         <v/>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
         <v>44509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44538</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>44614</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>44803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>44510</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44504</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44462</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>44517</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>44666</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>44756</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44796</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 36114-2022</t>
+          <t>A 15790-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44803</v>
+        <v>45748</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3643,7 +3643,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 47600-2023</t>
+          <t>A 6705-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45203</v>
+        <v>45342</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3672,8 +3672,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3716,7 +3721,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 15906-2024</t>
+          <t>A 35661-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3726,14 +3731,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45405</v>
+        <v>45532</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3746,7 +3751,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3789,7 +3794,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30389-2024</t>
+          <t>A 36114-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3803,10 +3808,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45491</v>
+        <v>44803</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3819,7 +3824,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3862,7 +3867,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 64802-2021</t>
+          <t>A 26949-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3872,14 +3877,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44512</v>
+        <v>45093</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3892,7 +3897,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3935,7 +3940,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 54226-2021</t>
+          <t>A 5819-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3945,14 +3950,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44470</v>
+        <v>45335</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3964,8 +3969,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4008,7 +4018,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 6164-2024</t>
+          <t>A 3198-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4022,10 +4032,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45337</v>
+        <v>45316</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4038,7 +4048,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4081,7 +4091,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 48325-2022</t>
+          <t>A 15813-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4091,14 +4101,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44858</v>
+        <v>44664</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4112,11 +4122,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4159,7 +4169,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 6705-2024</t>
+          <t>A 8256-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4169,14 +4179,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45342</v>
+        <v>44974</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4188,13 +4198,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>8.300000000000001</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4237,7 +4242,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 47993-2024</t>
+          <t>A 22088-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4251,10 +4256,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45589</v>
+        <v>45069</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4267,7 +4272,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4310,7 +4315,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 35661-2024</t>
+          <t>A 38152-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4324,10 +4329,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45532</v>
+        <v>45161</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4340,7 +4345,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4383,7 +4388,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 1578-2023</t>
+          <t>A 56841-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4397,10 +4402,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44937</v>
+        <v>44894</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4413,7 +4418,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4456,7 +4461,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1323-2023</t>
+          <t>A 44069-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4470,10 +4475,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44936</v>
+        <v>45188</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4486,7 +4491,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4529,7 +4534,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 56841-2022</t>
+          <t>A 11280-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4543,10 +4548,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44894</v>
+        <v>45726</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4559,7 +4564,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4602,7 +4607,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 32335-2024</t>
+          <t>A 1578-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4616,10 +4621,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45512</v>
+        <v>44937</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4632,7 +4637,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4675,7 +4680,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3149-2024</t>
+          <t>A 15909-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4685,14 +4690,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45316</v>
+        <v>45405</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4705,7 +4710,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4748,7 +4753,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30388-2024</t>
+          <t>A 38259-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4762,10 +4767,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45491</v>
+        <v>45161</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4778,7 +4783,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4821,7 +4826,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 47597-2023</t>
+          <t>A 61629-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4835,10 +4840,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45203</v>
+        <v>46002</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4851,7 +4856,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4894,7 +4899,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 15907-2024</t>
+          <t>A 21336-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4904,14 +4909,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45405</v>
+        <v>45782</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4924,7 +4929,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4967,7 +4972,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 15915-2024</t>
+          <t>A 39032-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4977,14 +4982,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45405</v>
+        <v>45163</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4996,8 +5001,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5040,7 +5050,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 17618-2024</t>
+          <t>A 62482-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5054,10 +5064,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45416</v>
+        <v>46007</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5070,7 +5080,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>6.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5113,7 +5123,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 13129-2023</t>
+          <t>A 62202-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5127,10 +5137,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45002</v>
+        <v>46006</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5143,7 +5153,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>5.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5186,7 +5196,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 5283-2024</t>
+          <t>A 62801-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5200,10 +5210,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45331</v>
+        <v>46008</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5216,7 +5226,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5259,7 +5269,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 14750-2023</t>
+          <t>A 64010-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5273,10 +5283,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45014</v>
+        <v>46021</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5288,8 +5298,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>15.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5332,7 +5347,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 14156-2023</t>
+          <t>A 64015-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5346,10 +5361,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45009</v>
+        <v>46021</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5361,8 +5376,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5405,7 +5425,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8118-2026</t>
+          <t>A 602-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5419,10 +5439,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46062</v>
+        <v>46029</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5435,7 +5455,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>13.4</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5478,7 +5498,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 46528-2024</t>
+          <t>A 1279-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5492,10 +5512,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45582</v>
+        <v>46031</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5551,7 +5571,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 30600-2025</t>
+          <t>A 1261-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5565,10 +5585,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45831</v>
+        <v>46031</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5581,7 +5601,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5624,7 +5644,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 32476-2025</t>
+          <t>A 1268-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5638,10 +5658,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45838</v>
+        <v>46031</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5654,7 +5674,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5697,7 +5717,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 32466-2025</t>
+          <t>A 39920-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5711,10 +5731,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45838</v>
+        <v>45553</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5727,7 +5747,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5770,7 +5790,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 8256-2023</t>
+          <t>A 1264-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5780,14 +5800,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44974</v>
+        <v>46031</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5800,7 +5820,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5843,7 +5863,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 22088-2023</t>
+          <t>A 1273-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5857,10 +5877,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45069</v>
+        <v>46031</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5916,7 +5936,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 36099-2024</t>
+          <t>A 45973-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5930,10 +5950,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45533</v>
+        <v>45580</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5946,7 +5966,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5989,7 +6009,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 14736-2024</t>
+          <t>A 9448-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5999,14 +6019,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45397</v>
+        <v>44981</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6019,7 +6039,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6062,7 +6082,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 20232-2022</t>
+          <t>A 1585-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6076,10 +6096,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44698</v>
+        <v>46034</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6097,7 +6117,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6140,7 +6160,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 41730-2025</t>
+          <t>A 1589-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6154,10 +6174,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45902</v>
+        <v>46034</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6169,8 +6189,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6213,7 +6238,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14185-2023</t>
+          <t>A 54226-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6227,10 +6252,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45009</v>
+        <v>44470</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6243,7 +6268,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6286,7 +6311,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14166-2023</t>
+          <t>A 46528-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6300,10 +6325,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45009</v>
+        <v>45582</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6316,7 +6341,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6359,7 +6384,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 19350-2023</t>
+          <t>A 41730-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6373,10 +6398,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45049</v>
+        <v>45902</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6432,7 +6457,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11972-2023</t>
+          <t>A 36075-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6446,10 +6471,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44994</v>
+        <v>45149</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6462,7 +6487,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6505,7 +6530,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 46059-2025</t>
+          <t>A 30600-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6519,10 +6544,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45924</v>
+        <v>45831</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6535,7 +6560,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6578,7 +6603,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 46788-2025</t>
+          <t>A 1674-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6592,10 +6617,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45926</v>
+        <v>44938</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6608,7 +6633,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6651,7 +6676,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 46778-2025</t>
+          <t>A 35079-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6665,10 +6690,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45926</v>
+        <v>45145</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6681,7 +6706,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6724,7 +6749,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 46999-2025</t>
+          <t>A 32466-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6738,10 +6763,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45929</v>
+        <v>45838</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6754,7 +6779,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6797,7 +6822,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39024-2023</t>
+          <t>A 32476-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6811,10 +6836,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45163</v>
+        <v>45838</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6826,13 +6851,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6875,7 +6895,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 48063-2025</t>
+          <t>A 6421-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6889,10 +6909,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45932</v>
+        <v>45699</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6905,7 +6925,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6948,7 +6968,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 47648-2025</t>
+          <t>A 6456-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6962,10 +6982,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45931</v>
+        <v>45699</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6978,7 +6998,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7021,7 +7041,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 54419-2024</t>
+          <t>A 17618-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7035,10 +7055,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45617</v>
+        <v>45416</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7050,13 +7070,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>22.7</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7099,7 +7114,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 48575-2025</t>
+          <t>A 47993-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7113,10 +7128,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45936</v>
+        <v>45589</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7129,7 +7144,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7172,7 +7187,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 48611-2025</t>
+          <t>A 46059-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7186,10 +7201,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45936</v>
+        <v>45924</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7202,7 +7217,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7245,7 +7260,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 48614-2025</t>
+          <t>A 46778-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7259,10 +7274,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45936</v>
+        <v>45926</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7275,7 +7290,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7318,7 +7333,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 50416-2025</t>
+          <t>A 7375-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7332,10 +7347,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45944</v>
+        <v>46059</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7348,7 +7363,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7391,7 +7406,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 39032-2023</t>
+          <t>A 46999-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7405,10 +7420,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45163</v>
+        <v>45929</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7420,13 +7435,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7469,7 +7479,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 14993-2023</t>
+          <t>A 46788-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7483,10 +7493,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45015</v>
+        <v>45926</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7499,7 +7509,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7542,7 +7552,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 12859-2026</t>
+          <t>A 5513-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7556,10 +7566,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46092</v>
+        <v>45693</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7572,7 +7582,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7615,7 +7625,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 12872-2026</t>
+          <t>A 47648-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7629,10 +7639,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46092</v>
+        <v>45931</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7645,7 +7655,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7688,7 +7698,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 51171-2025</t>
+          <t>A 6164-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7702,10 +7712,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45947</v>
+        <v>45337</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7718,7 +7728,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7761,7 +7771,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 51328-2025</t>
+          <t>A 14156-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7775,10 +7785,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45950</v>
+        <v>45009</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7791,7 +7801,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7834,7 +7844,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 11280-2025</t>
+          <t>A 8118-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7848,10 +7858,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45726</v>
+        <v>46062</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7864,7 +7874,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.4</v>
+        <v>13.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7907,7 +7917,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 14617-2026</t>
+          <t>A 13129-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7921,10 +7931,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46101</v>
+        <v>45002</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7937,7 +7947,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7980,7 +7990,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 8049-2025</t>
+          <t>A 48063-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7994,10 +8004,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45707</v>
+        <v>45932</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8010,7 +8020,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8053,7 +8063,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 38152-2023</t>
+          <t>A 48611-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8067,10 +8077,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45161</v>
+        <v>45936</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8083,7 +8093,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8126,7 +8136,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 8515-2022</t>
+          <t>A 48614-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8140,10 +8150,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44613</v>
+        <v>45936</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8156,7 +8166,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8199,7 +8209,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 16341-2026</t>
+          <t>A 35411-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8213,10 +8223,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46111</v>
+        <v>45146</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8228,13 +8238,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8277,7 +8282,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 38723-2023</t>
+          <t>A 48575-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8291,10 +8296,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45163</v>
+        <v>45936</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8307,7 +8312,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8350,7 +8355,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 16402-2026</t>
+          <t>A 16270-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8364,10 +8369,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46111</v>
+        <v>45407</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8379,13 +8384,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8428,7 +8428,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 3130-2025</t>
+          <t>A 50416-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8442,10 +8442,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45678</v>
+        <v>45944</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8457,13 +8457,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>18.6</v>
+        <v>3.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8506,7 +8501,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 16414-2026</t>
+          <t>A 51171-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8520,10 +8515,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46111</v>
+        <v>45947</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8535,13 +8530,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>8.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8584,7 +8574,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 16370-2026</t>
+          <t>A 51328-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8598,10 +8588,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46111</v>
+        <v>45950</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8613,13 +8603,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8662,7 +8647,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 16128-2025</t>
+          <t>A 20244-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8676,10 +8661,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45750</v>
+        <v>44698</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8697,7 +8682,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.6</v>
+        <v>9.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8740,7 +8725,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 20720-2025</t>
+          <t>A 6557-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8754,10 +8739,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45776</v>
+        <v>45699</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8770,7 +8755,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8813,7 +8798,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 55971-2023</t>
+          <t>A 32378-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8827,10 +8812,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45240</v>
+        <v>45512</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8843,7 +8828,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8886,7 +8871,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 30945-2023</t>
+          <t>A 39024-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8900,10 +8885,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45113</v>
+        <v>45163</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8915,8 +8900,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8959,7 +8949,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 16164-2023</t>
+          <t>A 12872-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8973,10 +8963,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45027</v>
+        <v>46092</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8988,13 +8978,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9037,7 +9022,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 55908-2025</t>
+          <t>A 19351-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9051,10 +9036,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45973</v>
+        <v>45049</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9067,7 +9052,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9110,7 +9095,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 55901-2025</t>
+          <t>A 12859-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9124,10 +9109,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45973</v>
+        <v>46092</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9183,7 +9168,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 55906-2025</t>
+          <t>A 32335-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9197,10 +9182,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45973</v>
+        <v>45512</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9213,7 +9198,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9256,7 +9241,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 30964-2023</t>
+          <t>A 14617-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9270,10 +9255,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45113</v>
+        <v>46101</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9286,7 +9271,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9329,7 +9314,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 16259-2026</t>
+          <t>A 8515-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9343,10 +9328,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46109</v>
+        <v>44613</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9359,7 +9344,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9402,7 +9387,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 16262-2026</t>
+          <t>A 61880-2021</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9416,10 +9401,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46109</v>
+        <v>44502</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9432,7 +9417,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9475,7 +9460,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 17950-2026</t>
+          <t>A 16370-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9489,10 +9474,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46122</v>
+        <v>46111</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9504,8 +9489,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>4.6</v>
+        <v>6.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9548,7 +9538,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 21770-2023</t>
+          <t>A 16414-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9562,10 +9552,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45065</v>
+        <v>46111</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9577,8 +9567,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>1.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9621,7 +9616,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 19351-2023</t>
+          <t>A 16402-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9635,10 +9630,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45049</v>
+        <v>46111</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9650,8 +9645,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>5.8</v>
+        <v>2.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9694,7 +9694,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 61801-2025</t>
+          <t>A 16341-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9708,10 +9708,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46002</v>
+        <v>46111</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9723,8 +9723,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9767,7 +9772,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 61470-2025</t>
+          <t>A 16259-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9781,10 +9786,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46001</v>
+        <v>46109</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9796,13 +9801,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>8</v>
+        <v>1.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9845,7 +9845,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 61798-2025</t>
+          <t>A 16262-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9859,10 +9859,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46002</v>
+        <v>46109</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9874,13 +9874,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9923,7 +9918,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 61800-2025</t>
+          <t>A 20720-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9937,10 +9932,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46002</v>
+        <v>45776</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9953,7 +9948,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9996,7 +9991,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 61629-2025</t>
+          <t>A 55901-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10010,10 +10005,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46002</v>
+        <v>45973</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10026,7 +10021,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10069,7 +10064,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 38266-2022</t>
+          <t>A 17950-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10083,10 +10078,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44812</v>
+        <v>46122</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10099,7 +10094,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10142,7 +10137,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 61786-2025</t>
+          <t>A 33375-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10156,10 +10151,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46002</v>
+        <v>45519</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10171,8 +10166,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10215,7 +10215,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 62202-2025</t>
+          <t>A 55906-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10229,10 +10229,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46006</v>
+        <v>45973</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10288,7 +10288,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 61972-2025</t>
+          <t>A 55908-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10302,10 +10302,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46003</v>
+        <v>45973</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10317,13 +10317,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10366,7 +10361,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 62801-2025</t>
+          <t>A 43263-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10376,14 +10371,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46008</v>
+        <v>45183</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10396,7 +10391,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>6.6</v>
+        <v>1.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10439,7 +10434,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 62482-2025</t>
+          <t>A 46536-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10453,10 +10448,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46007</v>
+        <v>45582</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10469,7 +10464,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>6.7</v>
+        <v>1.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10512,7 +10507,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 39027-2023</t>
+          <t>A 38212-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10526,10 +10521,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45163</v>
+        <v>45161</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10541,13 +10536,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10590,7 +10580,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 21771-2023</t>
+          <t>A 39027-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10604,10 +10594,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45065</v>
+        <v>45163</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10619,8 +10609,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10663,7 +10658,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 64015-2025</t>
+          <t>A 3130-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10677,10 +10672,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46021</v>
+        <v>45678</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10698,7 +10693,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.9</v>
+        <v>18.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10741,7 +10736,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 64010-2025</t>
+          <t>A 15907-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10751,14 +10746,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46021</v>
+        <v>45405</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10770,13 +10765,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>15.4</v>
+        <v>0.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10819,7 +10809,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 602-2026</t>
+          <t>A 15915-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10829,14 +10819,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46029</v>
+        <v>45405</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10849,7 +10839,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10892,7 +10882,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 1589-2026</t>
+          <t>A 20232-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10906,10 +10896,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46034</v>
+        <v>44698</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10927,7 +10917,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10970,7 +10960,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 1279-2026</t>
+          <t>A 5350-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10984,10 +10974,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46031</v>
+        <v>45692</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11000,7 +10990,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11043,7 +11033,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 1264-2026</t>
+          <t>A 61786-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11057,10 +11047,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46031</v>
+        <v>46002</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11073,7 +11063,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11116,7 +11106,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 1585-2026</t>
+          <t>A 61798-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11130,10 +11120,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46034</v>
+        <v>46002</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11151,7 +11141,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11194,7 +11184,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 1273-2026</t>
+          <t>A 61800-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11208,10 +11198,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46031</v>
+        <v>46002</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11224,7 +11214,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11267,7 +11257,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 35079-2023</t>
+          <t>A 61801-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11281,10 +11271,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45145</v>
+        <v>46002</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11297,7 +11287,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11340,7 +11330,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 1261-2026</t>
+          <t>A 61972-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11354,10 +11344,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46031</v>
+        <v>46003</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11369,8 +11359,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11413,7 +11408,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 1268-2026</t>
+          <t>A 61470-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11427,10 +11422,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46031</v>
+        <v>46001</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11442,8 +11437,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11486,7 +11486,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 45973-2024</t>
+          <t>A 8063-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11500,10 +11500,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45580</v>
+        <v>45707</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11559,7 +11559,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 35229-2023</t>
+          <t>A 32715-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11573,10 +11573,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45145</v>
+        <v>45516</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11632,7 +11632,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 5819-2024</t>
+          <t>A 6465-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11642,14 +11642,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45335</v>
+        <v>45699</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11661,13 +11661,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11710,7 +11705,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 63074-2025</t>
+          <t>A 1749-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11724,10 +11719,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46009</v>
+        <v>45671</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11739,13 +11734,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>8.699999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11788,7 +11778,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 61880-2021</t>
+          <t>A 165-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11802,10 +11792,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44502</v>
+        <v>46024</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11818,7 +11808,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11861,7 +11851,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 165-2026</t>
+          <t>A 63074-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11875,10 +11865,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46024</v>
+        <v>46009</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11890,8 +11880,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11934,7 +11929,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 38212-2023</t>
+          <t>A 17126-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11948,10 +11943,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45161</v>
+        <v>45412</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11964,7 +11959,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12007,7 +12002,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 7375-2026</t>
+          <t>A 4678-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12021,10 +12016,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46059</v>
+        <v>45328</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12037,7 +12032,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12080,7 +12075,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 27087-2024</t>
+          <t>A 21771-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12094,10 +12089,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45471</v>
+        <v>45065</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12110,7 +12105,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12153,7 +12148,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 5350-2025</t>
+          <t>A 64802-2021</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12163,14 +12158,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45692</v>
+        <v>44512</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12183,7 +12178,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12226,7 +12221,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 39920-2024</t>
+          <t>A 63115-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12240,10 +12235,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45553</v>
+        <v>46009</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12256,7 +12251,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12299,7 +12294,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 46536-2024</t>
+          <t>A 16128-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12313,10 +12308,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45582</v>
+        <v>45750</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12328,8 +12323,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 4678-2024</t>
+          <t>A 3149-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12386,10 +12386,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45328</v>
+        <v>45316</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 35095-2023</t>
+          <t>A 61011-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12455,14 +12455,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45145</v>
+        <v>45645</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12518,7 +12518,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 1749-2025</t>
+          <t>A 1337-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12532,10 +12532,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45671</v>
+        <v>46031</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12591,7 +12591,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 15909-2024</t>
+          <t>A 32464-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12601,14 +12601,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45405</v>
+        <v>45838</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.1</v>
+        <v>1.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12664,7 +12664,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 6375-2025</t>
+          <t>A 8067-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12678,10 +12678,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45699</v>
+        <v>45707</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12737,7 +12737,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 32378-2024</t>
+          <t>A 25895-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12751,10 +12751,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45512</v>
+        <v>46178</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12810,7 +12810,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 63115-2025</t>
+          <t>A 25863-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12824,10 +12824,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46009</v>
+        <v>46178</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12883,7 +12883,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 51180-2024</t>
+          <t>A 25816-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12897,10 +12897,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45603</v>
+        <v>46178</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 39190-2023</t>
+          <t>A 25975-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12966,14 +12966,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45166</v>
+        <v>46181</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13029,7 +13029,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 16168-2023</t>
+          <t>A 27274-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13043,10 +13043,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45027</v>
+        <v>46184</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13058,13 +13058,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13107,7 +13102,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 38718-2023</t>
+          <t>A 27292-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13121,10 +13116,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45163</v>
+        <v>46184</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13137,7 +13132,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13180,7 +13175,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 2512-2024</t>
+          <t>A 28718-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13194,10 +13189,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45313</v>
+        <v>46198</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13209,8 +13204,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13253,7 +13253,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 61011-2024</t>
+          <t>A 28704-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13263,14 +13263,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45645</v>
+        <v>46198</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13282,8 +13282,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13326,7 +13331,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 51178-2024</t>
+          <t>A 51180-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13343,7 +13348,7 @@
         <v>45603</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13356,7 +13361,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13399,7 +13404,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 1337-2026</t>
+          <t>A 35229-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13413,10 +13418,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46031</v>
+        <v>45145</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13429,7 +13434,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13472,7 +13477,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 8067-2025</t>
+          <t>A 28908-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13486,10 +13491,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45707</v>
+        <v>46199</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13502,7 +13507,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13545,7 +13550,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 32464-2025</t>
+          <t>A 30155-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13559,10 +13564,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45838</v>
+        <v>46206</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13574,8 +13579,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13618,7 +13628,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 35380-2023</t>
+          <t>A 51178-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13632,10 +13642,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45146</v>
+        <v>45603</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13648,7 +13658,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13691,7 +13701,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 6592-2025</t>
+          <t>A 19157-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13705,10 +13715,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45700</v>
+        <v>45048</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13721,7 +13731,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13764,7 +13774,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 43263-2023</t>
+          <t>A 55971-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13774,14 +13784,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45183</v>
+        <v>45240</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13794,7 +13804,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13837,7 +13847,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 20244-2022</t>
+          <t>A 16164-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13851,10 +13861,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44698</v>
+        <v>45027</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13872,7 +13882,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>9.5</v>
+        <v>1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13915,7 +13925,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 20612-2022</t>
+          <t>A 39024-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13929,10 +13939,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44700</v>
+        <v>45163</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13950,7 +13960,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>8.9</v>
+        <v>4.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13993,7 +14003,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 6421-2025</t>
+          <t>A 50358-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14007,10 +14017,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45699</v>
+        <v>45944</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14023,7 +14033,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14066,7 +14076,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 52469-2023</t>
+          <t>A 47597-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14080,10 +14090,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45225</v>
+        <v>45203</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14096,7 +14106,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14139,7 +14149,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 8063-2025</t>
+          <t>A 31447-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14153,10 +14163,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45707</v>
+        <v>46220</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14169,7 +14179,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14212,7 +14222,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 25895-2026</t>
+          <t>A 14166-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14226,10 +14236,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46178</v>
+        <v>45009</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14242,7 +14252,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14285,7 +14295,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 15790-2025</t>
+          <t>A 15344-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14299,10 +14309,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45748</v>
+        <v>45747</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14358,7 +14368,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 25816-2026</t>
+          <t>A 10335-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14372,10 +14382,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46178</v>
+        <v>44623</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14388,7 +14398,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14431,7 +14441,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 25863-2026</t>
+          <t>A 35095-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14445,10 +14455,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46178</v>
+        <v>45145</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14504,7 +14514,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 25975-2026</t>
+          <t>A 20612-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14518,10 +14528,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46181</v>
+        <v>44700</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14533,8 +14543,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>2.6</v>
+        <v>8.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14577,7 +14592,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 37843-2023</t>
+          <t>A 15198-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14591,10 +14606,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45160</v>
+        <v>44658</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14607,7 +14622,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14650,7 +14665,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 27274-2026</t>
+          <t>A 6375-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14664,10 +14679,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46184</v>
+        <v>45699</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14680,7 +14695,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14723,7 +14738,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 27292-2026</t>
+          <t>A 6592-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14737,10 +14752,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46184</v>
+        <v>45700</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14753,7 +14768,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14796,7 +14811,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 6465-2025</t>
+          <t>A 37843-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14810,10 +14825,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45699</v>
+        <v>45160</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14826,7 +14841,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14869,7 +14884,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 1674-2023</t>
+          <t>A 36824-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14883,10 +14898,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44938</v>
+        <v>46272</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14898,8 +14913,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>2.3</v>
+        <v>8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14942,7 +14962,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 34961-2022</t>
+          <t>A 6506-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14956,10 +14976,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44796</v>
+        <v>45699</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14972,7 +14992,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15015,7 +15035,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 19157-2023</t>
+          <t>A 37482-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15029,10 +15049,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45048</v>
+        <v>46275</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15044,8 +15064,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>0.5</v>
+        <v>16.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15088,7 +15113,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 39024-2023</t>
+          <t>A 37473-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15102,10 +15127,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45163</v>
+        <v>46275</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15117,13 +15142,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15166,7 +15186,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 17126-2024</t>
+          <t>A 37494-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15180,10 +15200,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45412</v>
+        <v>46275</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15196,7 +15216,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15239,7 +15259,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 28908-2026</t>
+          <t>A 37469-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15253,10 +15273,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46199</v>
+        <v>46275</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15269,7 +15289,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15312,7 +15332,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 28704-2026</t>
+          <t>A 5283-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15326,10 +15346,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46198</v>
+        <v>45331</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15341,13 +15361,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15390,7 +15405,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 28718-2026</t>
+          <t>A 38723-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15404,10 +15419,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46198</v>
+        <v>45163</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15419,13 +15434,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15468,7 +15478,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 11193-2023</t>
+          <t>A 50387-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15478,14 +15488,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44992</v>
+        <v>45600</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15498,7 +15508,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.9</v>
+        <v>8.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15541,7 +15551,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 26949-2023</t>
+          <t>A 2512-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15555,10 +15565,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45093</v>
+        <v>45313</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15571,7 +15581,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15614,7 +15624,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 6506-2025</t>
+          <t>A 64709-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15628,10 +15638,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45699</v>
+        <v>45281</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15644,7 +15654,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15687,7 +15697,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 30155-2026</t>
+          <t>A 64710-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15701,10 +15711,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46206</v>
+        <v>45281</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15716,13 +15726,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>5.8</v>
+        <v>0.1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15765,7 +15770,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 12332-2023</t>
+          <t>A 36730-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15779,10 +15784,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44999</v>
+        <v>45153</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15795,7 +15800,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15838,7 +15843,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 36075-2023</t>
+          <t>A 16168-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15852,10 +15857,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45149</v>
+        <v>45027</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15867,8 +15872,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15911,7 +15921,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 15198-2022</t>
+          <t>A 21770-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15925,10 +15935,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>44658</v>
+        <v>45065</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15941,7 +15951,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15984,7 +15994,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 6456-2025</t>
+          <t>A 36099-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15998,10 +16008,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45699</v>
+        <v>45533</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16014,7 +16024,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16057,7 +16067,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 21855-2022</t>
+          <t>A 38718-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16071,10 +16081,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44709</v>
+        <v>45163</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16087,7 +16097,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16130,7 +16140,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 72603-2021</t>
+          <t>A 15906-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16140,14 +16150,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44546</v>
+        <v>45405</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16160,7 +16170,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16203,7 +16213,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 9448-2023</t>
+          <t>A 35097-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16217,10 +16227,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44981</v>
+        <v>45145</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16233,7 +16243,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16276,7 +16286,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 64709-2023</t>
+          <t>A 30945-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16290,10 +16300,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45281</v>
+        <v>45113</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16306,7 +16316,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16349,7 +16359,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 64710-2023</t>
+          <t>A 30964-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16363,10 +16373,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45281</v>
+        <v>45113</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16379,7 +16389,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16422,7 +16432,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 35097-2023</t>
+          <t>A 48325-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16432,14 +16442,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45145</v>
+        <v>44858</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16451,8 +16461,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16495,7 +16510,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 35411-2023</t>
+          <t>A 11699-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16509,10 +16524,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45146</v>
+        <v>45373</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16525,7 +16540,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16568,7 +16583,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 36730-2023</t>
+          <t>A 11704-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16582,10 +16597,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45153</v>
+        <v>45373</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16598,7 +16613,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16641,7 +16656,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 25729-2023</t>
+          <t>A 11193-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16651,14 +16666,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45084</v>
+        <v>44992</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16671,7 +16686,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16714,7 +16729,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 11699-2024</t>
+          <t>A 8049-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16728,10 +16743,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45373</v>
+        <v>45707</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16744,7 +16759,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16787,7 +16802,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 11704-2024</t>
+          <t>A 30389-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16801,10 +16816,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45373</v>
+        <v>45491</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16817,7 +16832,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16860,7 +16875,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 54590-2024</t>
+          <t>A 35380-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16874,10 +16889,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45617</v>
+        <v>45146</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16890,7 +16905,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16933,7 +16948,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 50358-2025</t>
+          <t>A 54419-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16947,10 +16962,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45944</v>
+        <v>45617</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16962,8 +16977,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>4.1</v>
+        <v>22.7</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17006,7 +17026,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 10335-2022</t>
+          <t>A 34961-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17020,10 +17040,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44623</v>
+        <v>44796</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17036,7 +17056,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17079,7 +17099,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 31447-2026</t>
+          <t>A 14185-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17093,10 +17113,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46220</v>
+        <v>45009</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17109,7 +17129,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17152,7 +17172,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 33375-2024</t>
+          <t>A 27087-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17166,10 +17186,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45519</v>
+        <v>45471</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17181,13 +17201,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17230,7 +17245,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 5513-2025</t>
+          <t>A 6368-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17244,10 +17259,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45693</v>
+        <v>45699</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17260,7 +17275,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17303,7 +17318,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 15813-2022</t>
+          <t>A 39190-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17313,14 +17328,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44664</v>
+        <v>45166</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17332,13 +17347,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17381,7 +17391,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 6368-2025</t>
+          <t>A 54590-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17395,10 +17405,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45699</v>
+        <v>45617</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17411,7 +17421,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17454,7 +17464,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 44069-2023</t>
+          <t>A 14993-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17468,10 +17478,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45188</v>
+        <v>45015</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17484,7 +17494,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17527,7 +17537,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 3198-2024</t>
+          <t>A 52469-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17541,10 +17551,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45316</v>
+        <v>45225</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17557,7 +17567,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17600,7 +17610,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 16270-2024</t>
+          <t>A 19350-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17614,10 +17624,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45407</v>
+        <v>45049</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17630,7 +17640,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17673,7 +17683,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 36824-2026</t>
+          <t>A 51041-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17687,10 +17697,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46272</v>
+        <v>45603</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17702,13 +17712,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>8</v>
+        <v>0.4</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17751,7 +17756,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 37473-2026</t>
+          <t>A 11972-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17765,10 +17770,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46275</v>
+        <v>44994</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17781,7 +17786,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17824,7 +17829,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 51041-2024</t>
+          <t>A 12332-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17838,10 +17843,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45603</v>
+        <v>44999</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17897,7 +17902,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 6557-2025</t>
+          <t>A 38266-2022</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17911,10 +17916,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45699</v>
+        <v>44812</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17927,7 +17932,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17970,7 +17975,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 15344-2025</t>
+          <t>A 1323-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17984,10 +17989,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45747</v>
+        <v>44936</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18000,7 +18005,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18043,7 +18048,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 37482-2026</t>
+          <t>A 14736-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18053,14 +18058,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46275</v>
+        <v>45397</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18072,13 +18077,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I230" t="n">
-        <v>16.5</v>
+        <v>1.3</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18121,7 +18121,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 37469-2026</t>
+          <t>A 25729-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18135,10 +18135,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46275</v>
+        <v>45084</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 50387-2024</t>
+          <t>A 30388-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18208,10 +18208,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45600</v>
+        <v>45491</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>8.5</v>
+        <v>1.9</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18267,7 +18267,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 37494-2026</t>
+          <t>A 21855-2022</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18281,10 +18281,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46275</v>
+        <v>44709</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18340,7 +18340,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 32715-2024</t>
+          <t>A 72603-2021</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18354,10 +18354,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45516</v>
+        <v>44546</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18413,7 +18413,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 38259-2023</t>
+          <t>A 14750-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18427,10 +18427,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45161</v>
+        <v>45014</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18486,7 +18486,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 21530-2025</t>
+          <t>A 47600-2023</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18500,10 +18500,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45782</v>
+        <v>45203</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18576,7 +18576,7 @@
         <v>45782</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 3554-2025</t>
+          <t>A 21530-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18646,10 +18646,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45680</v>
+        <v>45782</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18705,7 +18705,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 50818-2023</t>
+          <t>A 3554-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18719,10 +18719,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45217</v>
+        <v>45680</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18778,7 +18778,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 21336-2025</t>
+          <t>A 50818-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18792,10 +18792,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45782</v>
+        <v>45217</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18868,7 +18868,7 @@
         <v>45376</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>44879</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>

--- a/Översikt ÖDESHÖG.xlsx
+++ b/Översikt ÖDESHÖG.xlsx
@@ -601,7 +601,7 @@
         <v>45805</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45723</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44698</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 35443-2022</t>
+          <t>A 15823-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -947,14 +947,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44798</v>
+        <v>44664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -966,17 +966,22 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>4.7</v>
+        <v>6.5</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -991,7 +996,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1003,264 +1008,259 @@
         <v>2</v>
       </c>
       <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa
+Hasselmus</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 15823-2022 artfynd.xlsx", "A 15823-2022")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 15823-2022 karta.png", "A 15823-2022")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 15823-2022 georefererad karta.tif", "A 15823-2022")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 15823-2022 FSC-klagomål.docx", "A 15823-2022")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 15823-2022 FSC-klagomål mail.docx", "A 15823-2022")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 15823-2022 tillsynsbegäran.docx", "A 15823-2022")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 15823-2022 tillsynsbegäran mail.docx", "A 15823-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 56797-2023</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45244</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 56797-2023 artfynd.xlsx", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 56797-2023 karta.png", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 56797-2023 georefererad karta.tif", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 56797-2023 FSC-klagomål.docx", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 56797-2023 FSC-klagomål mail.docx", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 56797-2023 tillsynsbegäran.docx", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 56797-2023 tillsynsbegäran mail.docx", "A 56797-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 35443-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44798</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Axveronika
 Bivråk</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 35443-2022 artfynd.xlsx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 35443-2022 karta.png", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 35443-2022 georefererad karta.tif", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 35443-2022 FSC-klagomål.docx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 35443-2022 FSC-klagomål mail.docx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 35443-2022 tillsynsbegäran.docx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 35443-2022 tillsynsbegäran mail.docx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/fåglar/A 35443-2022 prioriterade fågelarter.docx", "A 35443-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A 15823-2022</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44664</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Trubbfjädermossa
-Hasselmus</t>
-        </is>
-      </c>
-      <c r="W6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 15823-2022 artfynd.xlsx", "A 15823-2022")</f>
-        <v/>
-      </c>
-      <c r="X6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 15823-2022 karta.png", "A 15823-2022")</f>
-        <v/>
-      </c>
-      <c r="Y6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 15823-2022 georefererad karta.tif", "A 15823-2022")</f>
-        <v/>
-      </c>
-      <c r="AA6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 15823-2022 FSC-klagomål.docx", "A 15823-2022")</f>
-        <v/>
-      </c>
-      <c r="AB6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 15823-2022 FSC-klagomål mail.docx", "A 15823-2022")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 15823-2022 tillsynsbegäran.docx", "A 15823-2022")</f>
-        <v/>
-      </c>
-      <c r="AD6">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 15823-2022 tillsynsbegäran mail.docx", "A 15823-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 56797-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45244</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 56797-2023 artfynd.xlsx", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 56797-2023 karta.png", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 56797-2023 georefererad karta.tif", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 56797-2023 FSC-klagomål.docx", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 56797-2023 FSC-klagomål mail.docx", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 56797-2023 tillsynsbegäran.docx", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 56797-2023 tillsynsbegäran mail.docx", "A 56797-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 15437-2025</t>
+          <t>A 71038-2021</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45747</v>
+        <v>44538</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1398,25 +1398,20 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>11.9</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1428,10 +1423,10 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1444,1102 +1439,1107 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 71038-2021 artfynd.xlsx", "A 71038-2021")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 71038-2021 karta.png", "A 71038-2021")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 71038-2021 georefererad karta.tif", "A 71038-2021")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 71038-2021 FSC-klagomål.docx", "A 71038-2021")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 71038-2021 FSC-klagomål mail.docx", "A 71038-2021")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 71038-2021 tillsynsbegäran.docx", "A 71038-2021")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 71038-2021 tillsynsbegäran mail.docx", "A 71038-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 58551-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45251</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58551-2023 artfynd.xlsx", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58551-2023 karta.png", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58551-2023 georefererad karta.tif", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58551-2023 FSC-klagomål.docx", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58551-2023 FSC-klagomål mail.docx", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58551-2023 tillsynsbegäran.docx", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58551-2023 tillsynsbegäran mail.docx", "A 58551-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 32776-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Smalsprötad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32776-2025 artfynd.xlsx", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32776-2025 karta.png", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32776-2025 georefererad karta.tif", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32776-2025 FSC-klagomål.docx", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32776-2025 FSC-klagomål mail.docx", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32776-2025 tillsynsbegäran.docx", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32776-2025 tillsynsbegäran mail.docx", "A 32776-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 50774-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Mörk dunört</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 50774-2023 artfynd.xlsx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 50774-2023 karta.png", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 50774-2023 georefererad karta.tif", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 50774-2023 FSC-klagomål.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 50774-2023 FSC-klagomål mail.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 50774-2023 tillsynsbegäran.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 50774-2023 tillsynsbegäran mail.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 15437-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>Knärot</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 15437-2025 artfynd.xlsx", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 15437-2025 karta.png", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 15437-2025 georefererad karta.tif", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/knärot/A 15437-2025 karta knärot.png", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 15437-2025 FSC-klagomål.docx", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 15437-2025 FSC-klagomål mail.docx", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 15437-2025 tillsynsbegäran.docx", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 15437-2025 tillsynsbegäran mail.docx", "A 15437-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 71038-2021</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44538</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 32713-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45516</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Stubbspretmossa</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 71038-2021 artfynd.xlsx", "A 71038-2021")</f>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Kristinspindling</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32713-2024 artfynd.xlsx", "A 32713-2024")</f>
         <v/>
       </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 71038-2021 karta.png", "A 71038-2021")</f>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32713-2024 karta.png", "A 32713-2024")</f>
         <v/>
       </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 71038-2021 georefererad karta.tif", "A 71038-2021")</f>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32713-2024 georefererad karta.tif", "A 32713-2024")</f>
         <v/>
       </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 71038-2021 FSC-klagomål.docx", "A 71038-2021")</f>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32713-2024 FSC-klagomål.docx", "A 32713-2024")</f>
         <v/>
       </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 71038-2021 FSC-klagomål mail.docx", "A 71038-2021")</f>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32713-2024 FSC-klagomål mail.docx", "A 32713-2024")</f>
         <v/>
       </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 71038-2021 tillsynsbegäran.docx", "A 71038-2021")</f>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32713-2024 tillsynsbegäran.docx", "A 32713-2024")</f>
         <v/>
       </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 71038-2021 tillsynsbegäran mail.docx", "A 71038-2021")</f>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32713-2024 tillsynsbegäran mail.docx", "A 32713-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 62988-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45272</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>19</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 62988-2023 artfynd.xlsx", "A 62988-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 62988-2023 karta.png", "A 62988-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 62988-2023 georefererad karta.tif", "A 62988-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 62988-2023 FSC-klagomål.docx", "A 62988-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 62988-2023 FSC-klagomål mail.docx", "A 62988-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 62988-2023 tillsynsbegäran.docx", "A 62988-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 62988-2023 tillsynsbegäran mail.docx", "A 62988-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 38720-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Hässleklocka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 38720-2023 artfynd.xlsx", "A 38720-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 38720-2023 karta.png", "A 38720-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 38720-2023 georefererad karta.tif", "A 38720-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 38720-2023 FSC-klagomål.docx", "A 38720-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 38720-2023 FSC-klagomål mail.docx", "A 38720-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 38720-2023 tillsynsbegäran.docx", "A 38720-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 38720-2023 tillsynsbegäran mail.docx", "A 38720-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 56637-2023</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>45243</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>2.9</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>1</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R17" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S17" t="n">
         <v>1</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T17" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Skogsalm</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 56637-2023 artfynd.xlsx", "A 56637-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 56637-2023 karta.png", "A 56637-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 56637-2023 georefererad karta.tif", "A 56637-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 56637-2023 FSC-klagomål.docx", "A 56637-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 56637-2023 FSC-klagomål mail.docx", "A 56637-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 56637-2023 tillsynsbegäran.docx", "A 56637-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 56637-2023 tillsynsbegäran mail.docx", "A 56637-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 58052-2021</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44487</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58052-2021 artfynd.xlsx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58052-2021 karta.png", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58052-2021 georefererad karta.tif", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58052-2021 FSC-klagomål.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58052-2021 FSC-klagomål mail.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58052-2021 tillsynsbegäran.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58052-2021 tillsynsbegäran mail.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 4772-2022</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>44592</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>1.2</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>1</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R19" t="n">
         <v>1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S19" t="n">
         <v>1</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T19" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 4772-2022 artfynd.xlsx", "A 4772-2022")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 4772-2022 karta.png", "A 4772-2022")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 4772-2022 georefererad karta.tif", "A 4772-2022")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 4772-2022 FSC-klagomål.docx", "A 4772-2022")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 4772-2022 FSC-klagomål mail.docx", "A 4772-2022")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 4772-2022 tillsynsbegäran.docx", "A 4772-2022")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 4772-2022 tillsynsbegäran mail.docx", "A 4772-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 50774-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Mörk dunört</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 50774-2023 artfynd.xlsx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 50774-2023 karta.png", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 50774-2023 georefererad karta.tif", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 50774-2023 FSC-klagomål.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 50774-2023 FSC-klagomål mail.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 50774-2023 tillsynsbegäran.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 50774-2023 tillsynsbegäran mail.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 58052-2021</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44487</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Granbarkgnagare</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58052-2021 artfynd.xlsx", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58052-2021 karta.png", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58052-2021 georefererad karta.tif", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58052-2021 FSC-klagomål.docx", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58052-2021 FSC-klagomål mail.docx", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58052-2021 tillsynsbegäran.docx", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58052-2021 tillsynsbegäran mail.docx", "A 58052-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 58551-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45251</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58551-2023 artfynd.xlsx", "A 58551-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58551-2023 karta.png", "A 58551-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58551-2023 georefererad karta.tif", "A 58551-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58551-2023 FSC-klagomål.docx", "A 58551-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58551-2023 FSC-klagomål mail.docx", "A 58551-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58551-2023 tillsynsbegäran.docx", "A 58551-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58551-2023 tillsynsbegäran mail.docx", "A 58551-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 62988-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>19</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 62988-2023 artfynd.xlsx", "A 62988-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 62988-2023 karta.png", "A 62988-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 62988-2023 georefererad karta.tif", "A 62988-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 62988-2023 FSC-klagomål.docx", "A 62988-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 62988-2023 FSC-klagomål mail.docx", "A 62988-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 62988-2023 tillsynsbegäran.docx", "A 62988-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 62988-2023 tillsynsbegäran mail.docx", "A 62988-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 38720-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45163</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Hässleklocka</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 38720-2023 artfynd.xlsx", "A 38720-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 38720-2023 karta.png", "A 38720-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 38720-2023 georefererad karta.tif", "A 38720-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 38720-2023 FSC-klagomål.docx", "A 38720-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 38720-2023 FSC-klagomål mail.docx", "A 38720-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 38720-2023 tillsynsbegäran.docx", "A 38720-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 38720-2023 tillsynsbegäran mail.docx", "A 38720-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 32713-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45516</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Kristinspindling</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32713-2024 artfynd.xlsx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32713-2024 karta.png", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32713-2024 georefererad karta.tif", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32713-2024 FSC-klagomål.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32713-2024 FSC-klagomål mail.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32713-2024 tillsynsbegäran.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32713-2024 tillsynsbegäran mail.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 32776-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45839</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Smalsprötad bastardsvärmare</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32776-2025 artfynd.xlsx", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32776-2025 karta.png", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32776-2025 georefererad karta.tif", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32776-2025 FSC-klagomål.docx", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32776-2025 FSC-klagomål mail.docx", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32776-2025 tillsynsbegäran.docx", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32776-2025 tillsynsbegäran mail.docx", "A 32776-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44538</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>44614</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>44803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>44510</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44504</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44462</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>44517</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 20244-2022</t>
+          <t>A 16152-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44698</v>
+        <v>44666</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3380,13 +3380,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>9.5</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3429,7 +3424,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 16152-2022</t>
+          <t>A 29967-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3443,10 +3438,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44666</v>
+        <v>44756</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3459,7 +3454,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3502,7 +3497,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 15906-2024</t>
+          <t>A 34979-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3512,14 +3507,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45405</v>
+        <v>44796</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3532,7 +3527,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3575,7 +3570,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20612-2022</t>
+          <t>A 6705-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3589,10 +3584,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44700</v>
+        <v>45342</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3610,7 +3605,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3653,7 +3648,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 29967-2022</t>
+          <t>A 15790-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3667,10 +3662,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44756</v>
+        <v>45748</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3683,7 +3678,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3726,7 +3721,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 34979-2022</t>
+          <t>A 5819-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3736,14 +3731,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44796</v>
+        <v>45335</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3755,8 +3750,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3799,7 +3799,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 6421-2025</t>
+          <t>A 35661-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45699</v>
+        <v>45532</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3872,7 +3872,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 52469-2023</t>
+          <t>A 36114-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45225</v>
+        <v>44803</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3945,7 +3945,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8063-2025</t>
+          <t>A 3198-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3959,10 +3959,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45707</v>
+        <v>45316</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4018,7 +4018,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 36114-2022</t>
+          <t>A 26949-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44803</v>
+        <v>45093</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4091,7 +4091,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 47600-2023</t>
+          <t>A 22088-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45203</v>
+        <v>45069</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 15790-2025</t>
+          <t>A 8256-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4174,14 +4174,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45748</v>
+        <v>44974</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4237,7 +4237,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37843-2023</t>
+          <t>A 15813-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4247,14 +4247,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45160</v>
+        <v>44664</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4266,8 +4266,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4310,7 +4315,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 39024-2023</t>
+          <t>A 38152-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4324,10 +4329,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45163</v>
+        <v>45161</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4339,13 +4344,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 6465-2025</t>
+          <t>A 44069-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45699</v>
+        <v>45188</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1674-2023</t>
+          <t>A 56841-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44938</v>
+        <v>44894</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 34961-2022</t>
+          <t>A 1578-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44796</v>
+        <v>44937</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 19157-2023</t>
+          <t>A 11280-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45048</v>
+        <v>45726</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 30389-2024</t>
+          <t>A 15909-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4690,14 +4690,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45491</v>
+        <v>45405</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.6</v>
+        <v>0.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4753,7 +4753,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 1578-2023</t>
+          <t>A 38259-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4767,10 +4767,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44937</v>
+        <v>45161</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.7</v>
+        <v>2.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 54226-2021</t>
+          <t>A 39032-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44470</v>
+        <v>45163</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4855,8 +4855,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4899,7 +4904,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 48325-2022</t>
+          <t>A 39920-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4909,14 +4914,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44858</v>
+        <v>45553</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4928,13 +4933,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4977,7 +4977,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 47993-2024</t>
+          <t>A 45973-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45589</v>
+        <v>45580</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5050,7 +5050,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 64802-2021</t>
+          <t>A 9448-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5060,14 +5060,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44512</v>
+        <v>44981</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 6164-2024</t>
+          <t>A 602-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45337</v>
+        <v>46029</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5196,7 +5196,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 6705-2024</t>
+          <t>A 54226-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5210,10 +5210,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45342</v>
+        <v>44470</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5225,13 +5225,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>8.300000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5274,7 +5269,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 35661-2024</t>
+          <t>A 46528-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5288,10 +5283,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45532</v>
+        <v>45582</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5304,7 +5299,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5347,7 +5342,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56841-2022</t>
+          <t>A 1279-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5361,10 +5356,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44894</v>
+        <v>46031</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5377,7 +5372,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5420,7 +5415,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 1323-2023</t>
+          <t>A 1261-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5434,10 +5429,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44936</v>
+        <v>46031</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5450,7 +5445,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5493,7 +5488,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 12859-2026</t>
+          <t>A 1268-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5507,10 +5502,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46092</v>
+        <v>46031</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5523,7 +5518,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5566,7 +5561,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 32335-2024</t>
+          <t>A 36075-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5580,10 +5575,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45512</v>
+        <v>45149</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5596,7 +5591,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5639,7 +5634,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 12872-2026</t>
+          <t>A 1264-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5653,10 +5648,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46092</v>
+        <v>46031</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5669,7 +5664,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5712,7 +5707,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 41730-2025</t>
+          <t>A 1273-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5726,10 +5721,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45902</v>
+        <v>46031</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5785,7 +5780,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 14617-2026</t>
+          <t>A 1674-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5799,10 +5794,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46101</v>
+        <v>44938</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5815,7 +5810,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5858,7 +5853,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30388-2024</t>
+          <t>A 35079-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5872,10 +5867,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45491</v>
+        <v>45145</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5888,7 +5883,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5931,7 +5926,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 3149-2024</t>
+          <t>A 1585-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5945,10 +5940,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45316</v>
+        <v>46034</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5960,8 +5955,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6004,7 +6004,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 47597-2023</t>
+          <t>A 6421-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6018,10 +6018,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45203</v>
+        <v>45699</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15907-2024</t>
+          <t>A 6456-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6087,14 +6087,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45405</v>
+        <v>45699</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 15915-2024</t>
+          <t>A 17618-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6160,14 +6160,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45405</v>
+        <v>45416</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6223,7 +6223,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 16341-2026</t>
+          <t>A 47993-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6237,10 +6237,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46111</v>
+        <v>45589</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6252,13 +6252,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6301,7 +6296,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 16402-2026</t>
+          <t>A 41730-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6315,10 +6310,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46111</v>
+        <v>45902</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6330,13 +6325,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6379,7 +6369,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 16414-2026</t>
+          <t>A 30600-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6393,10 +6383,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46111</v>
+        <v>45831</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6408,13 +6398,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>8.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6457,7 +6442,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 16370-2026</t>
+          <t>A 1589-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6471,10 +6456,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46111</v>
+        <v>46034</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6492,7 +6477,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.9</v>
+        <v>3.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6535,7 +6520,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17618-2024</t>
+          <t>A 5513-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6549,10 +6534,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45416</v>
+        <v>45693</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6565,7 +6550,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6608,7 +6593,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 39024-2023</t>
+          <t>A 6164-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6622,10 +6607,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45163</v>
+        <v>45337</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6637,13 +6622,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6686,7 +6666,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13129-2023</t>
+          <t>A 14156-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6700,10 +6680,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45002</v>
+        <v>45009</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6716,7 +6696,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6759,7 +6739,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 5283-2024</t>
+          <t>A 13129-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6773,10 +6753,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45331</v>
+        <v>45002</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6789,7 +6769,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6832,7 +6812,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 14750-2023</t>
+          <t>A 32466-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6846,10 +6826,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45014</v>
+        <v>45838</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6862,7 +6842,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6905,7 +6885,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 46059-2025</t>
+          <t>A 32476-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6919,10 +6899,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45924</v>
+        <v>45838</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6935,7 +6915,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6978,7 +6958,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 14156-2023</t>
+          <t>A 35411-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6992,10 +6972,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45009</v>
+        <v>45146</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7008,7 +6988,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7051,7 +7031,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 46788-2025</t>
+          <t>A 16270-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7065,10 +7045,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45926</v>
+        <v>45407</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7081,7 +7061,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7124,7 +7104,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 46778-2025</t>
+          <t>A 46059-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7138,10 +7118,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45926</v>
+        <v>45924</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7154,7 +7134,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7197,7 +7177,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 46999-2025</t>
+          <t>A 46778-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7211,10 +7191,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45929</v>
+        <v>45926</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7227,7 +7207,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7270,7 +7250,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 48063-2025</t>
+          <t>A 46999-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7284,10 +7264,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45932</v>
+        <v>45929</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7300,7 +7280,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7343,7 +7323,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 46528-2024</t>
+          <t>A 46788-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7357,10 +7337,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45582</v>
+        <v>45926</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7373,7 +7353,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7433,7 +7413,7 @@
         <v>45931</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7489,7 +7469,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 17126-2024</t>
+          <t>A 20244-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7503,10 +7483,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45412</v>
+        <v>44698</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7518,8 +7498,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>9.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7562,7 +7547,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 16259-2026</t>
+          <t>A 6557-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7576,10 +7561,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46109</v>
+        <v>45699</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7592,7 +7577,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7635,7 +7620,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 16262-2026</t>
+          <t>A 32378-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7649,10 +7634,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46109</v>
+        <v>45512</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7665,7 +7650,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7708,7 +7693,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 48575-2025</t>
+          <t>A 48063-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7722,10 +7707,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45936</v>
+        <v>45932</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7738,7 +7723,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7781,7 +7766,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 17950-2026</t>
+          <t>A 48611-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7795,10 +7780,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46122</v>
+        <v>45936</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7811,7 +7796,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.6</v>
+        <v>0.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7854,7 +7839,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 48611-2025</t>
+          <t>A 48614-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7871,7 +7856,7 @@
         <v>45936</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7884,7 +7869,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7927,7 +7912,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 48614-2025</t>
+          <t>A 48575-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7944,7 +7929,7 @@
         <v>45936</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7957,7 +7942,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8017,7 +8002,7 @@
         <v>45944</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8073,7 +8058,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 8256-2023</t>
+          <t>A 19351-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8083,14 +8068,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44974</v>
+        <v>45049</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8103,7 +8088,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8146,7 +8131,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 22088-2023</t>
+          <t>A 51171-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8160,10 +8145,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45069</v>
+        <v>45947</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8176,7 +8161,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8219,7 +8204,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 36099-2024</t>
+          <t>A 51328-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8233,10 +8218,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45533</v>
+        <v>45950</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8249,7 +8234,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8292,7 +8277,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 51171-2025</t>
+          <t>A 32335-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8306,10 +8291,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45947</v>
+        <v>45512</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8322,7 +8307,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8365,7 +8350,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 51328-2025</t>
+          <t>A 8515-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8379,10 +8364,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45950</v>
+        <v>44613</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8395,7 +8380,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8438,7 +8423,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 39027-2023</t>
+          <t>A 61880-2021</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8452,10 +8437,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45163</v>
+        <v>44502</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8467,13 +8452,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8516,7 +8496,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 14736-2024</t>
+          <t>A 7375-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8526,14 +8506,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45397</v>
+        <v>46059</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8546,7 +8526,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8589,7 +8569,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 20232-2022</t>
+          <t>A 39024-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8603,10 +8583,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44698</v>
+        <v>45163</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8624,7 +8604,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8667,7 +8647,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 14185-2023</t>
+          <t>A 8118-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8681,10 +8661,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45009</v>
+        <v>46062</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8697,7 +8677,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>13.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8740,7 +8720,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 14166-2023</t>
+          <t>A 33375-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8754,10 +8734,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45009</v>
+        <v>45519</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8769,8 +8749,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8813,7 +8798,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 19350-2023</t>
+          <t>A 20720-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8827,10 +8812,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45049</v>
+        <v>45776</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8843,7 +8828,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8886,7 +8871,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 20720-2025</t>
+          <t>A 55901-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8900,10 +8885,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45776</v>
+        <v>45973</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8916,7 +8901,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8959,7 +8944,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 63074-2025</t>
+          <t>A 55906-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8973,10 +8958,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46009</v>
+        <v>45973</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8988,13 +8973,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>8.699999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9037,7 +9017,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 11972-2023</t>
+          <t>A 43263-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9047,14 +9027,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44994</v>
+        <v>45183</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9067,7 +9047,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9127,7 +9107,7 @@
         <v>45973</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9183,7 +9163,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 55901-2025</t>
+          <t>A 46536-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9197,10 +9177,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45973</v>
+        <v>45582</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9213,7 +9193,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9256,7 +9236,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 55906-2025</t>
+          <t>A 38212-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9270,10 +9250,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45973</v>
+        <v>45161</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9286,7 +9266,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9329,7 +9309,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 165-2026</t>
+          <t>A 3130-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9343,10 +9323,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46024</v>
+        <v>45678</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9358,8 +9338,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>3</v>
+        <v>18.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9402,7 +9387,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 11193-2023</t>
+          <t>A 15907-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9416,10 +9401,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44992</v>
+        <v>45405</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9432,7 +9417,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9475,7 +9460,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 5350-2025</t>
+          <t>A 15915-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9485,14 +9470,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45692</v>
+        <v>45405</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9505,7 +9490,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9548,7 +9533,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 54419-2024</t>
+          <t>A 20232-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9562,10 +9547,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45617</v>
+        <v>44698</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9583,7 +9568,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>22.7</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9626,7 +9611,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 39032-2023</t>
+          <t>A 61786-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9640,10 +9625,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45163</v>
+        <v>46002</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9655,13 +9640,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9704,7 +9684,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 14993-2023</t>
+          <t>A 8063-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9718,10 +9698,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45015</v>
+        <v>45707</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9734,7 +9714,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9777,7 +9757,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 26949-2023</t>
+          <t>A 61798-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9791,10 +9771,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45093</v>
+        <v>46002</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9806,8 +9786,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9850,7 +9835,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 11280-2025</t>
+          <t>A 61800-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9864,10 +9849,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45726</v>
+        <v>46002</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9880,7 +9865,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9923,7 +9908,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 8049-2025</t>
+          <t>A 61801-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9937,10 +9922,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45707</v>
+        <v>46002</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9953,7 +9938,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9996,7 +9981,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 61801-2025</t>
+          <t>A 61972-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10010,10 +9995,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10025,8 +10010,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10086,7 +10076,7 @@
         <v>46001</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10147,7 +10137,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 61798-2025</t>
+          <t>A 61629-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10164,7 +10154,7 @@
         <v>46002</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10176,13 +10166,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10225,7 +10210,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 61800-2025</t>
+          <t>A 32715-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10239,10 +10224,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46002</v>
+        <v>45516</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10255,7 +10240,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10298,7 +10283,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 61629-2025</t>
+          <t>A 12872-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10312,10 +10297,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46002</v>
+        <v>46092</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10328,7 +10313,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10371,7 +10356,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 38152-2023</t>
+          <t>A 6465-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10385,10 +10370,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45161</v>
+        <v>45699</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10401,7 +10386,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10444,7 +10429,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 61786-2025</t>
+          <t>A 1749-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10458,10 +10443,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46002</v>
+        <v>45671</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10474,7 +10459,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10517,7 +10502,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 62202-2025</t>
+          <t>A 62482-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10531,10 +10516,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10547,7 +10532,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>5.1</v>
+        <v>6.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10590,7 +10575,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 8515-2022</t>
+          <t>A 62202-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10604,10 +10589,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44613</v>
+        <v>46006</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10620,7 +10605,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10663,7 +10648,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 61972-2025</t>
+          <t>A 62801-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10677,10 +10662,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10692,13 +10677,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10741,7 +10721,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 38723-2023</t>
+          <t>A 12859-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10755,10 +10735,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45163</v>
+        <v>46092</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10771,7 +10751,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10814,7 +10794,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 62801-2025</t>
+          <t>A 64010-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10828,10 +10808,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46008</v>
+        <v>46021</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10843,8 +10823,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>6.6</v>
+        <v>15.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10887,7 +10872,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 63115-2025</t>
+          <t>A 64015-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10901,10 +10886,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46009</v>
+        <v>46021</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10916,8 +10901,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10960,7 +10950,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 62482-2025</t>
+          <t>A 17126-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10974,10 +10964,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46007</v>
+        <v>45412</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10990,7 +10980,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>6.7</v>
+        <v>0.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11033,7 +11023,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 3130-2025</t>
+          <t>A 14617-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11047,10 +11037,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45678</v>
+        <v>46101</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11062,13 +11052,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>18.6</v>
+        <v>0.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11111,7 +11096,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 16128-2025</t>
+          <t>A 4678-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11125,10 +11110,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45750</v>
+        <v>45328</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11140,13 +11125,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11189,7 +11169,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 55971-2023</t>
+          <t>A 21771-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11203,10 +11183,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45240</v>
+        <v>45065</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11219,7 +11199,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.6</v>
+        <v>5.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11262,7 +11242,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 30945-2023</t>
+          <t>A 16370-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11276,10 +11256,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45113</v>
+        <v>46111</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11291,8 +11271,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>2.9</v>
+        <v>6.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11335,7 +11320,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 16164-2023</t>
+          <t>A 64802-2021</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11345,14 +11330,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45027</v>
+        <v>44512</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11364,13 +11349,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11413,7 +11393,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 64015-2025</t>
+          <t>A 16414-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11427,10 +11407,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46021</v>
+        <v>46111</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11448,7 +11428,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11491,7 +11471,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 64010-2025</t>
+          <t>A 16402-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11505,10 +11485,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46021</v>
+        <v>46111</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11526,7 +11506,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>15.4</v>
+        <v>2.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11569,7 +11549,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 61011-2024</t>
+          <t>A 16341-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11579,14 +11559,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45645</v>
+        <v>46111</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11598,8 +11578,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11642,7 +11627,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 602-2026</t>
+          <t>A 16128-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11656,10 +11641,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46029</v>
+        <v>45750</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11671,8 +11656,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11715,7 +11705,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 1337-2026</t>
+          <t>A 3149-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11729,10 +11719,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46031</v>
+        <v>45316</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11745,7 +11735,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11788,7 +11778,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 1589-2026</t>
+          <t>A 16259-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11802,10 +11792,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46034</v>
+        <v>46109</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11817,13 +11807,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11866,7 +11851,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 1279-2026</t>
+          <t>A 16262-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11880,10 +11865,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46031</v>
+        <v>46109</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11896,7 +11881,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11939,7 +11924,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 1264-2026</t>
+          <t>A 17950-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11953,10 +11938,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46031</v>
+        <v>46122</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11969,7 +11954,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12012,7 +11997,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 8067-2025</t>
+          <t>A 51180-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12026,10 +12011,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45707</v>
+        <v>45603</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12042,7 +12027,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12085,7 +12070,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 32464-2025</t>
+          <t>A 35229-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12099,10 +12084,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45838</v>
+        <v>45145</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12115,7 +12100,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12158,7 +12143,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 1585-2026</t>
+          <t>A 51178-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12172,10 +12157,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46034</v>
+        <v>45603</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12187,13 +12172,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12236,7 +12216,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 1273-2026</t>
+          <t>A 19157-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12250,10 +12230,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46031</v>
+        <v>45048</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12266,7 +12246,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12309,7 +12289,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 1261-2026</t>
+          <t>A 55971-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12323,10 +12303,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46031</v>
+        <v>45240</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12339,7 +12319,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12382,7 +12362,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 1268-2026</t>
+          <t>A 16164-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12396,10 +12376,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46031</v>
+        <v>45027</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12411,8 +12391,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12455,7 +12440,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 30964-2023</t>
+          <t>A 39024-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12469,10 +12454,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45113</v>
+        <v>45163</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12484,8 +12469,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>0.7</v>
+        <v>4.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12528,7 +12518,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 6506-2025</t>
+          <t>A 47597-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12542,10 +12532,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45699</v>
+        <v>45203</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12558,7 +12548,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12601,7 +12591,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 21770-2023</t>
+          <t>A 39027-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12615,10 +12605,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45065</v>
+        <v>45163</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12630,8 +12620,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12674,7 +12669,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 19351-2023</t>
+          <t>A 14166-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12688,10 +12683,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45049</v>
+        <v>45009</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12704,7 +12699,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12747,7 +12742,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 12332-2023</t>
+          <t>A 15344-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12761,10 +12756,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44999</v>
+        <v>45747</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12777,7 +12772,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12820,7 +12815,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 36075-2023</t>
+          <t>A 10335-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12834,10 +12829,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45149</v>
+        <v>44623</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12850,7 +12845,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12893,7 +12888,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 38266-2022</t>
+          <t>A 35095-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12907,10 +12902,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44812</v>
+        <v>45145</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12923,7 +12918,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12966,7 +12961,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 25895-2026</t>
+          <t>A 5350-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12980,10 +12975,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46178</v>
+        <v>45692</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12996,7 +12991,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13039,7 +13034,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 15198-2022</t>
+          <t>A 20612-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13053,10 +13048,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44658</v>
+        <v>44700</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13068,8 +13063,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>2.3</v>
+        <v>8.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13112,7 +13112,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 25816-2026</t>
+          <t>A 15198-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13126,10 +13126,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46178</v>
+        <v>44658</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13185,7 +13185,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 25863-2026</t>
+          <t>A 6375-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13199,10 +13199,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46178</v>
+        <v>45699</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13258,7 +13258,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 7375-2026</t>
+          <t>A 6592-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13272,10 +13272,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46059</v>
+        <v>45700</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13331,7 +13331,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 21771-2023</t>
+          <t>A 37843-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13345,10 +13345,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45065</v>
+        <v>45160</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 25975-2026</t>
+          <t>A 6506-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13418,10 +13418,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46181</v>
+        <v>45699</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 27274-2026</t>
+          <t>A 165-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13491,10 +13491,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46184</v>
+        <v>46024</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13507,7 +13507,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13550,7 +13550,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 27292-2026</t>
+          <t>A 63074-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13564,10 +13564,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46184</v>
+        <v>46009</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13579,8 +13579,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>4.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13623,7 +13628,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 8118-2026</t>
+          <t>A 5283-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13637,10 +13642,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46062</v>
+        <v>45331</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13653,7 +13658,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>13.4</v>
+        <v>3.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13696,7 +13701,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 35079-2023</t>
+          <t>A 38723-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13710,10 +13715,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45145</v>
+        <v>45163</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13726,7 +13731,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13769,7 +13774,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 45973-2024</t>
+          <t>A 50387-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13783,10 +13788,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45580</v>
+        <v>45600</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13799,7 +13804,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.9</v>
+        <v>8.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13842,7 +13847,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 6456-2025</t>
+          <t>A 63115-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13856,10 +13861,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45699</v>
+        <v>46009</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13872,7 +13877,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13915,7 +13920,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 35229-2023</t>
+          <t>A 2512-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13929,10 +13934,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45145</v>
+        <v>45313</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13945,7 +13950,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13988,7 +13993,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 5819-2024</t>
+          <t>A 64709-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13998,14 +14003,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45335</v>
+        <v>45281</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14017,13 +14022,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14066,7 +14066,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 21855-2022</t>
+          <t>A 64710-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14080,10 +14080,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44709</v>
+        <v>45281</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14139,7 +14139,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 72603-2021</t>
+          <t>A 36730-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14153,10 +14153,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44546</v>
+        <v>45153</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14212,7 +14212,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 61880-2021</t>
+          <t>A 16168-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14226,10 +14226,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44502</v>
+        <v>45027</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14241,8 +14241,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14285,7 +14290,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 9448-2023</t>
+          <t>A 21770-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14299,10 +14304,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44981</v>
+        <v>45065</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14315,7 +14320,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14358,7 +14363,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 64709-2023</t>
+          <t>A 36099-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14372,10 +14377,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45281</v>
+        <v>45533</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14388,7 +14393,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14431,7 +14436,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 64710-2023</t>
+          <t>A 38718-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14445,10 +14450,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45281</v>
+        <v>45163</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14461,7 +14466,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.1</v>
+        <v>3.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14504,7 +14509,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 35097-2023</t>
+          <t>A 61011-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14514,14 +14519,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45145</v>
+        <v>45645</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14534,7 +14539,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14577,7 +14582,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 35411-2023</t>
+          <t>A 1337-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14591,10 +14596,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45146</v>
+        <v>46031</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14607,7 +14612,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14650,7 +14655,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 36730-2023</t>
+          <t>A 32464-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14664,10 +14669,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45153</v>
+        <v>45838</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14680,7 +14685,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14723,7 +14728,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 38212-2023</t>
+          <t>A 8067-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14737,10 +14742,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45161</v>
+        <v>45707</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14753,7 +14758,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14796,7 +14801,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 25729-2023</t>
+          <t>A 15906-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14806,14 +14811,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45084</v>
+        <v>45405</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14826,7 +14831,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14869,7 +14874,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 11699-2024</t>
+          <t>A 35097-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14883,10 +14888,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45373</v>
+        <v>45145</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14899,7 +14904,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14942,7 +14947,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 11704-2024</t>
+          <t>A 30945-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14956,10 +14961,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45373</v>
+        <v>45113</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14972,7 +14977,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15015,7 +15020,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 28908-2026</t>
+          <t>A 30964-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15029,10 +15034,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46199</v>
+        <v>45113</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15045,7 +15050,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15088,7 +15093,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 54590-2024</t>
+          <t>A 25895-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15102,10 +15107,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45617</v>
+        <v>46178</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15118,7 +15123,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15161,7 +15166,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 28704-2026</t>
+          <t>A 25863-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15175,10 +15180,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46198</v>
+        <v>46178</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15190,13 +15195,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15239,7 +15239,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 27087-2024</t>
+          <t>A 25816-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15253,10 +15253,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45471</v>
+        <v>46178</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15312,7 +15312,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 28718-2026</t>
+          <t>A 48325-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15322,14 +15322,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46198</v>
+        <v>44858</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15390,7 +15390,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 39920-2024</t>
+          <t>A 25975-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15404,10 +15404,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45553</v>
+        <v>46181</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15463,7 +15463,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 46536-2024</t>
+          <t>A 27274-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15477,10 +15477,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45582</v>
+        <v>46184</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15536,7 +15536,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 4678-2024</t>
+          <t>A 11699-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15550,10 +15550,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45328</v>
+        <v>45373</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15609,7 +15609,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 35095-2023</t>
+          <t>A 11704-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15623,10 +15623,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45145</v>
+        <v>45373</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 1749-2025</t>
+          <t>A 27292-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45671</v>
+        <v>46184</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15755,7 +15755,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 15909-2024</t>
+          <t>A 11193-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15769,10 +15769,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45405</v>
+        <v>44992</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.1</v>
+        <v>2.9</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15828,7 +15828,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 6375-2025</t>
+          <t>A 8049-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15842,10 +15842,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45699</v>
+        <v>45707</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15901,7 +15901,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 32378-2024</t>
+          <t>A 30389-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15915,10 +15915,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45512</v>
+        <v>45491</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.1</v>
+        <v>5.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 10335-2022</t>
+          <t>A 35380-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15988,10 +15988,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44623</v>
+        <v>45146</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16047,7 +16047,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 30155-2026</t>
+          <t>A 54419-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16061,10 +16061,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46206</v>
+        <v>45617</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16078,11 +16078,11 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I203" t="n">
-        <v>5.8</v>
+        <v>22.7</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16125,7 +16125,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 51180-2024</t>
+          <t>A 28718-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16139,10 +16139,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45603</v>
+        <v>46198</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16154,8 +16154,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16198,7 +16203,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 39190-2023</t>
+          <t>A 28704-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16208,14 +16213,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45166</v>
+        <v>46198</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16227,8 +16232,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16271,7 +16281,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 16168-2023</t>
+          <t>A 34961-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16285,10 +16295,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45027</v>
+        <v>44796</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16300,13 +16310,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16349,7 +16354,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 38718-2023</t>
+          <t>A 14185-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16363,10 +16368,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45163</v>
+        <v>45009</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16379,7 +16384,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16422,7 +16427,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 2512-2024</t>
+          <t>A 27087-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16436,10 +16441,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45313</v>
+        <v>45471</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16452,7 +16457,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16495,7 +16500,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 33375-2024</t>
+          <t>A 28908-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16509,10 +16514,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45519</v>
+        <v>46199</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16524,13 +16529,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16573,7 +16573,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 5513-2025</t>
+          <t>A 6368-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16587,10 +16587,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45693</v>
+        <v>45699</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16646,7 +16646,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 51178-2024</t>
+          <t>A 39190-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16656,14 +16656,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45603</v>
+        <v>45166</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16719,7 +16719,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 15813-2022</t>
+          <t>A 54590-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16729,14 +16729,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44664</v>
+        <v>45617</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16748,13 +16748,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I212" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16797,7 +16792,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 6368-2025</t>
+          <t>A 30155-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16811,10 +16806,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45699</v>
+        <v>46206</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16826,8 +16821,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>1.7</v>
+        <v>5.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16870,7 +16870,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 35380-2023</t>
+          <t>A 14993-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16884,10 +16884,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45146</v>
+        <v>45015</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 50358-2025</t>
+          <t>A 52469-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45944</v>
+        <v>45225</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17016,7 +17016,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 6592-2025</t>
+          <t>A 19350-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17030,10 +17030,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45700</v>
+        <v>45049</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17089,7 +17089,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 43263-2023</t>
+          <t>A 51041-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17099,14 +17099,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45183</v>
+        <v>45603</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17162,7 +17162,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 31447-2026</t>
+          <t>A 50358-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17176,10 +17176,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46220</v>
+        <v>45944</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17235,7 +17235,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 44069-2023</t>
+          <t>A 11972-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17249,10 +17249,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45188</v>
+        <v>44994</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17308,7 +17308,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 3198-2024</t>
+          <t>A 31447-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17322,10 +17322,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45316</v>
+        <v>46220</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17381,7 +17381,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 16270-2024</t>
+          <t>A 12332-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17395,10 +17395,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45407</v>
+        <v>44999</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17454,7 +17454,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 51041-2024</t>
+          <t>A 38266-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17468,10 +17468,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45603</v>
+        <v>44812</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17527,7 +17527,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 36824-2026</t>
+          <t>A 1323-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17541,10 +17541,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46272</v>
+        <v>44936</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17556,13 +17556,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17605,7 +17600,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 6557-2025</t>
+          <t>A 14736-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17615,14 +17610,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45699</v>
+        <v>45397</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17635,7 +17630,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17678,7 +17673,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 15344-2025</t>
+          <t>A 25729-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17692,10 +17687,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45747</v>
+        <v>45084</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17708,7 +17703,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17751,7 +17746,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 37473-2026</t>
+          <t>A 30388-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17765,10 +17760,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46275</v>
+        <v>45491</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17781,7 +17776,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17824,7 +17819,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 37482-2026</t>
+          <t>A 36824-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17838,10 +17833,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46275</v>
+        <v>46272</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17859,7 +17854,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>16.5</v>
+        <v>8</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17902,7 +17897,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 37469-2026</t>
+          <t>A 21855-2022</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17916,10 +17911,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46275</v>
+        <v>44709</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17932,7 +17927,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17975,7 +17970,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 50387-2024</t>
+          <t>A 72603-2021</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17989,10 +17984,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45600</v>
+        <v>44546</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18005,7 +18000,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>8.5</v>
+        <v>1.9</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18048,7 +18043,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 37494-2026</t>
+          <t>A 37482-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18065,7 +18060,7 @@
         <v>46275</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18077,8 +18072,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I230" t="n">
-        <v>1.3</v>
+        <v>16.5</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18121,7 +18121,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 32715-2024</t>
+          <t>A 37473-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18135,10 +18135,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45516</v>
+        <v>46275</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 38259-2023</t>
+          <t>A 37469-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18208,10 +18208,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45161</v>
+        <v>46275</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18267,7 +18267,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 37991-2026</t>
+          <t>A 14750-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18281,10 +18281,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46280</v>
+        <v>45014</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18340,7 +18340,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 21530-2025</t>
+          <t>A 47600-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18354,10 +18354,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45782</v>
+        <v>45203</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18413,7 +18413,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 21357-2025</t>
+          <t>A 37494-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18427,10 +18427,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45782</v>
+        <v>46275</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18486,7 +18486,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 3554-2025</t>
+          <t>A 37991-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18500,10 +18500,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45680</v>
+        <v>46280</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18559,7 +18559,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 50818-2023</t>
+          <t>A 21357-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18573,10 +18573,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45217</v>
+        <v>45782</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18632,7 +18632,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 21336-2025</t>
+          <t>A 21530-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18649,7 +18649,7 @@
         <v>45782</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18705,7 +18705,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 30600-2025</t>
+          <t>A 3554-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18719,10 +18719,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45831</v>
+        <v>45680</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18778,7 +18778,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 32476-2025</t>
+          <t>A 50818-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18792,10 +18792,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45838</v>
+        <v>45217</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18851,7 +18851,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 32466-2025</t>
+          <t>A 21336-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18865,10 +18865,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45838</v>
+        <v>45782</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18941,7 +18941,7 @@
         <v>45376</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44879</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>

--- a/Översikt ÖDESHÖG.xlsx
+++ b/Översikt ÖDESHÖG.xlsx
@@ -601,7 +601,7 @@
         <v>45805</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45723</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44698</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>44664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 56797-2023</t>
+          <t>A 35443-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1058,14 +1058,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45244</v>
+        <v>44798</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1118,149 +1118,149 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Axveronika
+Bivråk</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 35443-2022 artfynd.xlsx", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 35443-2022 karta.png", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 35443-2022 georefererad karta.tif", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 35443-2022 FSC-klagomål.docx", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 35443-2022 FSC-klagomål mail.docx", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 35443-2022 tillsynsbegäran.docx", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 35443-2022 tillsynsbegäran mail.docx", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/fåglar/A 35443-2022 prioriterade fågelarter.docx", "A 35443-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 56797-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45244</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Jungfrulin
 Svinrot</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 56797-2023 artfynd.xlsx", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 56797-2023 karta.png", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 56797-2023 georefererad karta.tif", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 56797-2023 FSC-klagomål.docx", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 56797-2023 FSC-klagomål mail.docx", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 56797-2023 tillsynsbegäran.docx", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 56797-2023 tillsynsbegäran mail.docx", "A 56797-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 35443-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44798</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Axveronika
-Bivråk</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 35443-2022 artfynd.xlsx", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 35443-2022 karta.png", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 35443-2022 georefererad karta.tif", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 35443-2022 FSC-klagomål.docx", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 35443-2022 FSC-klagomål mail.docx", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 35443-2022 tillsynsbegäran.docx", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 35443-2022 tillsynsbegäran mail.docx", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/fåglar/A 35443-2022 prioriterade fågelarter.docx", "A 35443-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>44538</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 58551-2023</t>
+          <t>A 15437-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45251</v>
+        <v>45747</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1503,8 +1503,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>11.9</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1516,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1528,10 +1533,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1544,467 +1549,467 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 15437-2025 artfynd.xlsx", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 15437-2025 karta.png", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 15437-2025 georefererad karta.tif", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/knärot/A 15437-2025 karta knärot.png", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 15437-2025 FSC-klagomål.docx", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 15437-2025 FSC-klagomål mail.docx", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 15437-2025 tillsynsbegäran.docx", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 15437-2025 tillsynsbegäran mail.docx", "A 15437-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 4772-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44592</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 4772-2022 artfynd.xlsx", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 4772-2022 karta.png", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 4772-2022 georefererad karta.tif", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 4772-2022 FSC-klagomål.docx", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 4772-2022 FSC-klagomål mail.docx", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 4772-2022 tillsynsbegäran.docx", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 4772-2022 tillsynsbegäran mail.docx", "A 4772-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 32776-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Smalsprötad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32776-2025 artfynd.xlsx", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32776-2025 karta.png", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32776-2025 georefererad karta.tif", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32776-2025 FSC-klagomål.docx", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32776-2025 FSC-klagomål mail.docx", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32776-2025 tillsynsbegäran.docx", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32776-2025 tillsynsbegäran mail.docx", "A 32776-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 58052-2021</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>44487</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58052-2021 artfynd.xlsx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58052-2021 karta.png", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58052-2021 georefererad karta.tif", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58052-2021 FSC-klagomål.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58052-2021 FSC-klagomål mail.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58052-2021 tillsynsbegäran.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58052-2021 tillsynsbegäran mail.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 58551-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45251</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58551-2023 artfynd.xlsx", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58551-2023 karta.png", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58551-2023 georefererad karta.tif", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58551-2023 FSC-klagomål.docx", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58551-2023 FSC-klagomål mail.docx", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58551-2023 tillsynsbegäran.docx", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58551-2023 tillsynsbegäran mail.docx", "A 58551-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 32776-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45839</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Smalsprötad bastardsvärmare</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32776-2025 artfynd.xlsx", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32776-2025 karta.png", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32776-2025 georefererad karta.tif", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32776-2025 FSC-klagomål.docx", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32776-2025 FSC-klagomål mail.docx", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32776-2025 tillsynsbegäran.docx", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32776-2025 tillsynsbegäran mail.docx", "A 32776-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 50774-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Mörk dunört</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 50774-2023 artfynd.xlsx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 50774-2023 karta.png", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 50774-2023 georefererad karta.tif", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 50774-2023 FSC-klagomål.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 50774-2023 FSC-klagomål mail.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 50774-2023 tillsynsbegäran.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 50774-2023 tillsynsbegäran mail.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 15437-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45747</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 15437-2025 artfynd.xlsx", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 15437-2025 karta.png", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 15437-2025 georefererad karta.tif", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/knärot/A 15437-2025 karta knärot.png", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 15437-2025 FSC-klagomål.docx", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 15437-2025 FSC-klagomål mail.docx", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 15437-2025 tillsynsbegäran.docx", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 15437-2025 tillsynsbegäran mail.docx", "A 15437-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 32713-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45516</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Kristinspindling</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32713-2024 artfynd.xlsx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32713-2024 karta.png", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32713-2024 georefererad karta.tif", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32713-2024 FSC-klagomål.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32713-2024 FSC-klagomål mail.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32713-2024 tillsynsbegäran.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32713-2024 tillsynsbegäran mail.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
@@ -2025,7 +2030,7 @@
         <v>45272</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2118,7 +2123,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 38720-2023</t>
+          <t>A 56637-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2128,14 +2133,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45163</v>
+        <v>45243</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2148,23 +2153,23 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
@@ -2172,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2184,261 +2189,256 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 56637-2023 artfynd.xlsx", "A 56637-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 56637-2023 karta.png", "A 56637-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 56637-2023 georefererad karta.tif", "A 56637-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 56637-2023 FSC-klagomål.docx", "A 56637-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 56637-2023 FSC-klagomål mail.docx", "A 56637-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 56637-2023 tillsynsbegäran.docx", "A 56637-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 56637-2023 tillsynsbegäran mail.docx", "A 56637-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 50774-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Mörk dunört</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 50774-2023 artfynd.xlsx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 50774-2023 karta.png", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 50774-2023 georefererad karta.tif", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 50774-2023 FSC-klagomål.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 50774-2023 FSC-klagomål mail.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 50774-2023 tillsynsbegäran.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 50774-2023 tillsynsbegäran mail.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 38720-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Hässleklocka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 38720-2023 artfynd.xlsx", "A 38720-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 38720-2023 karta.png", "A 38720-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 38720-2023 georefererad karta.tif", "A 38720-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 38720-2023 FSC-klagomål.docx", "A 38720-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 38720-2023 FSC-klagomål mail.docx", "A 38720-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 38720-2023 tillsynsbegäran.docx", "A 38720-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 38720-2023 tillsynsbegäran mail.docx", "A 38720-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 56637-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45243</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 56637-2023 artfynd.xlsx", "A 56637-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 56637-2023 karta.png", "A 56637-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 56637-2023 georefererad karta.tif", "A 56637-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 56637-2023 FSC-klagomål.docx", "A 56637-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 56637-2023 FSC-klagomål mail.docx", "A 56637-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 56637-2023 tillsynsbegäran.docx", "A 56637-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 56637-2023 tillsynsbegäran mail.docx", "A 56637-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 58052-2021</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44487</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Granbarkgnagare</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58052-2021 artfynd.xlsx", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58052-2021 karta.png", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58052-2021 georefererad karta.tif", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58052-2021 FSC-klagomål.docx", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58052-2021 FSC-klagomål mail.docx", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58052-2021 tillsynsbegäran.docx", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58052-2021 tillsynsbegäran mail.docx", "A 58052-2021")</f>
-        <v/>
-      </c>
-    </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 4772-2022</t>
+          <t>A 32713-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2452,10 +2452,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44592</v>
+        <v>45516</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.2</v>
+        <v>6.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2483,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2508,35 +2508,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Kristinspindling</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 4772-2022 artfynd.xlsx", "A 4772-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32713-2024 artfynd.xlsx", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 4772-2022 karta.png", "A 4772-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32713-2024 karta.png", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 4772-2022 georefererad karta.tif", "A 4772-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32713-2024 georefererad karta.tif", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 4772-2022 FSC-klagomål.docx", "A 4772-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32713-2024 FSC-klagomål.docx", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 4772-2022 FSC-klagomål mail.docx", "A 4772-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32713-2024 FSC-klagomål mail.docx", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 4772-2022 tillsynsbegäran.docx", "A 4772-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32713-2024 tillsynsbegäran.docx", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 4772-2022 tillsynsbegäran mail.docx", "A 4772-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32713-2024 tillsynsbegäran mail.docx", "A 32713-2024")</f>
         <v/>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
         <v>44509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44538</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>44614</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>44803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>44510</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44504</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44462</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>44517</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>44666</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>44756</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44796</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 6705-2024</t>
+          <t>A 36114-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45342</v>
+        <v>44803</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3599,13 +3599,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>8.300000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3648,7 +3643,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 15790-2025</t>
+          <t>A 47600-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3662,10 +3657,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45748</v>
+        <v>45203</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3678,7 +3673,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3721,7 +3716,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 5819-2024</t>
+          <t>A 15906-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3735,10 +3730,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45335</v>
+        <v>45405</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3750,13 +3745,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3799,7 +3789,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 35661-2024</t>
+          <t>A 54226-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3813,10 +3803,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45532</v>
+        <v>44470</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3829,7 +3819,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3872,7 +3862,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 36114-2022</t>
+          <t>A 30389-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3886,10 +3876,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44803</v>
+        <v>45491</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3902,7 +3892,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3945,7 +3935,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 3198-2024</t>
+          <t>A 48325-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3955,14 +3945,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45316</v>
+        <v>44858</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3974,8 +3964,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4018,7 +4013,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 26949-2023</t>
+          <t>A 47993-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4032,10 +4027,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45093</v>
+        <v>45589</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4048,7 +4043,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4091,7 +4086,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 22088-2023</t>
+          <t>A 64802-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4101,14 +4096,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45069</v>
+        <v>44512</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4121,7 +4116,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4164,7 +4159,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 8256-2023</t>
+          <t>A 1323-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4174,14 +4169,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44974</v>
+        <v>44936</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4237,7 +4232,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15813-2022</t>
+          <t>A 1578-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4247,14 +4242,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44664</v>
+        <v>44937</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4266,13 +4261,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4315,7 +4305,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38152-2023</t>
+          <t>A 6164-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4329,10 +4319,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45161</v>
+        <v>45337</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4345,7 +4335,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4388,7 +4378,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 44069-2023</t>
+          <t>A 32335-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4402,10 +4392,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45188</v>
+        <v>45512</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4418,7 +4408,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4461,7 +4451,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 56841-2022</t>
+          <t>A 6705-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4475,10 +4465,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44894</v>
+        <v>45342</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4490,8 +4480,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4534,7 +4529,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1578-2023</t>
+          <t>A 35661-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4548,10 +4543,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44937</v>
+        <v>45532</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4564,7 +4559,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4607,7 +4602,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11280-2025</t>
+          <t>A 56841-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4621,10 +4616,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45726</v>
+        <v>44894</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4637,7 +4632,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4680,7 +4675,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 15909-2024</t>
+          <t>A 3149-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4690,14 +4685,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45405</v>
+        <v>45316</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4710,7 +4705,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4753,7 +4748,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38259-2023</t>
+          <t>A 47597-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4767,10 +4762,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45161</v>
+        <v>45203</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4783,7 +4778,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4826,7 +4821,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 39032-2023</t>
+          <t>A 15907-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4836,14 +4831,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45163</v>
+        <v>45405</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4855,13 +4850,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4904,7 +4894,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 39920-2024</t>
+          <t>A 15915-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4914,14 +4904,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45553</v>
+        <v>45405</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4977,7 +4967,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45973-2024</t>
+          <t>A 30388-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4991,10 +4981,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45580</v>
+        <v>45491</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5050,7 +5040,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9448-2023</t>
+          <t>A 17618-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5064,10 +5054,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44981</v>
+        <v>45416</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5080,7 +5070,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5123,7 +5113,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 602-2026</t>
+          <t>A 13129-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5137,10 +5127,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46029</v>
+        <v>45002</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5153,7 +5143,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5196,7 +5186,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 54226-2021</t>
+          <t>A 5283-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5210,10 +5200,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44470</v>
+        <v>45331</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5226,7 +5216,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5269,7 +5259,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 46528-2024</t>
+          <t>A 14750-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5283,10 +5273,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45582</v>
+        <v>45014</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5299,7 +5289,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5342,7 +5332,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 1279-2026</t>
+          <t>A 8118-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5356,10 +5346,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46031</v>
+        <v>46062</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5372,7 +5362,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>13.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5415,7 +5405,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 1261-2026</t>
+          <t>A 14156-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5429,10 +5419,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46031</v>
+        <v>45009</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5445,7 +5435,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5488,7 +5478,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 1268-2026</t>
+          <t>A 46528-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5502,10 +5492,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46031</v>
+        <v>45582</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5518,7 +5508,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5561,7 +5551,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 36075-2023</t>
+          <t>A 30600-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5575,10 +5565,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45149</v>
+        <v>45831</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5591,7 +5581,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5634,7 +5624,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 1264-2026</t>
+          <t>A 8256-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5644,14 +5634,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46031</v>
+        <v>44974</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5664,7 +5654,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5707,7 +5697,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1273-2026</t>
+          <t>A 32476-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5721,10 +5711,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46031</v>
+        <v>45838</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5737,7 +5727,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5780,7 +5770,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1674-2023</t>
+          <t>A 22088-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5794,10 +5784,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44938</v>
+        <v>45069</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5810,7 +5800,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5853,7 +5843,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 35079-2023</t>
+          <t>A 32466-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5867,10 +5857,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45145</v>
+        <v>45838</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5883,7 +5873,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5926,7 +5916,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1585-2026</t>
+          <t>A 36099-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5940,10 +5930,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46034</v>
+        <v>45533</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5955,13 +5945,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6004,7 +5989,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 6421-2025</t>
+          <t>A 14736-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6014,14 +5999,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45699</v>
+        <v>45397</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6034,7 +6019,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6077,7 +6062,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6456-2025</t>
+          <t>A 20232-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6091,10 +6076,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45699</v>
+        <v>44698</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6106,8 +6091,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6150,7 +6140,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 17618-2024</t>
+          <t>A 12859-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6164,10 +6154,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45416</v>
+        <v>46092</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6180,7 +6170,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6223,7 +6213,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 47993-2024</t>
+          <t>A 12872-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6237,10 +6227,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45589</v>
+        <v>46092</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6253,7 +6243,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6296,7 +6286,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 41730-2025</t>
+          <t>A 14185-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6310,10 +6300,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45902</v>
+        <v>45009</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6326,7 +6316,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6369,7 +6359,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 30600-2025</t>
+          <t>A 14617-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6383,10 +6373,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45831</v>
+        <v>46101</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6399,7 +6389,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6442,7 +6432,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 1589-2026</t>
+          <t>A 14166-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6456,10 +6446,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46034</v>
+        <v>45009</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6471,13 +6461,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6520,7 +6505,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 5513-2025</t>
+          <t>A 19350-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6534,10 +6519,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45693</v>
+        <v>45049</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6550,7 +6535,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6593,7 +6578,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 6164-2024</t>
+          <t>A 16341-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6607,10 +6592,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45337</v>
+        <v>46111</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6622,8 +6607,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6666,7 +6656,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 14156-2023</t>
+          <t>A 16402-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6680,10 +6670,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45009</v>
+        <v>46111</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6695,8 +6685,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6739,7 +6734,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13129-2023</t>
+          <t>A 16414-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6753,10 +6748,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45002</v>
+        <v>46111</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6768,8 +6763,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6812,7 +6812,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 32466-2025</t>
+          <t>A 11972-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6826,10 +6826,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45838</v>
+        <v>44994</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6885,7 +6885,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 32476-2025</t>
+          <t>A 16370-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45838</v>
+        <v>46111</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6914,8 +6914,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>6.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6958,7 +6963,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 35411-2023</t>
+          <t>A 54419-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6972,10 +6977,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45146</v>
+        <v>45617</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6987,8 +6992,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>22.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7031,7 +7041,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 16270-2024</t>
+          <t>A 16259-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7045,10 +7055,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45407</v>
+        <v>46109</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7061,7 +7071,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7104,7 +7114,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 46059-2025</t>
+          <t>A 16262-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7118,10 +7128,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45924</v>
+        <v>46109</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7134,7 +7144,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7177,7 +7187,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 46778-2025</t>
+          <t>A 41730-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7191,10 +7201,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45926</v>
+        <v>45902</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7207,7 +7217,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7250,7 +7260,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 46999-2025</t>
+          <t>A 39024-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7264,10 +7274,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45929</v>
+        <v>45163</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7279,8 +7289,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7323,7 +7338,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 46788-2025</t>
+          <t>A 17950-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7337,10 +7352,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45926</v>
+        <v>46122</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7353,7 +7368,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7396,7 +7411,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 47648-2025</t>
+          <t>A 39032-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7410,10 +7425,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45931</v>
+        <v>45163</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7425,8 +7440,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7469,7 +7489,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 20244-2022</t>
+          <t>A 14993-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7483,10 +7503,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44698</v>
+        <v>45015</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7498,13 +7518,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>9.5</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7547,7 +7562,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 6557-2025</t>
+          <t>A 11280-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7561,10 +7576,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45699</v>
+        <v>45726</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7577,7 +7592,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7620,7 +7635,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 32378-2024</t>
+          <t>A 8049-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7634,10 +7649,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45512</v>
+        <v>45707</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7650,7 +7665,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7693,7 +7708,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 48063-2025</t>
+          <t>A 39027-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7707,10 +7722,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45932</v>
+        <v>45163</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7722,8 +7737,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7766,7 +7786,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 48611-2025</t>
+          <t>A 38152-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7780,10 +7800,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45936</v>
+        <v>45161</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7796,7 +7816,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7839,7 +7859,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 48614-2025</t>
+          <t>A 8515-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7853,10 +7873,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45936</v>
+        <v>44613</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7869,7 +7889,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7912,7 +7932,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 48575-2025</t>
+          <t>A 38723-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7926,10 +7946,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45936</v>
+        <v>45163</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7942,7 +7962,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7985,7 +8005,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 50416-2025</t>
+          <t>A 3130-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7999,10 +8019,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45944</v>
+        <v>45678</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8014,8 +8034,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>3.4</v>
+        <v>18.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8058,7 +8083,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 19351-2023</t>
+          <t>A 16128-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8072,10 +8097,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45049</v>
+        <v>45750</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8087,8 +8112,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8131,7 +8161,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 51171-2025</t>
+          <t>A 55971-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8145,10 +8175,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45947</v>
+        <v>45240</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8161,7 +8191,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8204,7 +8234,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 51328-2025</t>
+          <t>A 30945-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8218,10 +8248,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45950</v>
+        <v>45113</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8234,7 +8264,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8277,7 +8307,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 32335-2024</t>
+          <t>A 16164-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8291,10 +8321,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45512</v>
+        <v>45027</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8306,8 +8336,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8350,7 +8385,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 8515-2022</t>
+          <t>A 46059-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8364,10 +8399,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44613</v>
+        <v>45924</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8380,7 +8415,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8423,7 +8458,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 61880-2021</t>
+          <t>A 63074-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8437,10 +8472,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44502</v>
+        <v>46009</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8452,8 +8487,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8496,7 +8536,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 7375-2026</t>
+          <t>A 165-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8510,10 +8550,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46059</v>
+        <v>46024</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8526,7 +8566,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8569,7 +8609,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 39024-2023</t>
+          <t>A 5350-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8583,10 +8623,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45163</v>
+        <v>45692</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8598,13 +8638,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8647,7 +8682,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 8118-2026</t>
+          <t>A 30964-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8661,10 +8696,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46062</v>
+        <v>45113</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8677,7 +8712,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>13.4</v>
+        <v>0.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8720,7 +8755,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 33375-2024</t>
+          <t>A 46788-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8734,10 +8769,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45519</v>
+        <v>45926</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8749,13 +8784,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8798,7 +8828,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 20720-2025</t>
+          <t>A 46778-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8812,10 +8842,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45776</v>
+        <v>45926</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8828,7 +8858,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8871,7 +8901,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 55901-2025</t>
+          <t>A 21770-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8885,10 +8915,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45973</v>
+        <v>45065</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8901,7 +8931,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8944,7 +8974,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 55906-2025</t>
+          <t>A 19351-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8958,10 +8988,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45973</v>
+        <v>45049</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8974,7 +9004,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.7</v>
+        <v>5.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9017,7 +9047,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 43263-2023</t>
+          <t>A 46999-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9027,14 +9057,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45183</v>
+        <v>45929</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9047,7 +9077,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9090,7 +9120,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 55908-2025</t>
+          <t>A 38266-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9104,10 +9134,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45973</v>
+        <v>44812</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9120,7 +9150,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9163,7 +9193,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 46536-2024</t>
+          <t>A 48063-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9177,10 +9207,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45582</v>
+        <v>45932</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9193,7 +9223,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.3</v>
+        <v>5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9236,7 +9266,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 38212-2023</t>
+          <t>A 47648-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9250,10 +9280,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45161</v>
+        <v>45931</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9266,7 +9296,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9309,7 +9339,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 3130-2025</t>
+          <t>A 48575-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9323,10 +9353,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45678</v>
+        <v>45936</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9338,13 +9368,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>18.6</v>
+        <v>4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9387,7 +9412,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 15907-2024</t>
+          <t>A 21771-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9397,14 +9422,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45405</v>
+        <v>45065</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9417,7 +9442,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9460,7 +9485,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 15915-2024</t>
+          <t>A 48611-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9470,14 +9495,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45405</v>
+        <v>45936</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9533,7 +9558,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 20232-2022</t>
+          <t>A 48614-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9547,10 +9572,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44698</v>
+        <v>45936</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9562,13 +9587,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9611,7 +9631,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 61786-2025</t>
+          <t>A 63115-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9625,10 +9645,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46002</v>
+        <v>46009</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9641,7 +9661,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9684,7 +9704,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 8063-2025</t>
+          <t>A 35079-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9698,10 +9718,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45707</v>
+        <v>45145</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9714,7 +9734,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9757,7 +9777,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 61798-2025</t>
+          <t>A 45973-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9771,10 +9791,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46002</v>
+        <v>45580</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9786,13 +9806,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9835,7 +9850,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 61800-2025</t>
+          <t>A 61011-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9845,14 +9860,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46002</v>
+        <v>45645</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9865,7 +9880,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9908,7 +9923,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 61801-2025</t>
+          <t>A 50416-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9922,10 +9937,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46002</v>
+        <v>45944</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9938,7 +9953,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9981,7 +9996,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 61972-2025</t>
+          <t>A 1337-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9995,10 +10010,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46003</v>
+        <v>46031</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10010,13 +10025,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10059,7 +10069,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 61470-2025</t>
+          <t>A 8067-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10073,10 +10083,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46001</v>
+        <v>45707</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10088,13 +10098,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>8</v>
+        <v>0.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10137,7 +10142,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 61629-2025</t>
+          <t>A 35229-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10151,10 +10156,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46002</v>
+        <v>45145</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10167,7 +10172,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10210,7 +10215,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 32715-2024</t>
+          <t>A 5819-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10220,14 +10225,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45516</v>
+        <v>45335</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10239,8 +10244,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10283,7 +10293,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 12872-2026</t>
+          <t>A 32464-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10297,10 +10307,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46092</v>
+        <v>45838</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10313,7 +10323,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10356,7 +10366,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 6465-2025</t>
+          <t>A 61880-2021</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10370,10 +10380,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45699</v>
+        <v>44502</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10386,7 +10396,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10429,7 +10439,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 1749-2025</t>
+          <t>A 38212-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10443,10 +10453,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45671</v>
+        <v>45161</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10459,7 +10469,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10502,7 +10512,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 62482-2025</t>
+          <t>A 27087-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10516,10 +10526,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46007</v>
+        <v>45471</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10532,7 +10542,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>6.7</v>
+        <v>2.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10575,7 +10585,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 62202-2025</t>
+          <t>A 39920-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10589,10 +10599,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46006</v>
+        <v>45553</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10605,7 +10615,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>5.1</v>
+        <v>0.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10648,7 +10658,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 62801-2025</t>
+          <t>A 46536-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10662,10 +10672,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46008</v>
+        <v>45582</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10678,7 +10688,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10721,7 +10731,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 12859-2026</t>
+          <t>A 51171-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10735,10 +10745,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46092</v>
+        <v>45947</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10751,7 +10761,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10794,7 +10804,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 64010-2025</t>
+          <t>A 51328-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10808,10 +10818,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46021</v>
+        <v>45950</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10823,13 +10833,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>15.4</v>
+        <v>6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10872,7 +10877,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 64015-2025</t>
+          <t>A 4678-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10886,10 +10891,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46021</v>
+        <v>45328</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10901,13 +10906,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10950,7 +10950,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 17126-2024</t>
+          <t>A 25895-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10964,10 +10964,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45412</v>
+        <v>46178</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11023,7 +11023,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 14617-2026</t>
+          <t>A 35095-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11037,10 +11037,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46101</v>
+        <v>45145</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11096,7 +11096,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 4678-2024</t>
+          <t>A 1749-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11110,10 +11110,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45328</v>
+        <v>45671</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11169,7 +11169,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 21771-2023</t>
+          <t>A 25816-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11183,10 +11183,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45065</v>
+        <v>46178</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11242,7 +11242,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 16370-2026</t>
+          <t>A 25863-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11256,10 +11256,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46111</v>
+        <v>46178</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11271,13 +11271,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>6.9</v>
+        <v>0.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11320,7 +11315,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 64802-2021</t>
+          <t>A 15909-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11334,10 +11329,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44512</v>
+        <v>45405</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11350,7 +11345,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.5</v>
+        <v>0.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11393,7 +11388,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 16414-2026</t>
+          <t>A 25975-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11407,10 +11402,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46111</v>
+        <v>46181</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11422,13 +11417,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>8.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11471,7 +11461,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 16402-2026</t>
+          <t>A 6375-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11485,10 +11475,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46111</v>
+        <v>45699</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11500,13 +11490,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11549,7 +11534,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 16341-2026</t>
+          <t>A 27274-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11563,10 +11548,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46111</v>
+        <v>46184</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11578,13 +11563,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11627,7 +11607,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 16128-2025</t>
+          <t>A 27292-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11641,10 +11621,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45750</v>
+        <v>46184</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11656,13 +11636,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11705,7 +11680,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 3149-2024</t>
+          <t>A 32378-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11719,10 +11694,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45316</v>
+        <v>45512</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11735,7 +11710,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11778,7 +11753,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 16259-2026</t>
+          <t>A 51180-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11792,10 +11767,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46109</v>
+        <v>45603</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11808,7 +11783,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11851,7 +11826,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 16262-2026</t>
+          <t>A 20720-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11865,10 +11840,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46109</v>
+        <v>45776</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11881,7 +11856,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11924,7 +11899,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 17950-2026</t>
+          <t>A 39190-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11934,14 +11909,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46122</v>
+        <v>45166</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11954,7 +11929,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11997,7 +11972,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 51180-2024</t>
+          <t>A 28908-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12011,10 +11986,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45603</v>
+        <v>46199</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12027,7 +12002,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12070,7 +12045,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 35229-2023</t>
+          <t>A 16168-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12084,10 +12059,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45145</v>
+        <v>45027</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12099,8 +12074,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12143,7 +12123,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 51178-2024</t>
+          <t>A 38718-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12157,10 +12137,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45603</v>
+        <v>45163</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12173,7 +12153,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12216,7 +12196,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 19157-2023</t>
+          <t>A 28704-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12230,10 +12210,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45048</v>
+        <v>46198</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12245,8 +12225,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12289,7 +12274,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 55971-2023</t>
+          <t>A 55908-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12303,10 +12288,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45240</v>
+        <v>45973</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12319,7 +12304,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12362,7 +12347,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 16164-2023</t>
+          <t>A 55901-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12376,10 +12361,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45027</v>
+        <v>45973</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12391,13 +12376,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12440,7 +12420,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 39024-2023</t>
+          <t>A 2512-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12454,10 +12434,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45163</v>
+        <v>45313</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12469,13 +12449,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12518,7 +12493,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 47597-2023</t>
+          <t>A 55906-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12532,10 +12507,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45203</v>
+        <v>45973</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12548,7 +12523,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12591,7 +12566,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 39027-2023</t>
+          <t>A 28718-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12605,10 +12580,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45163</v>
+        <v>46198</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12626,7 +12601,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12669,7 +12644,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 14166-2023</t>
+          <t>A 51178-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12683,10 +12658,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45009</v>
+        <v>45603</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12699,7 +12674,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12742,7 +12717,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 15344-2025</t>
+          <t>A 35380-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12756,10 +12731,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45747</v>
+        <v>45146</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12772,7 +12747,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12815,7 +12790,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 10335-2022</t>
+          <t>A 30155-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12829,10 +12804,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44623</v>
+        <v>46206</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12844,8 +12819,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12888,7 +12868,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 35095-2023</t>
+          <t>A 6592-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12902,10 +12882,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45145</v>
+        <v>45700</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12918,7 +12898,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12961,7 +12941,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 5350-2025</t>
+          <t>A 43263-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12971,14 +12951,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45692</v>
+        <v>45183</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12991,7 +12971,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13034,7 +13014,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 20612-2022</t>
+          <t>A 20244-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13048,10 +13028,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44700</v>
+        <v>44698</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13069,7 +13049,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13112,7 +13092,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 15198-2022</t>
+          <t>A 20612-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13126,10 +13106,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44658</v>
+        <v>44700</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13141,8 +13121,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>2.3</v>
+        <v>8.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13185,7 +13170,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 6375-2025</t>
+          <t>A 6421-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13202,7 +13187,7 @@
         <v>45699</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13215,7 +13200,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13258,7 +13243,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 6592-2025</t>
+          <t>A 52469-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13272,10 +13257,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45700</v>
+        <v>45225</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13288,7 +13273,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13331,7 +13316,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 37843-2023</t>
+          <t>A 8063-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13345,10 +13330,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45160</v>
+        <v>45707</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13361,7 +13346,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13404,7 +13389,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 6506-2025</t>
+          <t>A 15790-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13418,10 +13403,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45699</v>
+        <v>45748</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13434,7 +13419,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13477,7 +13462,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 165-2026</t>
+          <t>A 37843-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13491,10 +13476,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46024</v>
+        <v>45160</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13507,7 +13492,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13550,7 +13535,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 63074-2025</t>
+          <t>A 6465-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13564,10 +13549,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46009</v>
+        <v>45699</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13579,13 +13564,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>8.699999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13628,7 +13608,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 5283-2024</t>
+          <t>A 50358-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13642,10 +13622,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45331</v>
+        <v>45944</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13658,7 +13638,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13701,7 +13681,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 38723-2023</t>
+          <t>A 1674-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13715,10 +13695,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45163</v>
+        <v>44938</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13731,7 +13711,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13774,7 +13754,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 50387-2024</t>
+          <t>A 34961-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13788,10 +13768,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45600</v>
+        <v>44796</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13804,7 +13784,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13847,7 +13827,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 63115-2025</t>
+          <t>A 61801-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13861,10 +13841,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13877,7 +13857,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13920,7 +13900,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 2512-2024</t>
+          <t>A 61470-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13934,10 +13914,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45313</v>
+        <v>46001</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13949,8 +13929,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13993,7 +13978,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 64709-2023</t>
+          <t>A 31447-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14007,10 +13992,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45281</v>
+        <v>46220</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14023,7 +14008,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14066,7 +14051,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 64710-2023</t>
+          <t>A 61798-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14080,10 +14065,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45281</v>
+        <v>46002</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14095,8 +14080,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14139,7 +14129,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 36730-2023</t>
+          <t>A 61800-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14153,10 +14143,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45153</v>
+        <v>46002</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14169,7 +14159,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14212,7 +14202,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 16168-2023</t>
+          <t>A 61629-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14226,10 +14216,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45027</v>
+        <v>46002</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14241,13 +14231,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14290,7 +14275,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 21770-2023</t>
+          <t>A 19157-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14304,10 +14289,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45065</v>
+        <v>45048</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14320,7 +14305,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14363,7 +14348,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 36099-2024</t>
+          <t>A 61786-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14377,10 +14362,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45533</v>
+        <v>46002</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14393,7 +14378,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14436,7 +14421,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 38718-2023</t>
+          <t>A 62202-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14450,10 +14435,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45163</v>
+        <v>46006</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14466,7 +14451,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14509,7 +14494,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 61011-2024</t>
+          <t>A 61972-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14519,14 +14504,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45645</v>
+        <v>46003</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14538,8 +14523,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14582,7 +14572,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 1337-2026</t>
+          <t>A 62801-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14596,10 +14586,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46031</v>
+        <v>46008</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14612,7 +14602,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14655,7 +14645,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 32464-2025</t>
+          <t>A 62482-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14669,10 +14659,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45838</v>
+        <v>46007</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14685,7 +14675,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.4</v>
+        <v>6.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14728,7 +14718,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 8067-2025</t>
+          <t>A 39024-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14742,10 +14732,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45707</v>
+        <v>45163</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14757,8 +14747,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14801,7 +14796,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 15906-2024</t>
+          <t>A 36824-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14811,14 +14806,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45405</v>
+        <v>46272</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14830,8 +14825,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>0.2</v>
+        <v>8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14874,7 +14874,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 35097-2023</t>
+          <t>A 17126-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14888,10 +14888,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45145</v>
+        <v>45412</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14947,7 +14947,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 30945-2023</t>
+          <t>A 37473-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14961,10 +14961,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45113</v>
+        <v>46275</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15020,7 +15020,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 30964-2023</t>
+          <t>A 37482-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15034,10 +15034,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45113</v>
+        <v>46275</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15049,8 +15049,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>0.7</v>
+        <v>16.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15093,7 +15098,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 25895-2026</t>
+          <t>A 37469-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15107,10 +15112,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46178</v>
+        <v>46275</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15123,7 +15128,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15166,7 +15171,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 25863-2026</t>
+          <t>A 64015-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15180,10 +15185,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46178</v>
+        <v>46021</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15195,8 +15200,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15239,7 +15249,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 25816-2026</t>
+          <t>A 64010-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15253,10 +15263,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46178</v>
+        <v>46021</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15268,8 +15278,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>1.3</v>
+        <v>15.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15312,7 +15327,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 48325-2022</t>
+          <t>A 37991-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15322,14 +15337,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44858</v>
+        <v>46280</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15341,13 +15356,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>1.8</v>
+        <v>4.9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15390,7 +15400,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 25975-2026</t>
+          <t>A 11193-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15400,14 +15410,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46181</v>
+        <v>44992</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15420,7 +15430,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15463,7 +15473,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 27274-2026</t>
+          <t>A 602-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15477,10 +15487,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46184</v>
+        <v>46029</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15493,7 +15503,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15536,7 +15546,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 11699-2024</t>
+          <t>A 1589-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15550,10 +15560,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45373</v>
+        <v>46034</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15565,8 +15575,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15609,7 +15624,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 11704-2024</t>
+          <t>A 1279-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15623,10 +15638,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45373</v>
+        <v>46031</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15639,7 +15654,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15682,7 +15697,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 27292-2026</t>
+          <t>A 1264-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15696,10 +15711,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46184</v>
+        <v>46031</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15712,7 +15727,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15755,7 +15770,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 11193-2023</t>
+          <t>A 26949-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15765,14 +15780,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44992</v>
+        <v>45093</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15785,7 +15800,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15828,7 +15843,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 8049-2025</t>
+          <t>A 1585-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15842,10 +15857,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45707</v>
+        <v>46034</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15857,8 +15872,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15901,7 +15921,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 30389-2024</t>
+          <t>A 37494-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15915,10 +15935,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45491</v>
+        <v>46275</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15931,7 +15951,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15974,7 +15994,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 35380-2023</t>
+          <t>A 1273-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15988,10 +16008,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45146</v>
+        <v>46031</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16004,7 +16024,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16047,7 +16067,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 54419-2024</t>
+          <t>A 1261-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16061,10 +16081,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45617</v>
+        <v>46031</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16076,13 +16096,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>22.7</v>
+        <v>1.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16125,7 +16140,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 28718-2026</t>
+          <t>A 1268-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16139,10 +16154,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46198</v>
+        <v>46031</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16154,13 +16169,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16203,7 +16213,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 28704-2026</t>
+          <t>A 6506-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16217,10 +16227,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46198</v>
+        <v>45699</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16232,13 +16242,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16281,7 +16286,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 34961-2022</t>
+          <t>A 12332-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16295,10 +16300,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44796</v>
+        <v>44999</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16311,7 +16316,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16354,7 +16359,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 14185-2023</t>
+          <t>A 36075-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16368,10 +16373,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45009</v>
+        <v>45149</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16384,7 +16389,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16427,7 +16432,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 27087-2024</t>
+          <t>A 15198-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16441,10 +16446,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45471</v>
+        <v>44658</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16457,7 +16462,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16500,7 +16505,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 28908-2026</t>
+          <t>A 6456-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16514,10 +16519,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46199</v>
+        <v>45699</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16530,7 +16535,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16573,7 +16578,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 6368-2025</t>
+          <t>A 21855-2022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16587,10 +16592,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45699</v>
+        <v>44709</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16603,7 +16608,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16646,7 +16651,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 39190-2023</t>
+          <t>A 72603-2021</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16656,14 +16661,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45166</v>
+        <v>44546</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16676,7 +16681,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16719,7 +16724,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 54590-2024</t>
+          <t>A 9448-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16733,10 +16738,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45617</v>
+        <v>44981</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16792,7 +16797,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 30155-2026</t>
+          <t>A 64709-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16806,10 +16811,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46206</v>
+        <v>45281</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16821,13 +16826,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16870,7 +16870,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 14993-2023</t>
+          <t>A 64710-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16884,10 +16884,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45015</v>
+        <v>45281</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 52469-2023</t>
+          <t>A 35097-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45225</v>
+        <v>45145</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17016,7 +17016,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 19350-2023</t>
+          <t>A 35411-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17030,10 +17030,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45049</v>
+        <v>45146</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17089,7 +17089,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 51041-2024</t>
+          <t>A 36730-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17103,10 +17103,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45603</v>
+        <v>45153</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17162,7 +17162,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 50358-2025</t>
+          <t>A 7375-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17176,10 +17176,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45944</v>
+        <v>46059</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17235,7 +17235,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 11972-2023</t>
+          <t>A 25729-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17249,10 +17249,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44994</v>
+        <v>45084</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17308,7 +17308,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 31447-2026</t>
+          <t>A 11699-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17322,10 +17322,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46220</v>
+        <v>45373</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17381,7 +17381,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 12332-2023</t>
+          <t>A 11704-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17395,10 +17395,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44999</v>
+        <v>45373</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17454,7 +17454,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 38266-2022</t>
+          <t>A 54590-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17468,10 +17468,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44812</v>
+        <v>45617</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17527,7 +17527,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 1323-2023</t>
+          <t>A 10335-2022</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17541,10 +17541,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>44936</v>
+        <v>44623</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17600,7 +17600,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 14736-2024</t>
+          <t>A 33375-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17610,14 +17610,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45397</v>
+        <v>45519</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17629,8 +17629,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17673,7 +17678,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 25729-2023</t>
+          <t>A 5513-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17687,10 +17692,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45084</v>
+        <v>45693</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17703,7 +17708,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17746,7 +17751,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 30388-2024</t>
+          <t>A 15813-2022</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17756,14 +17761,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45491</v>
+        <v>44664</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17775,8 +17780,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17819,7 +17829,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 36824-2026</t>
+          <t>A 6368-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17833,10 +17843,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46272</v>
+        <v>45699</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17848,13 +17858,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I227" t="n">
-        <v>8</v>
+        <v>1.7</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17897,7 +17902,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 21855-2022</t>
+          <t>A 44069-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17911,10 +17916,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44709</v>
+        <v>45188</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17927,7 +17932,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17970,7 +17975,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 72603-2021</t>
+          <t>A 3198-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17984,10 +17989,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44546</v>
+        <v>45316</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18000,7 +18005,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18043,7 +18048,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 37482-2026</t>
+          <t>A 16270-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18057,10 +18062,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46275</v>
+        <v>45407</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18072,13 +18077,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I230" t="n">
-        <v>16.5</v>
+        <v>0.7</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18121,7 +18121,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 37473-2026</t>
+          <t>A 51041-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18135,10 +18135,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46275</v>
+        <v>45603</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 37469-2026</t>
+          <t>A 6557-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18208,10 +18208,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46275</v>
+        <v>45699</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18267,7 +18267,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 14750-2023</t>
+          <t>A 15344-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18281,10 +18281,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45014</v>
+        <v>45747</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18340,7 +18340,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 47600-2023</t>
+          <t>A 50387-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18354,10 +18354,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45203</v>
+        <v>45600</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.6</v>
+        <v>8.5</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18413,7 +18413,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 37494-2026</t>
+          <t>A 32715-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18427,10 +18427,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46275</v>
+        <v>45516</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18486,7 +18486,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 37991-2026</t>
+          <t>A 38259-2023</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18500,10 +18500,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46280</v>
+        <v>45161</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18559,7 +18559,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 21357-2025</t>
+          <t>A 21530-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18576,7 +18576,7 @@
         <v>45782</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18632,7 +18632,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 21530-2025</t>
+          <t>A 21357-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18649,7 +18649,7 @@
         <v>45782</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18722,7 +18722,7 @@
         <v>45680</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>45217</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>45782</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>45376</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44879</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>

--- a/Översikt ÖDESHÖG.xlsx
+++ b/Översikt ÖDESHÖG.xlsx
@@ -601,7 +601,7 @@
         <v>45805</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45723</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44698</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>44664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 35443-2022</t>
+          <t>A 56797-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1058,14 +1058,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44798</v>
+        <v>45244</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1118,149 +1118,149 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Jungfrulin
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 56797-2023 artfynd.xlsx", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 56797-2023 karta.png", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 56797-2023 georefererad karta.tif", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 56797-2023 FSC-klagomål.docx", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 56797-2023 FSC-klagomål mail.docx", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 56797-2023 tillsynsbegäran.docx", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 56797-2023 tillsynsbegäran mail.docx", "A 56797-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 35443-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44798</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Axveronika
 Bivråk</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 35443-2022 artfynd.xlsx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 35443-2022 karta.png", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 35443-2022 georefererad karta.tif", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 35443-2022 FSC-klagomål.docx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 35443-2022 FSC-klagomål mail.docx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 35443-2022 tillsynsbegäran.docx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 35443-2022 tillsynsbegäran mail.docx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/fåglar/A 35443-2022 prioriterade fågelarter.docx", "A 35443-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 56797-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45244</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 56797-2023 artfynd.xlsx", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 56797-2023 karta.png", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 56797-2023 georefererad karta.tif", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 56797-2023 FSC-klagomål.docx", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 56797-2023 FSC-klagomål mail.docx", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 56797-2023 tillsynsbegäran.docx", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 56797-2023 tillsynsbegäran mail.docx", "A 56797-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>44538</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 15437-2025</t>
+          <t>A 58551-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45747</v>
+        <v>45251</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1503,13 +1503,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>11.9</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1521,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1533,10 +1528,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1549,256 +1544,261 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58551-2023 artfynd.xlsx", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58551-2023 karta.png", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58551-2023 georefererad karta.tif", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58551-2023 FSC-klagomål.docx", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58551-2023 FSC-klagomål mail.docx", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58551-2023 tillsynsbegäran.docx", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58551-2023 tillsynsbegäran mail.docx", "A 58551-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 50774-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Mörk dunört</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 50774-2023 artfynd.xlsx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 50774-2023 karta.png", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 50774-2023 georefererad karta.tif", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 50774-2023 FSC-klagomål.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 50774-2023 FSC-klagomål mail.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 50774-2023 tillsynsbegäran.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 50774-2023 tillsynsbegäran mail.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 15437-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>Knärot</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 15437-2025 artfynd.xlsx", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 15437-2025 karta.png", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 15437-2025 georefererad karta.tif", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="Z10">
+      <c r="Z12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/knärot/A 15437-2025 karta knärot.png", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 15437-2025 FSC-klagomål.docx", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 15437-2025 FSC-klagomål mail.docx", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 15437-2025 tillsynsbegäran.docx", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 15437-2025 tillsynsbegäran mail.docx", "A 15437-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 4772-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44592</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 4772-2022 artfynd.xlsx", "A 4772-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 4772-2022 karta.png", "A 4772-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 4772-2022 georefererad karta.tif", "A 4772-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 4772-2022 FSC-klagomål.docx", "A 4772-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 4772-2022 FSC-klagomål mail.docx", "A 4772-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 4772-2022 tillsynsbegäran.docx", "A 4772-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 4772-2022 tillsynsbegäran mail.docx", "A 4772-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 32776-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45839</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Smalsprötad bastardsvärmare</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32776-2025 artfynd.xlsx", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32776-2025 karta.png", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32776-2025 georefererad karta.tif", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32776-2025 FSC-klagomål.docx", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32776-2025 FSC-klagomål mail.docx", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32776-2025 tillsynsbegäran.docx", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32776-2025 tillsynsbegäran mail.docx", "A 32776-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 58052-2021</t>
+          <t>A 32713-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44487</v>
+        <v>45516</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1827,37 +1827,32 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>4.3</v>
+        <v>6.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1869,46 +1864,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kristinspindling</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58052-2021 artfynd.xlsx", "A 58052-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32713-2024 artfynd.xlsx", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58052-2021 karta.png", "A 58052-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32713-2024 karta.png", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58052-2021 georefererad karta.tif", "A 58052-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32713-2024 georefererad karta.tif", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58052-2021 FSC-klagomål.docx", "A 58052-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32713-2024 FSC-klagomål.docx", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58052-2021 FSC-klagomål mail.docx", "A 58052-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32713-2024 FSC-klagomål mail.docx", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58052-2021 tillsynsbegäran.docx", "A 58052-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32713-2024 tillsynsbegäran.docx", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58052-2021 tillsynsbegäran mail.docx", "A 58052-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32713-2024 tillsynsbegäran mail.docx", "A 32713-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 58551-2023</t>
+          <t>A 62988-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1918,14 +1913,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45251</v>
+        <v>45272</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1937,24 +1932,29 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>19</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
@@ -1962,10 +1962,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1978,42 +1978,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58551-2023 artfynd.xlsx", "A 58551-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 62988-2023 artfynd.xlsx", "A 62988-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58551-2023 karta.png", "A 58551-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 62988-2023 karta.png", "A 62988-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58551-2023 georefererad karta.tif", "A 58551-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 62988-2023 georefererad karta.tif", "A 62988-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58551-2023 FSC-klagomål.docx", "A 58551-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 62988-2023 FSC-klagomål.docx", "A 62988-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58551-2023 FSC-klagomål mail.docx", "A 58551-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 62988-2023 FSC-klagomål mail.docx", "A 62988-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58551-2023 tillsynsbegäran.docx", "A 58551-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 62988-2023 tillsynsbegäran.docx", "A 62988-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58551-2023 tillsynsbegäran mail.docx", "A 58551-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 62988-2023 tillsynsbegäran mail.docx", "A 62988-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 62988-2023</t>
+          <t>A 38720-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45272</v>
+        <v>45163</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2042,19 +2042,14 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2063,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2072,10 +2067,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2084,39 +2079,39 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Hässleklocka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 62988-2023 artfynd.xlsx", "A 62988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 38720-2023 artfynd.xlsx", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 62988-2023 karta.png", "A 62988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 38720-2023 karta.png", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 62988-2023 georefererad karta.tif", "A 62988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 38720-2023 georefererad karta.tif", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 62988-2023 FSC-klagomål.docx", "A 62988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 38720-2023 FSC-klagomål.docx", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 62988-2023 FSC-klagomål mail.docx", "A 62988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 38720-2023 FSC-klagomål mail.docx", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 62988-2023 tillsynsbegäran.docx", "A 62988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 38720-2023 tillsynsbegäran.docx", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 62988-2023 tillsynsbegäran mail.docx", "A 62988-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 38720-2023 tillsynsbegäran mail.docx", "A 38720-2023")</f>
         <v/>
       </c>
     </row>
@@ -2140,7 +2135,7 @@
         <v>45243</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2228,7 +2223,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 50774-2023</t>
+          <t>A 58052-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2242,10 +2237,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45210</v>
+        <v>44487</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2257,17 +2252,22 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>9.5</v>
+        <v>4.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2298,42 +2298,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Mörk dunört</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 50774-2023 artfynd.xlsx", "A 50774-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58052-2021 artfynd.xlsx", "A 58052-2021")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 50774-2023 karta.png", "A 50774-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58052-2021 karta.png", "A 58052-2021")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 50774-2023 georefererad karta.tif", "A 50774-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58052-2021 georefererad karta.tif", "A 58052-2021")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 50774-2023 FSC-klagomål.docx", "A 50774-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58052-2021 FSC-klagomål.docx", "A 58052-2021")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 50774-2023 FSC-klagomål mail.docx", "A 50774-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58052-2021 FSC-klagomål mail.docx", "A 58052-2021")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 50774-2023 tillsynsbegäran.docx", "A 50774-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58052-2021 tillsynsbegäran.docx", "A 58052-2021")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 50774-2023 tillsynsbegäran mail.docx", "A 50774-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58052-2021 tillsynsbegäran mail.docx", "A 58052-2021")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 38720-2023</t>
+          <t>A 4772-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45163</v>
+        <v>44592</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2363,23 +2363,23 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
@@ -2387,10 +2387,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2399,46 +2399,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Hässleklocka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 38720-2023 artfynd.xlsx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 4772-2022 artfynd.xlsx", "A 4772-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 38720-2023 karta.png", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 4772-2022 karta.png", "A 4772-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 38720-2023 georefererad karta.tif", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 4772-2022 georefererad karta.tif", "A 4772-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 38720-2023 FSC-klagomål.docx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 4772-2022 FSC-klagomål.docx", "A 4772-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 38720-2023 FSC-klagomål mail.docx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 4772-2022 FSC-klagomål mail.docx", "A 4772-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 38720-2023 tillsynsbegäran.docx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 4772-2022 tillsynsbegäran.docx", "A 4772-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 38720-2023 tillsynsbegäran mail.docx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 4772-2022 tillsynsbegäran mail.docx", "A 4772-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32713-2024</t>
+          <t>A 32776-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2448,14 +2448,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45516</v>
+        <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.1</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2504,39 +2504,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kristinspindling</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32713-2024 artfynd.xlsx", "A 32713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32776-2025 artfynd.xlsx", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32713-2024 karta.png", "A 32713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32776-2025 karta.png", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32713-2024 georefererad karta.tif", "A 32713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32776-2025 georefererad karta.tif", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32713-2024 FSC-klagomål.docx", "A 32713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32776-2025 FSC-klagomål.docx", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32713-2024 FSC-klagomål mail.docx", "A 32713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32776-2025 FSC-klagomål mail.docx", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32713-2024 tillsynsbegäran.docx", "A 32713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32776-2025 tillsynsbegäran.docx", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32713-2024 tillsynsbegäran mail.docx", "A 32713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32776-2025 tillsynsbegäran mail.docx", "A 32776-2025")</f>
         <v/>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
         <v>44509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44538</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>44614</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>44803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>44510</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44504</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44462</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>44517</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>44666</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>44756</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44796</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 36114-2022</t>
+          <t>A 6705-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44803</v>
+        <v>45342</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3599,8 +3599,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3643,7 +3648,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 47600-2023</t>
+          <t>A 15790-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3657,10 +3662,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45203</v>
+        <v>45748</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3673,7 +3678,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3716,7 +3721,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 15906-2024</t>
+          <t>A 36114-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3726,14 +3731,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45405</v>
+        <v>44803</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3746,7 +3751,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3789,7 +3794,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54226-2021</t>
+          <t>A 35661-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3803,10 +3808,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44470</v>
+        <v>45532</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3819,7 +3824,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3862,7 +3867,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 30389-2024</t>
+          <t>A 5819-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3872,14 +3877,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45491</v>
+        <v>45335</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3891,8 +3896,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>5.6</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3935,7 +3945,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 48325-2022</t>
+          <t>A 3198-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3945,14 +3955,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44858</v>
+        <v>45316</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3964,13 +3974,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4013,7 +4018,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 47993-2024</t>
+          <t>A 8256-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4023,14 +4028,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45589</v>
+        <v>44974</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4043,7 +4048,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4086,7 +4091,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 64802-2021</t>
+          <t>A 26949-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4096,14 +4101,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44512</v>
+        <v>45093</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4116,7 +4121,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4159,7 +4164,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 1323-2023</t>
+          <t>A 22088-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4173,10 +4178,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44936</v>
+        <v>45069</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4189,7 +4194,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4232,7 +4237,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 1578-2023</t>
+          <t>A 15813-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4242,14 +4247,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44937</v>
+        <v>44664</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4261,8 +4266,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4305,7 +4315,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 6164-2024</t>
+          <t>A 38152-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4319,10 +4329,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45337</v>
+        <v>45161</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4335,7 +4345,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4378,7 +4388,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 32335-2024</t>
+          <t>A 56841-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4392,10 +4402,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45512</v>
+        <v>44894</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4408,7 +4418,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4451,7 +4461,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 6705-2024</t>
+          <t>A 44069-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4465,10 +4475,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45342</v>
+        <v>45188</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4480,13 +4490,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>8.300000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4529,7 +4534,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 35661-2024</t>
+          <t>A 11280-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4543,10 +4548,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45532</v>
+        <v>45726</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4559,7 +4564,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4602,7 +4607,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 56841-2022</t>
+          <t>A 1578-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4616,10 +4621,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44894</v>
+        <v>44937</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4632,7 +4637,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4675,7 +4680,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 3149-2024</t>
+          <t>A 38259-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4689,10 +4694,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45316</v>
+        <v>45161</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4705,7 +4710,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4748,7 +4753,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 47597-2023</t>
+          <t>A 15909-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4758,14 +4763,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45203</v>
+        <v>45405</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4778,7 +4783,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4821,7 +4826,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 15907-2024</t>
+          <t>A 39032-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4831,14 +4836,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45405</v>
+        <v>45163</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4850,8 +4855,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4894,7 +4904,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 15915-2024</t>
+          <t>A 39920-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4904,14 +4914,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45405</v>
+        <v>45553</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4967,7 +4977,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 30388-2024</t>
+          <t>A 45973-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4981,10 +4991,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45491</v>
+        <v>45580</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5040,7 +5050,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 17618-2024</t>
+          <t>A 9448-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5054,10 +5064,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45416</v>
+        <v>44981</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5070,7 +5080,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5113,7 +5123,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 13129-2023</t>
+          <t>A 46528-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5127,10 +5137,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45002</v>
+        <v>45582</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5143,7 +5153,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5186,7 +5196,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 5283-2024</t>
+          <t>A 54226-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5200,10 +5210,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45331</v>
+        <v>44470</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5216,7 +5226,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5259,7 +5269,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 14750-2023</t>
+          <t>A 35079-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5273,10 +5283,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45014</v>
+        <v>45145</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5289,7 +5299,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5332,7 +5342,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8118-2026</t>
+          <t>A 36075-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5346,10 +5356,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46062</v>
+        <v>45149</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5362,7 +5372,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>13.4</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5405,7 +5415,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14156-2023</t>
+          <t>A 1674-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5419,10 +5429,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45009</v>
+        <v>44938</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5435,7 +5445,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5478,7 +5488,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 46528-2024</t>
+          <t>A 6421-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5492,10 +5502,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45582</v>
+        <v>45699</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5508,7 +5518,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5551,7 +5561,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 30600-2025</t>
+          <t>A 6456-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5565,10 +5575,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45831</v>
+        <v>45699</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5581,7 +5591,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5624,7 +5634,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8256-2023</t>
+          <t>A 17618-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5634,14 +5644,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44974</v>
+        <v>45416</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5654,7 +5664,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5697,7 +5707,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 32476-2025</t>
+          <t>A 47993-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5711,10 +5721,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45838</v>
+        <v>45589</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5727,7 +5737,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5770,7 +5780,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 22088-2023</t>
+          <t>A 5513-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5784,10 +5794,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45069</v>
+        <v>45693</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5800,7 +5810,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5843,7 +5853,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 32466-2025</t>
+          <t>A 13129-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5857,10 +5867,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45838</v>
+        <v>45002</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5873,7 +5883,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5916,7 +5926,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 36099-2024</t>
+          <t>A 6164-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5930,10 +5940,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45533</v>
+        <v>45337</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5946,7 +5956,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5989,7 +5999,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 14736-2024</t>
+          <t>A 14156-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5999,14 +6009,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45397</v>
+        <v>45009</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6062,7 +6072,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 20232-2022</t>
+          <t>A 16270-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6076,10 +6086,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44698</v>
+        <v>45407</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6091,13 +6101,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6140,7 +6145,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 12859-2026</t>
+          <t>A 35411-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6154,10 +6159,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46092</v>
+        <v>45146</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6170,7 +6175,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6213,7 +6218,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 12872-2026</t>
+          <t>A 20244-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6227,10 +6232,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46092</v>
+        <v>44698</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6242,8 +6247,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>9.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6286,7 +6296,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14185-2023</t>
+          <t>A 6557-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6300,10 +6310,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45009</v>
+        <v>45699</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6316,7 +6326,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6359,7 +6369,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 14617-2026</t>
+          <t>A 32378-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6373,10 +6383,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46101</v>
+        <v>45512</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6389,7 +6399,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6432,7 +6442,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 14166-2023</t>
+          <t>A 19351-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6446,10 +6456,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45009</v>
+        <v>45049</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6462,7 +6472,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6505,7 +6515,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 19350-2023</t>
+          <t>A 32335-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6519,10 +6529,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45049</v>
+        <v>45512</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6535,7 +6545,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6578,7 +6588,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 16341-2026</t>
+          <t>A 8515-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6592,10 +6602,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46111</v>
+        <v>44613</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6607,13 +6617,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6656,7 +6661,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16402-2026</t>
+          <t>A 61880-2021</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6670,10 +6675,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46111</v>
+        <v>44502</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6685,13 +6690,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6734,7 +6734,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 16414-2026</t>
+          <t>A 33375-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46111</v>
+        <v>45519</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>8.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6812,7 +6812,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 11972-2023</t>
+          <t>A 43263-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6822,14 +6822,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44994</v>
+        <v>45183</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6885,7 +6885,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 16370-2026</t>
+          <t>A 46536-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46111</v>
+        <v>45582</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6914,13 +6914,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>6.9</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6963,7 +6958,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 54419-2024</t>
+          <t>A 39027-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6977,10 +6972,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45617</v>
+        <v>45163</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6998,7 +6993,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>22.7</v>
+        <v>2.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7041,7 +7036,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 16259-2026</t>
+          <t>A 38212-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7055,10 +7050,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46109</v>
+        <v>45161</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7071,7 +7066,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7114,7 +7109,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 16262-2026</t>
+          <t>A 3130-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7128,10 +7123,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46109</v>
+        <v>45678</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7143,8 +7138,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>18.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7187,7 +7187,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 41730-2025</t>
+          <t>A 15907-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7197,14 +7197,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45902</v>
+        <v>45405</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7260,7 +7260,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 39024-2023</t>
+          <t>A 15915-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7270,14 +7270,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45163</v>
+        <v>45405</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7289,13 +7289,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7338,7 +7333,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 17950-2026</t>
+          <t>A 20232-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7352,10 +7347,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46122</v>
+        <v>44698</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7367,8 +7362,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7411,7 +7411,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 39032-2023</t>
+          <t>A 5350-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7425,10 +7425,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45163</v>
+        <v>45692</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7440,13 +7440,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7489,7 +7484,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 14993-2023</t>
+          <t>A 39024-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7503,10 +7498,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45015</v>
+        <v>45163</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7518,8 +7513,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7562,7 +7562,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 11280-2025</t>
+          <t>A 41730-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7576,10 +7576,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45726</v>
+        <v>45902</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7635,7 +7635,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 8049-2025</t>
+          <t>A 8063-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7652,7 +7652,7 @@
         <v>45707</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7708,7 +7708,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 39027-2023</t>
+          <t>A 32715-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7722,10 +7722,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45163</v>
+        <v>45516</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7737,13 +7737,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7786,7 +7781,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 38152-2023</t>
+          <t>A 6465-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7800,10 +7795,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45161</v>
+        <v>45699</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7816,7 +7811,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7859,7 +7854,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 8515-2022</t>
+          <t>A 1749-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7873,10 +7868,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44613</v>
+        <v>45671</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7889,7 +7884,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7932,7 +7927,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 38723-2023</t>
+          <t>A 165-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7946,10 +7941,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45163</v>
+        <v>46024</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7962,7 +7957,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8005,7 +8000,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 3130-2025</t>
+          <t>A 17126-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8019,10 +8014,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45678</v>
+        <v>45412</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8034,13 +8029,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>18.6</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8083,7 +8073,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 16128-2025</t>
+          <t>A 46059-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8097,10 +8087,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45750</v>
+        <v>45924</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8112,13 +8102,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8161,7 +8146,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 55971-2023</t>
+          <t>A 46778-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8175,10 +8160,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45240</v>
+        <v>45926</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8191,7 +8176,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8234,7 +8219,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 30945-2023</t>
+          <t>A 46999-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8248,10 +8233,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45113</v>
+        <v>45929</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8264,7 +8249,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8307,7 +8292,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 16164-2023</t>
+          <t>A 63074-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8321,10 +8306,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45027</v>
+        <v>46009</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8342,7 +8327,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8385,7 +8370,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 46059-2025</t>
+          <t>A 46788-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8399,10 +8384,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8415,7 +8400,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8458,7 +8443,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 63074-2025</t>
+          <t>A 47648-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8472,10 +8457,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46009</v>
+        <v>45931</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8487,13 +8472,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>8.699999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8536,7 +8516,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 165-2026</t>
+          <t>A 4678-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8550,10 +8530,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46024</v>
+        <v>45328</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8566,7 +8546,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8609,7 +8589,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 5350-2025</t>
+          <t>A 48063-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8623,10 +8603,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45692</v>
+        <v>45932</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8639,7 +8619,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8682,7 +8662,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 30964-2023</t>
+          <t>A 21771-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8696,10 +8676,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45113</v>
+        <v>45065</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8712,7 +8692,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.7</v>
+        <v>5.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8755,7 +8735,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 46788-2025</t>
+          <t>A 48611-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8769,10 +8749,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45926</v>
+        <v>45936</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8785,7 +8765,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8828,7 +8808,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 46778-2025</t>
+          <t>A 48614-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8842,10 +8822,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45926</v>
+        <v>45936</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8858,7 +8838,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8901,7 +8881,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 21770-2023</t>
+          <t>A 48575-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8915,10 +8895,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45065</v>
+        <v>45936</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8931,7 +8911,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8974,7 +8954,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 19351-2023</t>
+          <t>A 64802-2021</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8984,14 +8964,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45049</v>
+        <v>44512</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9004,7 +8984,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5.8</v>
+        <v>2.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9047,7 +9027,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 46999-2025</t>
+          <t>A 16128-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9061,10 +9041,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45929</v>
+        <v>45750</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9076,8 +9056,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9120,7 +9105,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 38266-2022</t>
+          <t>A 3149-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9134,10 +9119,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44812</v>
+        <v>45316</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9150,7 +9135,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9193,7 +9178,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 48063-2025</t>
+          <t>A 50416-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9207,10 +9192,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45932</v>
+        <v>45944</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9223,7 +9208,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9266,7 +9251,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 47648-2025</t>
+          <t>A 51171-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9280,10 +9265,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45931</v>
+        <v>45947</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9296,7 +9281,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9339,7 +9324,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 48575-2025</t>
+          <t>A 51328-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9353,10 +9338,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45936</v>
+        <v>45950</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9369,7 +9354,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9412,7 +9397,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 21771-2023</t>
+          <t>A 51180-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9426,10 +9411,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45065</v>
+        <v>45603</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9442,7 +9427,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>5.5</v>
+        <v>1.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9485,7 +9470,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 48611-2025</t>
+          <t>A 35229-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9499,10 +9484,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45936</v>
+        <v>45145</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9515,7 +9500,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9558,7 +9543,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 48614-2025</t>
+          <t>A 51178-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9572,10 +9557,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45936</v>
+        <v>45603</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9588,7 +9573,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9631,7 +9616,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 63115-2025</t>
+          <t>A 19157-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9645,10 +9630,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46009</v>
+        <v>45048</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9661,7 +9646,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9704,7 +9689,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 35079-2023</t>
+          <t>A 55971-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9718,10 +9703,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45145</v>
+        <v>45240</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9734,7 +9719,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9777,7 +9762,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 45973-2024</t>
+          <t>A 16164-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9791,10 +9776,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45580</v>
+        <v>45027</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9806,8 +9791,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9850,7 +9840,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 61011-2024</t>
+          <t>A 63115-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9860,14 +9850,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45645</v>
+        <v>46009</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9880,7 +9870,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9923,7 +9913,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 50416-2025</t>
+          <t>A 39024-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9937,10 +9927,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45944</v>
+        <v>45163</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9952,8 +9942,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9996,7 +9991,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 1337-2026</t>
+          <t>A 20720-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10010,10 +10005,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46031</v>
+        <v>45776</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10026,7 +10021,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10069,7 +10064,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 8067-2025</t>
+          <t>A 55901-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10083,10 +10078,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45707</v>
+        <v>45973</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10099,7 +10094,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10142,7 +10137,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 35229-2023</t>
+          <t>A 55906-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10156,10 +10151,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45145</v>
+        <v>45973</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10172,7 +10167,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10215,7 +10210,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 5819-2024</t>
+          <t>A 47597-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10225,14 +10220,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45335</v>
+        <v>45203</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10244,13 +10239,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10293,7 +10283,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 32464-2025</t>
+          <t>A 55908-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10307,10 +10297,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45838</v>
+        <v>45973</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10323,7 +10313,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10366,7 +10356,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 61880-2021</t>
+          <t>A 14166-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10380,10 +10370,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44502</v>
+        <v>45009</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10396,7 +10386,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10439,7 +10429,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 38212-2023</t>
+          <t>A 15344-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10453,10 +10443,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45161</v>
+        <v>45747</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10469,7 +10459,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10512,7 +10502,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 27087-2024</t>
+          <t>A 10335-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10526,10 +10516,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45471</v>
+        <v>44623</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10542,7 +10532,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10585,7 +10575,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 39920-2024</t>
+          <t>A 35095-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10599,10 +10589,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45553</v>
+        <v>45145</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10615,7 +10605,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10658,7 +10648,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 46536-2024</t>
+          <t>A 20612-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10672,10 +10662,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45582</v>
+        <v>44700</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10687,8 +10677,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1.3</v>
+        <v>8.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10731,7 +10726,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 51171-2025</t>
+          <t>A 15198-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10745,10 +10740,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45947</v>
+        <v>44658</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10761,7 +10756,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10804,7 +10799,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 51328-2025</t>
+          <t>A 6375-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10818,10 +10813,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45950</v>
+        <v>45699</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10834,7 +10829,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>6</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10877,7 +10872,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 4678-2024</t>
+          <t>A 6592-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10891,10 +10886,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45328</v>
+        <v>45700</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10907,7 +10902,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10950,7 +10945,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 25895-2026</t>
+          <t>A 37843-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10964,10 +10959,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46178</v>
+        <v>45160</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10980,7 +10975,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.5</v>
+        <v>4.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11023,7 +11018,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 35095-2023</t>
+          <t>A 6506-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11037,10 +11032,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45145</v>
+        <v>45699</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11053,7 +11048,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11096,7 +11091,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 1749-2025</t>
+          <t>A 61011-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11106,14 +11101,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45671</v>
+        <v>45645</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11126,7 +11121,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11169,7 +11164,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 25816-2026</t>
+          <t>A 61786-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11183,10 +11178,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46178</v>
+        <v>46002</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11199,7 +11194,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11242,7 +11237,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 25863-2026</t>
+          <t>A 1337-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11256,10 +11251,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46178</v>
+        <v>46031</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11272,7 +11267,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11315,7 +11310,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 15909-2024</t>
+          <t>A 5283-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11325,14 +11320,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45405</v>
+        <v>45331</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11345,7 +11340,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.1</v>
+        <v>3.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11388,7 +11383,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 25975-2026</t>
+          <t>A 32464-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11402,10 +11397,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46181</v>
+        <v>45838</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11418,7 +11413,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11461,7 +11456,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 6375-2025</t>
+          <t>A 61798-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11475,10 +11470,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45699</v>
+        <v>46002</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11490,8 +11485,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 27274-2026</t>
+          <t>A 61800-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11548,10 +11548,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46184</v>
+        <v>46002</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11607,7 +11607,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 27292-2026</t>
+          <t>A 61801-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11621,10 +11621,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46184</v>
+        <v>46002</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11680,7 +11680,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 32378-2024</t>
+          <t>A 61972-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11694,10 +11694,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45512</v>
+        <v>46003</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11709,8 +11709,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11753,7 +11758,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 51180-2024</t>
+          <t>A 8067-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11767,10 +11772,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45603</v>
+        <v>45707</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11783,7 +11788,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11826,7 +11831,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 20720-2025</t>
+          <t>A 61470-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11840,10 +11845,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45776</v>
+        <v>46001</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11855,8 +11860,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11899,7 +11909,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 39190-2023</t>
+          <t>A 61629-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11909,14 +11919,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45166</v>
+        <v>46002</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11929,7 +11939,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11972,7 +11982,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 28908-2026</t>
+          <t>A 62482-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11986,10 +11996,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46199</v>
+        <v>46007</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12002,7 +12012,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>5.3</v>
+        <v>6.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12045,7 +12055,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 16168-2023</t>
+          <t>A 62202-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12059,10 +12069,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45027</v>
+        <v>46006</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12074,13 +12084,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12123,7 +12128,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 38718-2023</t>
+          <t>A 62801-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12137,10 +12142,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45163</v>
+        <v>46008</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12153,7 +12158,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>3.2</v>
+        <v>6.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12196,7 +12201,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 28704-2026</t>
+          <t>A 38723-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12210,10 +12215,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46198</v>
+        <v>45163</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12225,13 +12230,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12274,7 +12274,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 55908-2025</t>
+          <t>A 50387-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12288,10 +12288,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45973</v>
+        <v>45600</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.8</v>
+        <v>8.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12347,7 +12347,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 55901-2025</t>
+          <t>A 2512-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12361,10 +12361,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45973</v>
+        <v>45313</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12377,7 +12377,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12420,7 +12420,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 2512-2024</t>
+          <t>A 64709-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12434,10 +12434,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45313</v>
+        <v>45281</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12493,7 +12493,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 55906-2025</t>
+          <t>A 64710-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12507,10 +12507,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45973</v>
+        <v>45281</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12566,7 +12566,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 28718-2026</t>
+          <t>A 64010-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12580,10 +12580,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46198</v>
+        <v>46021</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2</v>
+        <v>15.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12644,7 +12644,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 51178-2024</t>
+          <t>A 36730-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12658,10 +12658,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45603</v>
+        <v>45153</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12717,7 +12717,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 35380-2023</t>
+          <t>A 64015-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12731,10 +12731,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45146</v>
+        <v>46021</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12744,6 +12744,11 @@
       <c r="G158" t="inlineStr">
         <is>
           <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I158" t="n">
@@ -12790,7 +12795,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 30155-2026</t>
+          <t>A 602-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12804,10 +12809,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46206</v>
+        <v>46029</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12819,13 +12824,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 6592-2025</t>
+          <t>A 1279-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12882,10 +12882,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45700</v>
+        <v>46031</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12941,7 +12941,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 43263-2023</t>
+          <t>A 1261-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12951,14 +12951,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45183</v>
+        <v>46031</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13014,7 +13014,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 20244-2022</t>
+          <t>A 1268-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13028,10 +13028,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44698</v>
+        <v>46031</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13043,13 +13043,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>9.5</v>
+        <v>0.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13092,7 +13087,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 20612-2022</t>
+          <t>A 16168-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13106,10 +13101,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44700</v>
+        <v>45027</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13127,7 +13122,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>8.9</v>
+        <v>3.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13170,7 +13165,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 6421-2025</t>
+          <t>A 21770-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13184,10 +13179,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45699</v>
+        <v>45065</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13200,7 +13195,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13243,7 +13238,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 52469-2023</t>
+          <t>A 36099-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13257,10 +13252,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45225</v>
+        <v>45533</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13273,7 +13268,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13316,7 +13311,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 8063-2025</t>
+          <t>A 1264-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13330,10 +13325,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45707</v>
+        <v>46031</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13346,7 +13341,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13389,7 +13384,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 15790-2025</t>
+          <t>A 1273-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13403,10 +13398,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45748</v>
+        <v>46031</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13419,7 +13414,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13462,7 +13457,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 37843-2023</t>
+          <t>A 1585-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13476,10 +13471,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45160</v>
+        <v>46034</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13491,8 +13486,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13535,7 +13535,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 6465-2025</t>
+          <t>A 1589-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13549,10 +13549,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45699</v>
+        <v>46034</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13564,8 +13564,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13608,7 +13613,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 50358-2025</t>
+          <t>A 38718-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13622,10 +13627,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45944</v>
+        <v>45163</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13638,7 +13643,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13681,7 +13686,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 1674-2023</t>
+          <t>A 15906-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13691,14 +13696,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44938</v>
+        <v>45405</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13711,7 +13716,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.3</v>
+        <v>0.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13754,7 +13759,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 34961-2022</t>
+          <t>A 35097-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13768,10 +13773,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44796</v>
+        <v>45145</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13784,7 +13789,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13827,7 +13832,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 61801-2025</t>
+          <t>A 25895-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13841,10 +13846,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46002</v>
+        <v>46178</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13857,7 +13862,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13900,7 +13905,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 61470-2025</t>
+          <t>A 30945-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13914,10 +13919,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46001</v>
+        <v>45113</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13929,13 +13934,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>8</v>
+        <v>2.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13978,7 +13978,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 31447-2026</t>
+          <t>A 30964-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13992,10 +13992,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46220</v>
+        <v>45113</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14051,7 +14051,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 61798-2025</t>
+          <t>A 25863-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14065,10 +14065,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46002</v>
+        <v>46178</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14080,13 +14080,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14129,7 +14124,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 61800-2025</t>
+          <t>A 7375-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14143,10 +14138,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46002</v>
+        <v>46059</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14159,7 +14154,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14202,7 +14197,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 61629-2025</t>
+          <t>A 25816-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14216,10 +14211,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46002</v>
+        <v>46178</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14232,7 +14227,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14275,7 +14270,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 19157-2023</t>
+          <t>A 8118-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14289,10 +14284,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45048</v>
+        <v>46062</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14305,7 +14300,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.5</v>
+        <v>13.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14348,7 +14343,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 61786-2025</t>
+          <t>A 25975-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14362,10 +14357,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46002</v>
+        <v>46181</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14378,7 +14373,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14421,7 +14416,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 62202-2025</t>
+          <t>A 27274-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14435,10 +14430,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46006</v>
+        <v>46184</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14451,7 +14446,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14494,7 +14489,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 61972-2025</t>
+          <t>A 48325-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14504,14 +14499,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46003</v>
+        <v>44858</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14529,7 +14524,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14572,7 +14567,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 62801-2025</t>
+          <t>A 27292-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14586,10 +14581,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46008</v>
+        <v>46184</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14602,7 +14597,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14645,7 +14640,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 62482-2025</t>
+          <t>A 11699-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14659,10 +14654,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46007</v>
+        <v>45373</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14675,7 +14670,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>6.7</v>
+        <v>2.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14718,7 +14713,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 39024-2023</t>
+          <t>A 11704-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14732,10 +14727,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45163</v>
+        <v>45373</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14747,13 +14742,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14796,7 +14786,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 36824-2026</t>
+          <t>A 11193-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14806,14 +14796,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46272</v>
+        <v>44992</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14825,13 +14815,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>8</v>
+        <v>2.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14874,7 +14859,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 17126-2024</t>
+          <t>A 12872-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14888,10 +14873,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45412</v>
+        <v>46092</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14904,7 +14889,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14947,7 +14932,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 37473-2026</t>
+          <t>A 8049-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14961,10 +14946,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46275</v>
+        <v>45707</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14977,7 +14962,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15020,7 +15005,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 37482-2026</t>
+          <t>A 12859-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15034,10 +15019,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46275</v>
+        <v>46092</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15049,13 +15034,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>16.5</v>
+        <v>0.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15098,7 +15078,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 37469-2026</t>
+          <t>A 30389-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15112,10 +15092,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46275</v>
+        <v>45491</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15128,7 +15108,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15171,7 +15151,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 64015-2025</t>
+          <t>A 35380-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15185,10 +15165,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46021</v>
+        <v>45146</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15198,11 +15178,6 @@
       <c r="G191" t="inlineStr">
         <is>
           <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I191" t="n">
@@ -15249,7 +15224,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 64010-2025</t>
+          <t>A 54419-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15263,10 +15238,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46021</v>
+        <v>45617</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15284,7 +15259,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>15.4</v>
+        <v>22.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15327,7 +15302,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 37991-2026</t>
+          <t>A 14617-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15341,10 +15316,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46280</v>
+        <v>46101</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15357,7 +15332,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15400,7 +15375,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 11193-2023</t>
+          <t>A 28718-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15410,14 +15385,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44992</v>
+        <v>46198</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15429,8 +15404,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15473,7 +15453,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 602-2026</t>
+          <t>A 28704-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15487,10 +15467,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46029</v>
+        <v>46198</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15502,8 +15482,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15546,7 +15531,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 1589-2026</t>
+          <t>A 16370-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15560,10 +15545,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46034</v>
+        <v>46111</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15581,7 +15566,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3.7</v>
+        <v>6.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15624,7 +15609,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 1279-2026</t>
+          <t>A 34961-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15638,10 +15623,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46031</v>
+        <v>44796</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15654,7 +15639,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15697,7 +15682,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 1264-2026</t>
+          <t>A 14185-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15711,10 +15696,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46031</v>
+        <v>45009</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15727,7 +15712,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15770,7 +15755,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 26949-2023</t>
+          <t>A 16414-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15784,10 +15769,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45093</v>
+        <v>46111</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15799,8 +15784,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>1.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15843,7 +15833,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 1585-2026</t>
+          <t>A 16402-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15857,10 +15847,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46034</v>
+        <v>46111</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15878,7 +15868,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15921,7 +15911,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 37494-2026</t>
+          <t>A 16341-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15935,10 +15925,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46275</v>
+        <v>46111</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15948,6 +15938,11 @@
       <c r="G201" t="inlineStr">
         <is>
           <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I201" t="n">
@@ -15994,7 +15989,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 1273-2026</t>
+          <t>A 27087-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16008,10 +16003,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46031</v>
+        <v>45471</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16024,7 +16019,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16067,7 +16062,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 1261-2026</t>
+          <t>A 28908-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16081,10 +16076,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46031</v>
+        <v>46199</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16097,7 +16092,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16140,7 +16135,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 1268-2026</t>
+          <t>A 6368-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16154,10 +16149,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46031</v>
+        <v>45699</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16170,7 +16165,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16213,7 +16208,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 6506-2025</t>
+          <t>A 39190-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16223,14 +16218,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45699</v>
+        <v>45166</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16243,7 +16238,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16286,7 +16281,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 12332-2023</t>
+          <t>A 16259-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16300,10 +16295,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44999</v>
+        <v>46109</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16316,7 +16311,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16359,7 +16354,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 36075-2023</t>
+          <t>A 16262-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16373,10 +16368,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45149</v>
+        <v>46109</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16389,7 +16384,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16432,7 +16427,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 15198-2022</t>
+          <t>A 17950-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16446,10 +16441,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44658</v>
+        <v>46122</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16462,7 +16457,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16505,7 +16500,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 6456-2025</t>
+          <t>A 54590-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16519,10 +16514,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45699</v>
+        <v>45617</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16535,7 +16530,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16578,7 +16573,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 21855-2022</t>
+          <t>A 14993-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16592,10 +16587,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44709</v>
+        <v>45015</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16608,7 +16603,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16651,7 +16646,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 72603-2021</t>
+          <t>A 52469-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16665,10 +16660,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44546</v>
+        <v>45225</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16681,7 +16676,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16724,7 +16719,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 9448-2023</t>
+          <t>A 19350-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16738,10 +16733,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44981</v>
+        <v>45049</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16754,7 +16749,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16797,7 +16792,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 64709-2023</t>
+          <t>A 51041-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16811,10 +16806,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45281</v>
+        <v>45603</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16827,7 +16822,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16870,7 +16865,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 64710-2023</t>
+          <t>A 30155-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16884,10 +16879,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45281</v>
+        <v>46206</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16899,8 +16894,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>0.1</v>
+        <v>5.8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 35097-2023</t>
+          <t>A 11972-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45145</v>
+        <v>44994</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 35411-2023</t>
+          <t>A 12332-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17030,10 +17030,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45146</v>
+        <v>44999</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17089,7 +17089,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 36730-2023</t>
+          <t>A 38266-2022</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17103,10 +17103,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45153</v>
+        <v>44812</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17162,7 +17162,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 7375-2026</t>
+          <t>A 1323-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17176,10 +17176,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46059</v>
+        <v>44936</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17235,7 +17235,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 25729-2023</t>
+          <t>A 50358-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17249,10 +17249,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45084</v>
+        <v>45944</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17308,7 +17308,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 11699-2024</t>
+          <t>A 14736-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17318,14 +17318,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45373</v>
+        <v>45397</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17381,7 +17381,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 11704-2024</t>
+          <t>A 25729-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17395,10 +17395,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45373</v>
+        <v>45084</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17454,7 +17454,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 54590-2024</t>
+          <t>A 30388-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17468,10 +17468,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45617</v>
+        <v>45491</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17527,7 +17527,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 10335-2022</t>
+          <t>A 31447-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17541,10 +17541,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>44623</v>
+        <v>46220</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17600,7 +17600,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 33375-2024</t>
+          <t>A 21855-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17614,10 +17614,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45519</v>
+        <v>44709</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17629,13 +17629,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17678,7 +17673,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 5513-2025</t>
+          <t>A 72603-2021</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17692,10 +17687,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45693</v>
+        <v>44546</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17708,7 +17703,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17751,7 +17746,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 15813-2022</t>
+          <t>A 14750-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17761,14 +17756,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44664</v>
+        <v>45014</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17780,13 +17775,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17829,7 +17819,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 6368-2025</t>
+          <t>A 47600-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17843,10 +17833,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45699</v>
+        <v>45203</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17859,7 +17849,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17902,7 +17892,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 44069-2023</t>
+          <t>A 21357-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17916,10 +17906,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45188</v>
+        <v>45782</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17932,7 +17922,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17975,7 +17965,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 3198-2024</t>
+          <t>A 21530-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17989,10 +17979,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45316</v>
+        <v>45782</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18005,7 +17995,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18048,7 +18038,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 16270-2024</t>
+          <t>A 36824-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18062,10 +18052,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45407</v>
+        <v>46272</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18077,8 +18067,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I230" t="n">
-        <v>0.7</v>
+        <v>8</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18121,7 +18116,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 51041-2024</t>
+          <t>A 37482-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18135,10 +18130,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45603</v>
+        <v>46275</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18150,8 +18145,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I231" t="n">
-        <v>0.4</v>
+        <v>16.5</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 6557-2025</t>
+          <t>A 37473-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18208,10 +18208,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45699</v>
+        <v>46275</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18267,7 +18267,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 15344-2025</t>
+          <t>A 37469-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18281,10 +18281,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45747</v>
+        <v>46275</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18340,7 +18340,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 50387-2024</t>
+          <t>A 3554-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18354,10 +18354,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45600</v>
+        <v>45680</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>8.5</v>
+        <v>3.9</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18413,7 +18413,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 32715-2024</t>
+          <t>A 50818-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18427,10 +18427,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45516</v>
+        <v>45217</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18486,7 +18486,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 38259-2023</t>
+          <t>A 37991-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18500,10 +18500,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45161</v>
+        <v>46280</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18559,7 +18559,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 21530-2025</t>
+          <t>A 21336-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18576,7 +18576,7 @@
         <v>45782</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18632,7 +18632,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 21357-2025</t>
+          <t>A 37494-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18646,10 +18646,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45782</v>
+        <v>46275</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18705,7 +18705,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 3554-2025</t>
+          <t>A 30600-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18719,10 +18719,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45680</v>
+        <v>45831</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18778,7 +18778,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 50818-2023</t>
+          <t>A 32466-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18792,10 +18792,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45217</v>
+        <v>45838</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18851,7 +18851,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 21336-2025</t>
+          <t>A 32476-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18865,10 +18865,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45782</v>
+        <v>45838</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18941,7 +18941,7 @@
         <v>45376</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44879</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>

--- a/Översikt ÖDESHÖG.xlsx
+++ b/Översikt ÖDESHÖG.xlsx
@@ -601,7 +601,7 @@
         <v>45805</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45723</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44698</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>44664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>45244</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>44798</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>44538</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>45251</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45210</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>45747</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>45516</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>45272</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45163</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45243</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>44487</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>44592</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44538</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>44614</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>44803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>44510</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44504</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44462</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>44517</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>44666</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>44756</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44796</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>45342</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45748</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>44803</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>45532</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>45335</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45316</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>44974</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>45093</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>45069</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44664</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45161</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>44894</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>45188</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>45726</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>44937</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>45161</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>45405</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>45163</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45553</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>45580</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44981</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>45582</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>44470</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>45145</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>45149</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44938</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45699</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>45699</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45416</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>45589</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>45693</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45002</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>45337</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>45009</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>45407</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>45146</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44698</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>45699</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>45512</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>45049</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>45512</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>44613</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>44502</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>45519</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>45183</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>45582</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>45163</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         <v>45161</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         <v>45678</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>45405</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>45405</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>44698</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>45692</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>45163</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45902</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>45707</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>45516</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>45699</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>45671</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>46024</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8017,7 +8017,7 @@
         <v>45412</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>45924</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>45926</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>45929</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>46009</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45926</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>45931</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>45328</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>45932</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>45065</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>45936</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>45936</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>45936</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>44512</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>45750</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>45316</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>45944</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>45947</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>45950</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>45603</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>45145</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>45603</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>45048</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>45240</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>45027</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>46009</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>45163</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>45776</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>45973</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>45973</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>45203</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>45973</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>45009</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>45747</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>44623</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>45145</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>44700</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>44658</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>45699</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>45700</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>45160</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>45699</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>45645</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>46002</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>46031</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>45331</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>45838</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>46002</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>46002</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>46002</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>46003</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>45707</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>46001</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>46002</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>46007</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>46006</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>46008</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>45163</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>45600</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>45313</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>45281</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>45281</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>46021</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>45153</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>46021</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>46029</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>46031</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>46031</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>46031</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>45027</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>45065</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>45533</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>46031</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>46031</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>46034</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>46034</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>45163</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>45405</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>45145</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>46178</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>45113</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>45113</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>46178</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>46059</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>46178</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>46062</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>46181</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>46184</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>44858</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14584,7 +14584,7 @@
         <v>46184</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14657,7 +14657,7 @@
         <v>45373</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>45373</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>44992</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>46092</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>45707</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>46092</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>45491</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>45146</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15241,7 +15241,7 @@
         <v>45617</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>46101</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>46198</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>46198</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>46111</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>44796</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>45009</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
         <v>46111</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>46111</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
         <v>46111</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>45471</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16079,7 +16079,7 @@
         <v>46199</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>45699</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>45166</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>46109</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>46109</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>46122</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>45617</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>45015</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>45225</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>45049</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>45603</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>46206</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>44994</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>44999</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>44812</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>44936</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>45944</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45397</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>45084</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>45491</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>46220</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         <v>44709</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>44546</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>45014</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>45203</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45782</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>45782</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>46272</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>46275</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>46275</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>46275</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>45680</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45217</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>46280</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>45782</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>46275</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>45831</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>45838</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>45838</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>45376</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44879</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>

--- a/Översikt ÖDESHÖG.xlsx
+++ b/Översikt ÖDESHÖG.xlsx
@@ -601,7 +601,7 @@
         <v>45805</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45723</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44698</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>44664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>45244</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>44798</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>44538</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>45251</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>45210</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>45747</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>45516</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>45272</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>45163</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>45243</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>44487</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>44592</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44538</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>44614</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>44803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>44510</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44504</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44462</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>44517</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>44666</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>44756</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44796</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>45342</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45748</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 36114-2022</t>
+          <t>A 5819-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3731,14 +3731,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44803</v>
+        <v>45335</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3750,8 +3750,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3811,7 +3816,7 @@
         <v>45532</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3867,7 +3872,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 5819-2024</t>
+          <t>A 36114-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3877,14 +3882,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45335</v>
+        <v>44803</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3896,13 +3901,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3962,7 +3962,7 @@
         <v>45316</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8256-2023</t>
+          <t>A 22088-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4028,14 +4028,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44974</v>
+        <v>45069</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4091,7 +4091,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 26949-2023</t>
+          <t>A 8256-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4101,14 +4101,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45093</v>
+        <v>44974</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 22088-2023</t>
+          <t>A 26949-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45069</v>
+        <v>45093</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4254,7 +4254,7 @@
         <v>44664</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45161</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 56841-2022</t>
+          <t>A 44069-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44894</v>
+        <v>45188</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 44069-2023</t>
+          <t>A 1578-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45188</v>
+        <v>44937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11280-2025</t>
+          <t>A 56841-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45726</v>
+        <v>44894</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 1578-2023</t>
+          <t>A 11280-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4621,10 +4621,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44937</v>
+        <v>45726</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38259-2023</t>
+          <t>A 15909-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4690,14 +4690,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45161</v>
+        <v>45405</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4753,7 +4753,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 15909-2024</t>
+          <t>A 38259-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4763,14 +4763,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45405</v>
+        <v>45161</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.1</v>
+        <v>2.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4843,7 +4843,7 @@
         <v>45163</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45553</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>45580</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44981</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 46528-2024</t>
+          <t>A 54226-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45582</v>
+        <v>44470</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5196,7 +5196,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 54226-2021</t>
+          <t>A 36075-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5210,10 +5210,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44470</v>
+        <v>45149</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5269,7 +5269,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 35079-2023</t>
+          <t>A 1674-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45145</v>
+        <v>44938</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5342,7 +5342,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 36075-2023</t>
+          <t>A 35079-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5356,10 +5356,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45149</v>
+        <v>45145</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 1674-2023</t>
+          <t>A 6421-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44938</v>
+        <v>45699</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5488,7 +5488,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 6421-2025</t>
+          <t>A 6456-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5505,7 +5505,7 @@
         <v>45699</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5561,7 +5561,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 6456-2025</t>
+          <t>A 17618-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45699</v>
+        <v>45416</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 17618-2024</t>
+          <t>A 47993-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45416</v>
+        <v>45589</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5664,7 +5664,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5707,7 +5707,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 47993-2024</t>
+          <t>A 5513-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5721,10 +5721,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45589</v>
+        <v>45693</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5780,7 +5780,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 5513-2025</t>
+          <t>A 13129-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5794,10 +5794,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45693</v>
+        <v>45002</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5853,7 +5853,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 13129-2023</t>
+          <t>A 46528-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45002</v>
+        <v>45582</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5943,7 +5943,7 @@
         <v>45337</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>45009</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 16270-2024</t>
+          <t>A 35411-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6086,10 +6086,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45407</v>
+        <v>45146</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6145,7 +6145,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 35411-2023</t>
+          <t>A 16270-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6159,10 +6159,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45146</v>
+        <v>45407</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6235,7 +6235,7 @@
         <v>44698</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>45699</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>45512</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>45049</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>45512</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>44613</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>44502</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>45519</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 43263-2023</t>
+          <t>A 39027-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6822,14 +6822,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45183</v>
+        <v>45163</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6841,8 +6841,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6885,7 +6890,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 46536-2024</t>
+          <t>A 43263-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6895,14 +6900,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45582</v>
+        <v>45183</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6915,7 +6920,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6958,7 +6963,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 39027-2023</t>
+          <t>A 46536-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6972,10 +6977,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45163</v>
+        <v>45582</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6987,13 +6992,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 38212-2023</t>
+          <t>A 39024-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45161</v>
+        <v>45163</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7065,8 +7065,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7109,7 +7114,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3130-2025</t>
+          <t>A 41730-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7123,10 +7128,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45678</v>
+        <v>45902</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7138,13 +7143,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>18.6</v>
+        <v>1.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7187,7 +7187,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 15907-2024</t>
+          <t>A 5350-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7197,14 +7197,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45405</v>
+        <v>45692</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7260,7 +7260,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 15915-2024</t>
+          <t>A 38212-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7270,14 +7270,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45405</v>
+        <v>45161</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7333,7 +7333,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 20232-2022</t>
+          <t>A 3130-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44698</v>
+        <v>45678</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>18.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7411,7 +7411,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 5350-2025</t>
+          <t>A 15907-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7421,14 +7421,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45692</v>
+        <v>45405</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7484,7 +7484,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 39024-2023</t>
+          <t>A 15915-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7494,14 +7494,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45163</v>
+        <v>45405</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7513,13 +7513,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7562,7 +7557,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41730-2025</t>
+          <t>A 20232-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7576,10 +7571,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45902</v>
+        <v>44698</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7591,8 +7586,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7635,7 +7635,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 8063-2025</t>
+          <t>A 46059-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45707</v>
+        <v>45924</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7708,7 +7708,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 32715-2024</t>
+          <t>A 46778-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7722,10 +7722,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45516</v>
+        <v>45926</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7781,7 +7781,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 6465-2025</t>
+          <t>A 46999-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7795,10 +7795,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45699</v>
+        <v>45929</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 1749-2025</t>
+          <t>A 46788-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7868,10 +7868,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45671</v>
+        <v>45926</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7927,7 +7927,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 165-2026</t>
+          <t>A 47648-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46024</v>
+        <v>45931</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8000,7 +8000,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 17126-2024</t>
+          <t>A 48063-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8014,10 +8014,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45412</v>
+        <v>45932</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8073,7 +8073,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 46059-2025</t>
+          <t>A 48611-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8087,10 +8087,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45924</v>
+        <v>45936</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8146,7 +8146,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 46778-2025</t>
+          <t>A 48614-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8160,10 +8160,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45926</v>
+        <v>45936</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8219,7 +8219,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 46999-2025</t>
+          <t>A 48575-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8233,10 +8233,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45929</v>
+        <v>45936</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8249,7 +8249,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8292,7 +8292,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 63074-2025</t>
+          <t>A 165-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8306,10 +8306,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46009</v>
+        <v>46024</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8321,13 +8321,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>8.699999999999999</v>
+        <v>3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8370,7 +8365,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 46788-2025</t>
+          <t>A 63074-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8384,10 +8379,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45926</v>
+        <v>46009</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8399,8 +8394,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8443,7 +8443,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 47648-2025</t>
+          <t>A 8063-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8457,10 +8457,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45931</v>
+        <v>45707</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8516,7 +8516,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 4678-2024</t>
+          <t>A 32715-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8530,10 +8530,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45328</v>
+        <v>45516</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8589,7 +8589,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 48063-2025</t>
+          <t>A 6465-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8603,10 +8603,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45932</v>
+        <v>45699</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8662,7 +8662,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 21771-2023</t>
+          <t>A 1749-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45065</v>
+        <v>45671</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8735,7 +8735,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 48611-2025</t>
+          <t>A 63115-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8749,10 +8749,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45936</v>
+        <v>46009</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.4</v>
+        <v>3.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 48614-2025</t>
+          <t>A 50416-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8822,10 +8822,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45936</v>
+        <v>45944</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8881,7 +8881,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 48575-2025</t>
+          <t>A 51171-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8895,10 +8895,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45936</v>
+        <v>45947</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 64802-2021</t>
+          <t>A 51328-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8964,14 +8964,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44512</v>
+        <v>45950</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 16128-2025</t>
+          <t>A 17126-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9041,10 +9041,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45750</v>
+        <v>45412</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9056,13 +9056,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9105,7 +9100,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 3149-2024</t>
+          <t>A 4678-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9119,10 +9114,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45316</v>
+        <v>45328</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9178,7 +9173,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 50416-2025</t>
+          <t>A 20720-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9192,10 +9187,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45944</v>
+        <v>45776</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9208,7 +9203,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9251,7 +9246,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 51171-2025</t>
+          <t>A 55901-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9265,10 +9260,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45947</v>
+        <v>45973</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9281,7 +9276,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9324,7 +9319,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 51328-2025</t>
+          <t>A 55906-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9338,10 +9333,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45950</v>
+        <v>45973</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9354,7 +9349,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9397,7 +9392,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 51180-2024</t>
+          <t>A 21771-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9411,10 +9406,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45603</v>
+        <v>45065</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9427,7 +9422,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9470,7 +9465,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 35229-2023</t>
+          <t>A 55908-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9484,10 +9479,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45145</v>
+        <v>45973</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9500,7 +9495,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9543,7 +9538,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 51178-2024</t>
+          <t>A 61011-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9553,14 +9548,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45603</v>
+        <v>45645</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9573,7 +9568,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9616,7 +9611,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 19157-2023</t>
+          <t>A 1337-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9630,10 +9625,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45048</v>
+        <v>46031</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9646,7 +9641,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9689,7 +9684,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 55971-2023</t>
+          <t>A 32464-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9703,10 +9698,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45240</v>
+        <v>45838</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9719,7 +9714,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9762,7 +9757,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 16164-2023</t>
+          <t>A 64802-2021</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9772,14 +9767,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45027</v>
+        <v>44512</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9791,13 +9786,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9840,7 +9830,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 63115-2025</t>
+          <t>A 8067-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9854,10 +9844,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46009</v>
+        <v>45707</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9870,7 +9860,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9913,7 +9903,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 39024-2023</t>
+          <t>A 16128-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9927,10 +9917,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45163</v>
+        <v>45750</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9948,7 +9938,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.7</v>
+        <v>1.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9991,7 +9981,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 20720-2025</t>
+          <t>A 3149-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10005,10 +9995,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45776</v>
+        <v>45316</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10021,7 +10011,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10064,7 +10054,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 55901-2025</t>
+          <t>A 51180-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10078,10 +10068,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45973</v>
+        <v>45603</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10094,7 +10084,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10137,7 +10127,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 55906-2025</t>
+          <t>A 35229-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10151,10 +10141,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45973</v>
+        <v>45145</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10167,7 +10157,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10210,7 +10200,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 47597-2023</t>
+          <t>A 51178-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10224,10 +10214,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45203</v>
+        <v>45603</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10240,7 +10230,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10283,7 +10273,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 55908-2025</t>
+          <t>A 61786-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10297,10 +10287,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45973</v>
+        <v>46002</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10313,7 +10303,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10356,7 +10346,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 14166-2023</t>
+          <t>A 19157-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10370,10 +10360,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45009</v>
+        <v>45048</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10386,7 +10376,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10429,7 +10419,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 15344-2025</t>
+          <t>A 61798-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10443,10 +10433,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45747</v>
+        <v>46002</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10458,8 +10448,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10502,7 +10497,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 10335-2022</t>
+          <t>A 61800-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10516,10 +10511,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44623</v>
+        <v>46002</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10532,7 +10527,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10575,7 +10570,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 35095-2023</t>
+          <t>A 61801-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10589,10 +10584,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45145</v>
+        <v>46002</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10605,7 +10600,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10648,7 +10643,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 20612-2022</t>
+          <t>A 61972-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10662,10 +10657,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44700</v>
+        <v>46003</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10683,7 +10678,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>8.9</v>
+        <v>4.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10726,7 +10721,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 15198-2022</t>
+          <t>A 61470-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10740,10 +10735,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44658</v>
+        <v>46001</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10755,8 +10750,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>2.3</v>
+        <v>8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10799,7 +10799,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 6375-2025</t>
+          <t>A 61629-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10813,10 +10813,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45699</v>
+        <v>46002</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10872,7 +10872,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 6592-2025</t>
+          <t>A 55971-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10886,10 +10886,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45700</v>
+        <v>45240</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10945,7 +10945,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 37843-2023</t>
+          <t>A 16164-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10959,10 +10959,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45160</v>
+        <v>45027</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10974,8 +10974,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11018,7 +11023,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 6506-2025</t>
+          <t>A 62482-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11032,10 +11037,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45699</v>
+        <v>46007</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11048,7 +11053,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.6</v>
+        <v>6.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11091,7 +11096,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 61011-2024</t>
+          <t>A 39024-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11101,14 +11106,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45645</v>
+        <v>45163</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11118,6 +11123,11 @@
       <c r="G136" t="inlineStr">
         <is>
           <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I136" t="n">
@@ -11164,7 +11174,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 61786-2025</t>
+          <t>A 62202-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11178,10 +11188,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11194,7 +11204,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11237,7 +11247,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 1337-2026</t>
+          <t>A 62801-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11251,10 +11261,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46031</v>
+        <v>46008</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11267,7 +11277,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11310,7 +11320,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 5283-2024</t>
+          <t>A 25895-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11324,10 +11334,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45331</v>
+        <v>46178</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11340,7 +11350,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11383,7 +11393,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 32464-2025</t>
+          <t>A 47597-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11397,10 +11407,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45838</v>
+        <v>45203</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11413,7 +11423,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11456,7 +11466,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 61798-2025</t>
+          <t>A 25863-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11470,10 +11480,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46002</v>
+        <v>46178</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11485,13 +11495,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11534,7 +11539,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 61800-2025</t>
+          <t>A 25816-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11548,10 +11553,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46002</v>
+        <v>46178</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11564,7 +11569,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11607,7 +11612,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 61801-2025</t>
+          <t>A 14166-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11621,10 +11626,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46002</v>
+        <v>45009</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11637,7 +11642,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11680,7 +11685,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 61972-2025</t>
+          <t>A 64010-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11694,10 +11699,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46003</v>
+        <v>46021</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11715,7 +11720,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4.5</v>
+        <v>15.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11758,7 +11763,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 8067-2025</t>
+          <t>A 64015-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11772,10 +11777,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45707</v>
+        <v>46021</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11785,6 +11790,11 @@
       <c r="G145" t="inlineStr">
         <is>
           <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I145" t="n">
@@ -11831,7 +11841,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 61470-2025</t>
+          <t>A 15344-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11845,10 +11855,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46001</v>
+        <v>45747</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11860,13 +11870,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11909,7 +11914,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 61629-2025</t>
+          <t>A 10335-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11923,10 +11928,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46002</v>
+        <v>44623</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11939,7 +11944,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11982,7 +11987,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 62482-2025</t>
+          <t>A 35095-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11996,10 +12001,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46007</v>
+        <v>45145</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12012,7 +12017,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>6.7</v>
+        <v>0.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12055,7 +12060,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 62202-2025</t>
+          <t>A 602-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12069,10 +12074,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46006</v>
+        <v>46029</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12085,7 +12090,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12128,7 +12133,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 62801-2025</t>
+          <t>A 20612-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12142,10 +12147,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46008</v>
+        <v>44700</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12157,8 +12162,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>6.6</v>
+        <v>8.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12201,7 +12211,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 38723-2023</t>
+          <t>A 1279-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12215,10 +12225,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45163</v>
+        <v>46031</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12231,7 +12241,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12274,7 +12284,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 50387-2024</t>
+          <t>A 25975-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12288,10 +12298,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45600</v>
+        <v>46181</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12304,7 +12314,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>8.5</v>
+        <v>2.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12347,7 +12357,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 2512-2024</t>
+          <t>A 1261-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12361,10 +12371,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45313</v>
+        <v>46031</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12377,7 +12387,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12420,7 +12430,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 64709-2023</t>
+          <t>A 1268-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12434,10 +12444,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45281</v>
+        <v>46031</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12450,7 +12460,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12493,7 +12503,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 64710-2023</t>
+          <t>A 27274-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12507,10 +12517,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45281</v>
+        <v>46184</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12523,7 +12533,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12566,7 +12576,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 64010-2025</t>
+          <t>A 1264-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12580,10 +12590,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46021</v>
+        <v>46031</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12595,13 +12605,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>15.4</v>
+        <v>1.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12644,7 +12649,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 36730-2023</t>
+          <t>A 1273-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12658,10 +12663,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45153</v>
+        <v>46031</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12674,7 +12679,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12717,7 +12722,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 64015-2025</t>
+          <t>A 15198-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12731,10 +12736,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46021</v>
+        <v>44658</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12746,13 +12751,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12795,7 +12795,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 602-2026</t>
+          <t>A 27292-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12809,10 +12809,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46029</v>
+        <v>46184</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 1279-2026</t>
+          <t>A 1585-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12882,10 +12882,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12897,8 +12897,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12941,7 +12946,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 1261-2026</t>
+          <t>A 1589-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12955,10 +12960,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12970,8 +12975,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13014,7 +13024,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 1268-2026</t>
+          <t>A 6375-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13028,10 +13038,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46031</v>
+        <v>45699</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13044,7 +13054,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13087,7 +13097,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 16168-2023</t>
+          <t>A 6592-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13101,10 +13111,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45027</v>
+        <v>45700</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13116,13 +13126,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13165,7 +13170,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 21770-2023</t>
+          <t>A 37843-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13179,10 +13184,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45065</v>
+        <v>45160</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13195,7 +13200,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13238,7 +13243,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 36099-2024</t>
+          <t>A 6506-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13252,10 +13257,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45533</v>
+        <v>45699</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13268,7 +13273,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13311,7 +13316,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 1264-2026</t>
+          <t>A 7375-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13325,10 +13330,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46031</v>
+        <v>46059</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13341,7 +13346,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13384,7 +13389,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 1273-2026</t>
+          <t>A 28718-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13398,10 +13403,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46031</v>
+        <v>46198</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13413,8 +13418,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13457,7 +13467,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 1585-2026</t>
+          <t>A 28704-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13471,10 +13481,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46034</v>
+        <v>46198</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13535,7 +13545,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 1589-2026</t>
+          <t>A 5283-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13549,10 +13559,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46034</v>
+        <v>45331</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13564,13 +13574,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13613,7 +13618,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 38718-2023</t>
+          <t>A 8118-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13627,10 +13632,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45163</v>
+        <v>46062</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13643,7 +13648,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.2</v>
+        <v>13.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13686,7 +13691,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 15906-2024</t>
+          <t>A 38723-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13696,14 +13701,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45405</v>
+        <v>45163</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13716,7 +13721,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13759,7 +13764,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 35097-2023</t>
+          <t>A 50387-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13773,10 +13778,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45145</v>
+        <v>45600</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13789,7 +13794,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13832,7 +13837,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 25895-2026</t>
+          <t>A 2512-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13846,10 +13851,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46178</v>
+        <v>45313</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13862,7 +13867,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13905,7 +13910,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 30945-2023</t>
+          <t>A 64709-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13919,10 +13924,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45113</v>
+        <v>45281</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13935,7 +13940,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13978,7 +13983,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 30964-2023</t>
+          <t>A 64710-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13992,10 +13997,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45113</v>
+        <v>45281</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14008,7 +14013,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14051,7 +14056,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 25863-2026</t>
+          <t>A 28908-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14065,10 +14070,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46178</v>
+        <v>46199</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14081,7 +14086,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14124,7 +14129,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 7375-2026</t>
+          <t>A 36730-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14138,10 +14143,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46059</v>
+        <v>45153</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14154,7 +14159,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14197,7 +14202,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 25816-2026</t>
+          <t>A 12872-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14211,10 +14216,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46178</v>
+        <v>46092</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14227,7 +14232,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14270,7 +14275,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 8118-2026</t>
+          <t>A 12859-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14284,10 +14289,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46062</v>
+        <v>46092</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14300,7 +14305,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>13.4</v>
+        <v>0.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14343,7 +14348,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 25975-2026</t>
+          <t>A 16168-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14357,10 +14362,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46181</v>
+        <v>45027</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14372,8 +14377,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14416,7 +14426,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 27274-2026</t>
+          <t>A 21770-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14430,10 +14440,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46184</v>
+        <v>45065</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14446,7 +14456,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14489,7 +14499,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 48325-2022</t>
+          <t>A 36099-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14499,14 +14509,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44858</v>
+        <v>45533</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14518,13 +14528,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14567,7 +14572,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 27292-2026</t>
+          <t>A 38718-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14581,10 +14586,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46184</v>
+        <v>45163</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14597,7 +14602,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14640,7 +14645,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 11699-2024</t>
+          <t>A 14617-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14654,10 +14659,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45373</v>
+        <v>46101</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14670,7 +14675,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14713,7 +14718,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 11704-2024</t>
+          <t>A 16370-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14727,10 +14732,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45373</v>
+        <v>46111</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14742,8 +14747,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>0.5</v>
+        <v>6.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14786,7 +14796,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 11193-2023</t>
+          <t>A 16414-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14796,14 +14806,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44992</v>
+        <v>46111</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14815,8 +14825,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>2.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14859,7 +14874,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 12872-2026</t>
+          <t>A 15906-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14869,14 +14884,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46092</v>
+        <v>45405</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14889,7 +14904,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14932,7 +14947,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 8049-2025</t>
+          <t>A 16402-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14946,10 +14961,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45707</v>
+        <v>46111</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14961,8 +14976,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15005,7 +15025,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 12859-2026</t>
+          <t>A 16341-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15019,10 +15039,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46092</v>
+        <v>46111</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15034,8 +15054,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15078,7 +15103,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 30389-2024</t>
+          <t>A 35097-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15092,10 +15117,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45491</v>
+        <v>45145</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15108,7 +15133,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>5.6</v>
+        <v>1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15151,7 +15176,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 35380-2023</t>
+          <t>A 30945-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15165,10 +15190,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45146</v>
+        <v>45113</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15181,7 +15206,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15224,7 +15249,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 54419-2024</t>
+          <t>A 30964-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15238,10 +15263,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45617</v>
+        <v>45113</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15253,13 +15278,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>22.7</v>
+        <v>0.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15302,7 +15322,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 14617-2026</t>
+          <t>A 16259-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15316,10 +15336,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46101</v>
+        <v>46109</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15332,7 +15352,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15375,7 +15395,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 28718-2026</t>
+          <t>A 16262-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15389,10 +15409,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46198</v>
+        <v>46109</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15404,13 +15424,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15453,7 +15468,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 28704-2026</t>
+          <t>A 17950-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15467,10 +15482,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46198</v>
+        <v>46122</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15482,13 +15497,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15531,7 +15541,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 16370-2026</t>
+          <t>A 48325-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15541,14 +15551,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46111</v>
+        <v>44858</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15566,7 +15576,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>6.9</v>
+        <v>1.8</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15609,7 +15619,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 34961-2022</t>
+          <t>A 30155-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15623,10 +15633,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44796</v>
+        <v>46206</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15638,8 +15648,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15682,7 +15697,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 14185-2023</t>
+          <t>A 11699-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15696,10 +15711,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45009</v>
+        <v>45373</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15712,7 +15727,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15755,7 +15770,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 16414-2026</t>
+          <t>A 11704-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15769,10 +15784,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46111</v>
+        <v>45373</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15784,13 +15799,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>8.199999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15833,7 +15843,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 16402-2026</t>
+          <t>A 11193-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15843,14 +15853,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46111</v>
+        <v>44992</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15862,13 +15872,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15911,7 +15916,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 16341-2026</t>
+          <t>A 8049-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15925,10 +15930,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46111</v>
+        <v>45707</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15940,13 +15945,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15989,7 +15989,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 27087-2024</t>
+          <t>A 30389-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16003,10 +16003,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45471</v>
+        <v>45491</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16019,7 +16019,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.1</v>
+        <v>5.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16062,7 +16062,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 28908-2026</t>
+          <t>A 35380-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16076,10 +16076,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46199</v>
+        <v>45146</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16135,7 +16135,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 6368-2025</t>
+          <t>A 54419-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16149,10 +16149,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45699</v>
+        <v>45617</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16164,8 +16164,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>1.7</v>
+        <v>22.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16208,7 +16213,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 39190-2023</t>
+          <t>A 50358-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16218,14 +16223,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45166</v>
+        <v>45944</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16238,7 +16243,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16281,7 +16286,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 16259-2026</t>
+          <t>A 34961-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16295,10 +16300,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46109</v>
+        <v>44796</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16311,7 +16316,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16354,7 +16359,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 16262-2026</t>
+          <t>A 14185-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16368,10 +16373,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46109</v>
+        <v>45009</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16384,7 +16389,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16427,7 +16432,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 17950-2026</t>
+          <t>A 27087-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16441,10 +16446,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46122</v>
+        <v>45471</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16457,7 +16462,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16500,7 +16505,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 54590-2024</t>
+          <t>A 6368-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16514,10 +16519,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45617</v>
+        <v>45699</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16530,7 +16535,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16573,7 +16578,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 14993-2023</t>
+          <t>A 39190-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16583,14 +16588,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45015</v>
+        <v>45166</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16603,7 +16608,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16646,7 +16651,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 52469-2023</t>
+          <t>A 31447-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16660,10 +16665,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45225</v>
+        <v>46220</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16676,7 +16681,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16719,7 +16724,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 19350-2023</t>
+          <t>A 54590-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16733,10 +16738,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45049</v>
+        <v>45617</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16749,7 +16754,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16792,7 +16797,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 51041-2024</t>
+          <t>A 14993-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16806,10 +16811,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45603</v>
+        <v>45015</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16822,7 +16827,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16865,7 +16870,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 30155-2026</t>
+          <t>A 36824-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16879,10 +16884,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46206</v>
+        <v>46272</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16896,11 +16901,11 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I214" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16943,7 +16948,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 11972-2023</t>
+          <t>A 52469-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16957,10 +16962,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44994</v>
+        <v>45225</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16973,7 +16978,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17016,7 +17021,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 12332-2023</t>
+          <t>A 19350-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17030,10 +17035,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44999</v>
+        <v>45049</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17046,7 +17051,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17089,7 +17094,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 38266-2022</t>
+          <t>A 51041-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17103,10 +17108,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44812</v>
+        <v>45603</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17119,7 +17124,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17162,7 +17167,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 1323-2023</t>
+          <t>A 37482-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17176,10 +17181,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44936</v>
+        <v>46275</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17191,8 +17196,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>1</v>
+        <v>16.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17235,7 +17245,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 50358-2025</t>
+          <t>A 37473-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17249,10 +17259,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45944</v>
+        <v>46275</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17265,7 +17275,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17308,7 +17318,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 14736-2024</t>
+          <t>A 37469-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17318,14 +17328,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45397</v>
+        <v>46275</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17338,7 +17348,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17381,7 +17391,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 25729-2023</t>
+          <t>A 11972-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17395,10 +17405,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45084</v>
+        <v>44994</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17411,7 +17421,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17454,7 +17464,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 30388-2024</t>
+          <t>A 12332-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17468,10 +17478,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45491</v>
+        <v>44999</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17484,7 +17494,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17527,7 +17537,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 31447-2026</t>
+          <t>A 37991-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17541,10 +17551,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46220</v>
+        <v>46280</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17557,7 +17567,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17600,7 +17610,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 21855-2022</t>
+          <t>A 38266-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17614,10 +17624,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44709</v>
+        <v>44812</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17630,7 +17640,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17673,7 +17683,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 72603-2021</t>
+          <t>A 1323-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17687,10 +17697,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44546</v>
+        <v>44936</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17703,7 +17713,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17746,7 +17756,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 14750-2023</t>
+          <t>A 37494-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17760,10 +17770,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45014</v>
+        <v>46275</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17776,7 +17786,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17819,7 +17829,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 47600-2023</t>
+          <t>A 14736-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17829,14 +17839,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45203</v>
+        <v>45397</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17849,7 +17859,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17892,7 +17902,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 21357-2025</t>
+          <t>A 25729-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17906,10 +17916,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45782</v>
+        <v>45084</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17922,7 +17932,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17965,7 +17975,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 21530-2025</t>
+          <t>A 30388-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17979,10 +17989,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45782</v>
+        <v>45491</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17995,7 +18005,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18038,7 +18048,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 36824-2026</t>
+          <t>A 21855-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18052,10 +18062,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46272</v>
+        <v>44709</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18067,13 +18077,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I230" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18116,7 +18121,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 37482-2026</t>
+          <t>A 72603-2021</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18130,10 +18135,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46275</v>
+        <v>44546</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18145,13 +18150,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I231" t="n">
-        <v>16.5</v>
+        <v>1.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 37473-2026</t>
+          <t>A 14750-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18208,10 +18208,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46275</v>
+        <v>45014</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18267,7 +18267,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 37469-2026</t>
+          <t>A 47600-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18281,10 +18281,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46275</v>
+        <v>45203</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18340,7 +18340,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 3554-2025</t>
+          <t>A 21357-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18354,10 +18354,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45680</v>
+        <v>45782</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18413,7 +18413,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 50818-2023</t>
+          <t>A 21530-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18427,10 +18427,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45217</v>
+        <v>45782</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18486,7 +18486,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 37991-2026</t>
+          <t>A 3554-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18500,10 +18500,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46280</v>
+        <v>45680</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18559,7 +18559,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 21336-2025</t>
+          <t>A 50818-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18573,10 +18573,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45782</v>
+        <v>45217</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18632,7 +18632,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 37494-2026</t>
+          <t>A 21336-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18646,10 +18646,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46275</v>
+        <v>45782</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18722,7 +18722,7 @@
         <v>45831</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>45838</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>45838</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>45376</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44879</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>

--- a/Översikt ÖDESHÖG.xlsx
+++ b/Översikt ÖDESHÖG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE243"/>
+  <dimension ref="A1:AE242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45805</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45723</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44698</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>44664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 56797-2023</t>
+          <t>A 35443-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1058,14 +1058,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45244</v>
+        <v>44798</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1118,149 +1118,149 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Axveronika
+Bivråk</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 35443-2022 artfynd.xlsx", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 35443-2022 karta.png", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 35443-2022 georefererad karta.tif", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 35443-2022 FSC-klagomål.docx", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 35443-2022 FSC-klagomål mail.docx", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 35443-2022 tillsynsbegäran.docx", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 35443-2022 tillsynsbegäran mail.docx", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/fåglar/A 35443-2022 prioriterade fågelarter.docx", "A 35443-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 56797-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45244</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Jungfrulin
 Svinrot</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 56797-2023 artfynd.xlsx", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 56797-2023 karta.png", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 56797-2023 georefererad karta.tif", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 56797-2023 FSC-klagomål.docx", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 56797-2023 FSC-klagomål mail.docx", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 56797-2023 tillsynsbegäran.docx", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 56797-2023 tillsynsbegäran mail.docx", "A 56797-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 35443-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44798</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Axveronika
-Bivråk</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 35443-2022 artfynd.xlsx", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 35443-2022 karta.png", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 35443-2022 georefererad karta.tif", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 35443-2022 FSC-klagomål.docx", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 35443-2022 FSC-klagomål mail.docx", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 35443-2022 tillsynsbegäran.docx", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 35443-2022 tillsynsbegäran mail.docx", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/fåglar/A 35443-2022 prioriterade fågelarter.docx", "A 35443-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>44538</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 58551-2023</t>
+          <t>A 62988-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45251</v>
+        <v>45272</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1503,24 +1503,29 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
@@ -1528,10 +1533,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1544,476 +1549,476 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 62988-2023 artfynd.xlsx", "A 62988-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 62988-2023 karta.png", "A 62988-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 62988-2023 georefererad karta.tif", "A 62988-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 62988-2023 FSC-klagomål.docx", "A 62988-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 62988-2023 FSC-klagomål mail.docx", "A 62988-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 62988-2023 tillsynsbegäran.docx", "A 62988-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 62988-2023 tillsynsbegäran mail.docx", "A 62988-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 15437-2025</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 15437-2025 artfynd.xlsx", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 15437-2025 karta.png", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 15437-2025 georefererad karta.tif", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="Z11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/knärot/A 15437-2025 karta knärot.png", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 15437-2025 FSC-klagomål.docx", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 15437-2025 FSC-klagomål mail.docx", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 15437-2025 tillsynsbegäran.docx", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 15437-2025 tillsynsbegäran mail.docx", "A 15437-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 4772-2022</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44592</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 4772-2022 artfynd.xlsx", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 4772-2022 karta.png", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 4772-2022 georefererad karta.tif", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 4772-2022 FSC-klagomål.docx", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 4772-2022 FSC-klagomål mail.docx", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 4772-2022 tillsynsbegäran.docx", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 4772-2022 tillsynsbegäran mail.docx", "A 4772-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 58052-2021</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>44487</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58052-2021 artfynd.xlsx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58052-2021 karta.png", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58052-2021 georefererad karta.tif", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58052-2021 FSC-klagomål.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58052-2021 FSC-klagomål mail.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58052-2021 tillsynsbegäran.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58052-2021 tillsynsbegäran mail.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 58551-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45251</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58551-2023 artfynd.xlsx", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58551-2023 karta.png", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58551-2023 georefererad karta.tif", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58551-2023 FSC-klagomål.docx", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58551-2023 FSC-klagomål mail.docx", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58551-2023 tillsynsbegäran.docx", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58551-2023 tillsynsbegäran mail.docx", "A 58551-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 50774-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Mörk dunört</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 50774-2023 artfynd.xlsx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 50774-2023 karta.png", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 50774-2023 georefererad karta.tif", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 50774-2023 FSC-klagomål.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 50774-2023 FSC-klagomål mail.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 50774-2023 tillsynsbegäran.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 50774-2023 tillsynsbegäran mail.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 15437-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45747</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 15437-2025 artfynd.xlsx", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 15437-2025 karta.png", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 15437-2025 georefererad karta.tif", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/knärot/A 15437-2025 karta knärot.png", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 15437-2025 FSC-klagomål.docx", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 15437-2025 FSC-klagomål mail.docx", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 15437-2025 tillsynsbegäran.docx", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 15437-2025 tillsynsbegäran mail.docx", "A 15437-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 32713-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45516</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Kristinspindling</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32713-2024 artfynd.xlsx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32713-2024 karta.png", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32713-2024 georefererad karta.tif", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32713-2024 FSC-klagomål.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32713-2024 FSC-klagomål mail.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32713-2024 tillsynsbegäran.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32713-2024 tillsynsbegäran mail.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 62988-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>19</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 62988-2023 artfynd.xlsx", "A 62988-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 62988-2023 karta.png", "A 62988-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 62988-2023 georefererad karta.tif", "A 62988-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 62988-2023 FSC-klagomål.docx", "A 62988-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 62988-2023 FSC-klagomål mail.docx", "A 62988-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 62988-2023 tillsynsbegäran.docx", "A 62988-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 62988-2023 tillsynsbegäran mail.docx", "A 62988-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 38720-2023</t>
+          <t>A 32776-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2023,14 +2028,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45163</v>
+        <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2043,20 +2048,20 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
@@ -2067,10 +2072,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2083,35 +2088,35 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Hässleklocka</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 38720-2023 artfynd.xlsx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32776-2025 artfynd.xlsx", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 38720-2023 karta.png", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32776-2025 karta.png", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 38720-2023 georefererad karta.tif", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32776-2025 georefererad karta.tif", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 38720-2023 FSC-klagomål.docx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32776-2025 FSC-klagomål.docx", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 38720-2023 FSC-klagomål mail.docx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32776-2025 FSC-klagomål mail.docx", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 38720-2023 tillsynsbegäran.docx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32776-2025 tillsynsbegäran.docx", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 38720-2023 tillsynsbegäran mail.docx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32776-2025 tillsynsbegäran mail.docx", "A 32776-2025")</f>
         <v/>
       </c>
     </row>
@@ -2135,7 +2140,7 @@
         <v>45243</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2223,7 +2228,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 58052-2021</t>
+          <t>A 50774-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2237,10 +2242,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44487</v>
+        <v>45210</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2252,23 +2257,18 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>4.3</v>
+        <v>9.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2298,42 +2298,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mörk dunört</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58052-2021 artfynd.xlsx", "A 58052-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 50774-2023 artfynd.xlsx", "A 50774-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58052-2021 karta.png", "A 58052-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 50774-2023 karta.png", "A 50774-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58052-2021 georefererad karta.tif", "A 58052-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 50774-2023 georefererad karta.tif", "A 50774-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58052-2021 FSC-klagomål.docx", "A 58052-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 50774-2023 FSC-klagomål.docx", "A 50774-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58052-2021 FSC-klagomål mail.docx", "A 58052-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 50774-2023 FSC-klagomål mail.docx", "A 50774-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58052-2021 tillsynsbegäran.docx", "A 58052-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 50774-2023 tillsynsbegäran.docx", "A 50774-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58052-2021 tillsynsbegäran mail.docx", "A 58052-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 50774-2023 tillsynsbegäran mail.docx", "A 50774-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4772-2022</t>
+          <t>A 38720-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44592</v>
+        <v>45163</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2387,10 +2387,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2399,46 +2399,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Hässleklocka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 4772-2022 artfynd.xlsx", "A 4772-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 38720-2023 artfynd.xlsx", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 4772-2022 karta.png", "A 4772-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 38720-2023 karta.png", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 4772-2022 georefererad karta.tif", "A 4772-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 38720-2023 georefererad karta.tif", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 4772-2022 FSC-klagomål.docx", "A 4772-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 38720-2023 FSC-klagomål.docx", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 4772-2022 FSC-klagomål mail.docx", "A 4772-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 38720-2023 FSC-klagomål mail.docx", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 4772-2022 tillsynsbegäran.docx", "A 4772-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 38720-2023 tillsynsbegäran.docx", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 4772-2022 tillsynsbegäran mail.docx", "A 4772-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 38720-2023 tillsynsbegäran mail.docx", "A 38720-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32776-2025</t>
+          <t>A 32713-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2448,14 +2448,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45839</v>
+        <v>45516</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>6.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2504,39 +2504,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Kristinspindling</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32776-2025 artfynd.xlsx", "A 32776-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32713-2024 artfynd.xlsx", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32776-2025 karta.png", "A 32776-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32713-2024 karta.png", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32776-2025 georefererad karta.tif", "A 32776-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32713-2024 georefererad karta.tif", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32776-2025 FSC-klagomål.docx", "A 32776-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32713-2024 FSC-klagomål.docx", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32776-2025 FSC-klagomål mail.docx", "A 32776-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32713-2024 FSC-klagomål mail.docx", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32776-2025 tillsynsbegäran.docx", "A 32776-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32713-2024 tillsynsbegäran.docx", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32776-2025 tillsynsbegäran mail.docx", "A 32776-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32713-2024 tillsynsbegäran mail.docx", "A 32713-2024")</f>
         <v/>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
         <v>44509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44538</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>44614</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>44803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>44510</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44504</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 51771-2021</t>
+          <t>A 65821-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44462</v>
+        <v>44517</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 65821-2021</t>
+          <t>A 16152-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44517</v>
+        <v>44666</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3351,7 +3351,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 16152-2022</t>
+          <t>A 3554-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44666</v>
+        <v>45680</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3424,7 +3424,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 29967-2022</t>
+          <t>A 34979-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44756</v>
+        <v>44796</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3497,7 +3497,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 34979-2022</t>
+          <t>A 29967-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44796</v>
+        <v>44756</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3570,7 +3570,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 6705-2024</t>
+          <t>A 39032-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45342</v>
+        <v>45163</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8.300000000000001</v>
+        <v>5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 15790-2025</t>
+          <t>A 14993-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45748</v>
+        <v>45015</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 5819-2024</t>
+          <t>A 11280-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3731,14 +3731,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45335</v>
+        <v>45726</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3750,13 +3750,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3799,7 +3794,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 35661-2024</t>
+          <t>A 8049-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3813,10 +3808,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45532</v>
+        <v>45707</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3829,7 +3824,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3872,7 +3867,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 36114-2022</t>
+          <t>A 38152-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3886,10 +3881,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44803</v>
+        <v>45161</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3902,7 +3897,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3945,7 +3940,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 3198-2024</t>
+          <t>A 8515-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3959,10 +3954,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45316</v>
+        <v>44613</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3975,7 +3970,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4018,7 +4013,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22088-2023</t>
+          <t>A 36114-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4032,10 +4027,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45069</v>
+        <v>44803</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4048,7 +4043,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4091,7 +4086,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8256-2023</t>
+          <t>A 47600-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4101,14 +4096,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44974</v>
+        <v>45203</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4121,7 +4116,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4164,7 +4159,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 26949-2023</t>
+          <t>A 38723-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4178,10 +4173,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45093</v>
+        <v>45163</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4194,7 +4189,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4237,7 +4232,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15813-2022</t>
+          <t>A 3130-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4247,14 +4242,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44664</v>
+        <v>45678</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4268,11 +4263,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>18.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4315,7 +4310,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38152-2023</t>
+          <t>A 50818-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4329,10 +4324,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45161</v>
+        <v>45217</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4345,7 +4340,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4388,7 +4383,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 44069-2023</t>
+          <t>A 16128-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4402,10 +4397,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45188</v>
+        <v>45750</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4417,8 +4412,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1578-2023</t>
+          <t>A 55971-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44937</v>
+        <v>45240</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 56841-2022</t>
+          <t>A 30945-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44894</v>
+        <v>45113</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11280-2025</t>
+          <t>A 15906-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4617,14 +4617,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45726</v>
+        <v>45405</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 15909-2024</t>
+          <t>A 16164-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4690,14 +4690,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45405</v>
+        <v>45027</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4709,8 +4709,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4753,7 +4758,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38259-2023</t>
+          <t>A 30964-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4767,10 +4772,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45161</v>
+        <v>45113</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4783,7 +4788,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4826,7 +4831,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 39032-2023</t>
+          <t>A 21770-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4840,10 +4845,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45163</v>
+        <v>45065</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4855,13 +4860,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4904,7 +4904,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 39920-2024</t>
+          <t>A 19351-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45553</v>
+        <v>45049</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4977,7 +4977,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45973-2024</t>
+          <t>A 21336-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45580</v>
+        <v>45782</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9448-2023</t>
+          <t>A 38266-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44981</v>
+        <v>44812</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54226-2021</t>
+          <t>A 21771-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44470</v>
+        <v>45065</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5196,7 +5196,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 36075-2023</t>
+          <t>A 41730-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5210,10 +5210,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45149</v>
+        <v>45902</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5269,7 +5269,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 1674-2023</t>
+          <t>A 35079-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44938</v>
+        <v>45145</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5342,7 +5342,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35079-2023</t>
+          <t>A 45973-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5356,10 +5356,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45145</v>
+        <v>45580</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 6421-2025</t>
+          <t>A 30389-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45699</v>
+        <v>45491</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>5.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5488,7 +5488,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 6456-2025</t>
+          <t>A 35229-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45699</v>
+        <v>45145</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5561,7 +5561,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 17618-2024</t>
+          <t>A 1578-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45416</v>
+        <v>44937</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 47993-2024</t>
+          <t>A 5819-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5644,14 +5644,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45589</v>
+        <v>45335</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5663,8 +5663,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5707,7 +5712,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 5513-2025</t>
+          <t>A 54226-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5721,10 +5726,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45693</v>
+        <v>44470</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5737,7 +5742,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5780,7 +5785,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 13129-2023</t>
+          <t>A 48325-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5790,14 +5795,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45002</v>
+        <v>44858</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5809,8 +5814,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5853,7 +5863,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 46528-2024</t>
+          <t>A 47993-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5867,10 +5877,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45582</v>
+        <v>45589</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5926,7 +5936,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 6164-2024</t>
+          <t>A 64802-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5936,14 +5946,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45337</v>
+        <v>44512</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5956,7 +5966,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5999,7 +6009,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 14156-2023</t>
+          <t>A 61880-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6013,10 +6023,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45009</v>
+        <v>44502</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6029,7 +6039,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6072,7 +6082,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 35411-2023</t>
+          <t>A 6164-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6086,10 +6096,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45146</v>
+        <v>45337</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6102,7 +6112,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6145,7 +6155,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16270-2024</t>
+          <t>A 6705-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6159,10 +6169,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45407</v>
+        <v>45342</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6174,8 +6184,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6218,7 +6233,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 20244-2022</t>
+          <t>A 35661-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6232,10 +6247,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44698</v>
+        <v>45532</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6247,13 +6262,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>9.5</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6296,7 +6306,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 6557-2025</t>
+          <t>A 56841-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6310,10 +6320,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45699</v>
+        <v>44894</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6326,7 +6336,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6369,7 +6379,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32378-2024</t>
+          <t>A 1323-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6383,10 +6393,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45512</v>
+        <v>44936</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6399,7 +6409,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6442,7 +6452,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19351-2023</t>
+          <t>A 32335-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6456,10 +6466,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45049</v>
+        <v>45512</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6472,7 +6482,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6515,7 +6525,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32335-2024</t>
+          <t>A 38212-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6529,10 +6539,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45512</v>
+        <v>45161</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6545,7 +6555,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6588,7 +6598,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 8515-2022</t>
+          <t>A 27087-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6602,10 +6612,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44613</v>
+        <v>45471</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6661,7 +6671,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61880-2021</t>
+          <t>A 46059-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6675,10 +6685,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44502</v>
+        <v>45924</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6691,7 +6701,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6734,7 +6744,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 33375-2024</t>
+          <t>A 39920-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6748,10 +6758,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45519</v>
+        <v>45553</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6763,13 +6773,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6812,7 +6817,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39027-2023</t>
+          <t>A 30388-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6826,10 +6831,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45163</v>
+        <v>45491</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6841,13 +6846,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6890,7 +6890,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 43263-2023</t>
+          <t>A 46536-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6900,14 +6900,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45183</v>
+        <v>45582</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6963,7 +6963,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 46536-2024</t>
+          <t>A 3149-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6977,10 +6977,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45582</v>
+        <v>45316</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 39024-2023</t>
+          <t>A 46788-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45163</v>
+        <v>45926</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7065,13 +7065,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7114,7 +7109,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 41730-2025</t>
+          <t>A 46778-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7128,10 +7123,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45902</v>
+        <v>45926</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7144,7 +7139,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7187,7 +7182,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 5350-2025</t>
+          <t>A 47597-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7201,10 +7196,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45692</v>
+        <v>45203</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7217,7 +7212,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7260,7 +7255,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 38212-2023</t>
+          <t>A 4678-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7274,10 +7269,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45161</v>
+        <v>45328</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7290,7 +7285,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7333,7 +7328,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 3130-2025</t>
+          <t>A 35095-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7347,10 +7342,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45678</v>
+        <v>45145</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7362,13 +7357,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>18.6</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7411,7 +7401,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 15907-2024</t>
+          <t>A 46999-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7421,14 +7411,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45405</v>
+        <v>45929</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7441,7 +7431,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7484,7 +7474,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 15915-2024</t>
+          <t>A 15907-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7501,7 +7491,7 @@
         <v>45405</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7514,7 +7504,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7557,7 +7547,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 20232-2022</t>
+          <t>A 15915-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7567,14 +7557,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44698</v>
+        <v>45405</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7586,13 +7576,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7635,7 +7620,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 46059-2025</t>
+          <t>A 1749-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7649,10 +7634,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45924</v>
+        <v>45671</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7665,7 +7650,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7708,7 +7693,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 46778-2025</t>
+          <t>A 48063-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7722,10 +7707,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45926</v>
+        <v>45932</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7738,7 +7723,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7781,7 +7766,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 46999-2025</t>
+          <t>A 47648-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7795,10 +7780,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7811,7 +7796,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7854,7 +7839,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 46788-2025</t>
+          <t>A 15909-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7864,14 +7849,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45926</v>
+        <v>45405</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7884,7 +7869,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7927,7 +7912,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 47648-2025</t>
+          <t>A 48575-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7941,10 +7926,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45931</v>
+        <v>45936</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7957,7 +7942,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8000,7 +7985,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 48063-2025</t>
+          <t>A 6375-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8014,10 +7999,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45932</v>
+        <v>45699</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8030,7 +8015,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8073,7 +8058,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 48611-2025</t>
+          <t>A 17618-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8087,10 +8072,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45936</v>
+        <v>45416</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8103,7 +8088,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8146,7 +8131,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 48614-2025</t>
+          <t>A 48611-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8163,7 +8148,7 @@
         <v>45936</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8176,7 +8161,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8219,7 +8204,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48575-2025</t>
+          <t>A 48614-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8236,7 +8221,7 @@
         <v>45936</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8249,7 +8234,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8292,7 +8277,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 165-2026</t>
+          <t>A 13129-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8306,10 +8291,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46024</v>
+        <v>45002</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8322,7 +8307,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8365,7 +8350,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 63074-2025</t>
+          <t>A 5283-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8379,10 +8364,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46009</v>
+        <v>45331</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8394,13 +8379,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>8.699999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8443,7 +8423,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 8063-2025</t>
+          <t>A 14750-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8457,10 +8437,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45707</v>
+        <v>45014</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8473,7 +8453,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8516,7 +8496,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 32715-2024</t>
+          <t>A 32378-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8530,10 +8510,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45516</v>
+        <v>45512</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8546,7 +8526,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8589,7 +8569,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 6465-2025</t>
+          <t>A 50416-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8603,10 +8583,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45699</v>
+        <v>45944</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8619,7 +8599,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8662,7 +8642,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 1749-2025</t>
+          <t>A 14156-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8676,10 +8656,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45671</v>
+        <v>45009</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8692,7 +8672,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8735,7 +8715,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 63115-2025</t>
+          <t>A 51171-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8749,10 +8729,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46009</v>
+        <v>45947</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8765,7 +8745,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8808,7 +8788,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 50416-2025</t>
+          <t>A 51328-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8822,10 +8802,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45944</v>
+        <v>45950</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8838,7 +8818,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8881,7 +8861,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 51171-2025</t>
+          <t>A 46528-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8895,10 +8875,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45947</v>
+        <v>45582</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8911,7 +8891,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8954,7 +8934,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 51328-2025</t>
+          <t>A 8256-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8964,14 +8944,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45950</v>
+        <v>44974</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8984,7 +8964,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9027,7 +9007,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 17126-2024</t>
+          <t>A 51180-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9041,10 +9021,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45412</v>
+        <v>45603</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9057,7 +9037,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9100,7 +9080,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 4678-2024</t>
+          <t>A 22088-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9114,10 +9094,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45328</v>
+        <v>45069</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9130,7 +9110,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9173,7 +9153,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 20720-2025</t>
+          <t>A 36099-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9187,10 +9167,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45776</v>
+        <v>45533</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9203,7 +9183,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9246,7 +9226,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 55901-2025</t>
+          <t>A 39190-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9256,14 +9236,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45973</v>
+        <v>45166</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9276,7 +9256,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9319,7 +9299,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 55906-2025</t>
+          <t>A 14736-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9329,14 +9309,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45973</v>
+        <v>45397</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9349,7 +9329,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9392,7 +9372,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 21771-2023</t>
+          <t>A 16168-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9406,10 +9386,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45065</v>
+        <v>45027</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9421,8 +9401,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9465,7 +9450,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 55908-2025</t>
+          <t>A 38718-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9479,10 +9464,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45973</v>
+        <v>45163</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9495,7 +9480,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9538,7 +9523,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 61011-2024</t>
+          <t>A 2512-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9548,14 +9533,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45645</v>
+        <v>45313</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9568,7 +9553,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9611,7 +9596,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 1337-2026</t>
+          <t>A 20232-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9625,10 +9610,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46031</v>
+        <v>44698</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9640,8 +9625,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9684,7 +9674,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 32464-2025</t>
+          <t>A 14185-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9698,10 +9688,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45838</v>
+        <v>45009</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9714,7 +9704,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9757,7 +9747,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 64802-2021</t>
+          <t>A 51178-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9767,14 +9757,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44512</v>
+        <v>45603</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9787,7 +9777,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9830,7 +9820,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 8067-2025</t>
+          <t>A 20720-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9844,10 +9834,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45707</v>
+        <v>45776</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9860,7 +9850,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9903,7 +9893,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 16128-2025</t>
+          <t>A 14166-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9917,10 +9907,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45750</v>
+        <v>45009</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9932,13 +9922,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9981,7 +9966,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 3149-2024</t>
+          <t>A 19350-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9995,10 +9980,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45316</v>
+        <v>45049</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10011,7 +9996,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10054,7 +10039,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 51180-2024</t>
+          <t>A 55908-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10068,10 +10053,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45603</v>
+        <v>45973</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10084,7 +10069,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10127,7 +10112,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 35229-2023</t>
+          <t>A 35380-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10141,10 +10126,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45145</v>
+        <v>45146</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10157,7 +10142,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10200,7 +10185,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 51178-2024</t>
+          <t>A 55901-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10214,10 +10199,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45603</v>
+        <v>45973</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10230,7 +10215,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10273,7 +10258,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 61786-2025</t>
+          <t>A 55906-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10287,10 +10272,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46002</v>
+        <v>45973</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10303,7 +10288,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10346,7 +10331,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 19157-2023</t>
+          <t>A 6592-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10360,10 +10345,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45048</v>
+        <v>45700</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10376,7 +10361,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10419,7 +10404,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 61798-2025</t>
+          <t>A 11972-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10433,10 +10418,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46002</v>
+        <v>44994</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10448,13 +10433,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10497,7 +10477,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 61800-2025</t>
+          <t>A 43263-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10507,14 +10487,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46002</v>
+        <v>45183</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10527,7 +10507,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10570,7 +10550,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 61801-2025</t>
+          <t>A 20244-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10584,10 +10564,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46002</v>
+        <v>44698</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10599,8 +10579,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>3.6</v>
+        <v>9.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10643,7 +10628,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 61972-2025</t>
+          <t>A 20612-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10657,10 +10642,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46003</v>
+        <v>44700</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10678,7 +10663,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.5</v>
+        <v>8.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10721,7 +10706,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 61470-2025</t>
+          <t>A 54419-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10735,10 +10720,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46001</v>
+        <v>45617</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10756,7 +10741,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>8</v>
+        <v>22.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10799,7 +10784,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 61629-2025</t>
+          <t>A 6421-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10813,10 +10798,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46002</v>
+        <v>45699</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10829,7 +10814,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10872,7 +10857,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 55971-2023</t>
+          <t>A 52469-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10886,10 +10871,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45240</v>
+        <v>45225</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10902,7 +10887,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10945,7 +10930,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 16164-2023</t>
+          <t>A 8063-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10959,10 +10944,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45027</v>
+        <v>45707</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10974,13 +10959,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11023,7 +11003,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 62482-2025</t>
+          <t>A 30600-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11037,10 +11017,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46007</v>
+        <v>45831</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11053,7 +11033,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11096,7 +11076,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 39024-2023</t>
+          <t>A 15790-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11110,10 +11090,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45163</v>
+        <v>45748</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11125,13 +11105,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11174,7 +11149,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 62202-2025</t>
+          <t>A 602-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11188,10 +11163,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46006</v>
+        <v>46029</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11204,7 +11179,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11247,7 +11222,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 62801-2025</t>
+          <t>A 1589-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11261,10 +11236,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46008</v>
+        <v>46034</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11276,8 +11251,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>6.6</v>
+        <v>3.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11320,7 +11300,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 25895-2026</t>
+          <t>A 61801-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11334,10 +11314,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46178</v>
+        <v>46002</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11350,7 +11330,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11393,7 +11373,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 47597-2023</t>
+          <t>A 61470-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11407,10 +11387,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45203</v>
+        <v>46001</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11422,8 +11402,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11466,7 +11451,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 25863-2026</t>
+          <t>A 1279-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11480,10 +11465,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46178</v>
+        <v>46031</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11496,7 +11481,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11539,7 +11524,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 25816-2026</t>
+          <t>A 1264-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11553,10 +11538,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46178</v>
+        <v>46031</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11569,7 +11554,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11612,7 +11597,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 14166-2023</t>
+          <t>A 61798-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11626,10 +11611,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45009</v>
+        <v>46002</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11641,8 +11626,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11685,7 +11675,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 64010-2025</t>
+          <t>A 61800-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11699,10 +11689,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46021</v>
+        <v>46002</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11714,13 +11704,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>15.4</v>
+        <v>2.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11763,7 +11748,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 64015-2025</t>
+          <t>A 61629-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11777,10 +11762,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46021</v>
+        <v>46002</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11792,13 +11777,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11841,7 +11821,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 15344-2025</t>
+          <t>A 37843-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11855,10 +11835,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45747</v>
+        <v>45160</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11871,7 +11851,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11914,7 +11894,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 10335-2022</t>
+          <t>A 1585-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11928,10 +11908,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44623</v>
+        <v>46034</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11943,8 +11923,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11987,7 +11972,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 35095-2023</t>
+          <t>A 61786-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12001,10 +11986,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45145</v>
+        <v>46002</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12017,7 +12002,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12060,7 +12045,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 602-2026</t>
+          <t>A 1273-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12074,10 +12059,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12090,7 +12075,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12133,7 +12118,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 20612-2022</t>
+          <t>A 32476-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12147,10 +12132,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44700</v>
+        <v>45838</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12162,13 +12147,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>8.9</v>
+        <v>0.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12211,7 +12191,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 1279-2026</t>
+          <t>A 1261-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12228,7 +12208,7 @@
         <v>46031</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12241,7 +12221,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12284,7 +12264,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 25975-2026</t>
+          <t>A 1268-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12298,10 +12278,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46181</v>
+        <v>46031</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12314,7 +12294,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12357,7 +12337,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 1261-2026</t>
+          <t>A 62202-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12371,10 +12351,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46031</v>
+        <v>46006</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12387,7 +12367,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12430,7 +12410,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 1268-2026</t>
+          <t>A 6465-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12444,10 +12424,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46031</v>
+        <v>45699</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12460,7 +12440,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12503,7 +12483,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 27274-2026</t>
+          <t>A 61972-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12517,10 +12497,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46184</v>
+        <v>46003</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12532,8 +12512,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12576,7 +12561,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 1264-2026</t>
+          <t>A 32466-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12590,10 +12575,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46031</v>
+        <v>45838</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12606,7 +12591,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12649,7 +12634,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 1273-2026</t>
+          <t>A 62801-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12663,10 +12648,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46031</v>
+        <v>46008</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12679,7 +12664,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12722,7 +12707,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 15198-2022</t>
+          <t>A 62482-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12736,10 +12721,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44658</v>
+        <v>46007</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12752,7 +12737,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.3</v>
+        <v>6.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12795,7 +12780,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 27292-2026</t>
+          <t>A 1674-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12809,10 +12794,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46184</v>
+        <v>44938</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12825,7 +12810,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12868,7 +12853,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 1585-2026</t>
+          <t>A 34961-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12882,10 +12867,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46034</v>
+        <v>44796</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12897,13 +12882,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12946,7 +12926,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 1589-2026</t>
+          <t>A 19157-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12960,10 +12940,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46034</v>
+        <v>45048</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12975,13 +12955,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13024,7 +12999,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 6375-2025</t>
+          <t>A 64015-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13038,10 +13013,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45699</v>
+        <v>46021</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13053,8 +13028,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13097,7 +13077,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 6592-2025</t>
+          <t>A 64010-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13111,10 +13091,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45700</v>
+        <v>46021</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13126,8 +13106,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>1.1</v>
+        <v>15.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13170,7 +13155,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 37843-2023</t>
+          <t>A 39024-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13184,10 +13169,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45160</v>
+        <v>45163</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13199,8 +13184,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13243,7 +13233,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 6506-2025</t>
+          <t>A 7375-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13257,10 +13247,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45699</v>
+        <v>46059</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13273,7 +13263,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13316,7 +13306,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 7375-2026</t>
+          <t>A 37494-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13330,10 +13320,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46059</v>
+        <v>46275</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13346,7 +13336,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13389,7 +13379,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 28718-2026</t>
+          <t>A 8118-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13403,10 +13393,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46198</v>
+        <v>46062</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13418,13 +13408,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>2</v>
+        <v>13.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13467,7 +13452,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 28704-2026</t>
+          <t>A 17126-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13481,10 +13466,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46198</v>
+        <v>45412</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13496,13 +13481,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13545,7 +13525,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 5283-2024</t>
+          <t>A 11193-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13555,14 +13535,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45331</v>
+        <v>44992</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13575,7 +13555,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13618,7 +13598,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 8118-2026</t>
+          <t>A 12859-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13632,10 +13612,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46062</v>
+        <v>46092</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13648,7 +13628,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>13.4</v>
+        <v>0.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13691,7 +13671,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 38723-2023</t>
+          <t>A 12872-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13705,10 +13685,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45163</v>
+        <v>46092</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13721,7 +13701,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13764,7 +13744,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 50387-2024</t>
+          <t>A 26949-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13778,10 +13758,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45600</v>
+        <v>45093</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13794,7 +13774,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>8.5</v>
+        <v>1.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13837,7 +13817,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 2512-2024</t>
+          <t>A 14617-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13851,10 +13831,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45313</v>
+        <v>46101</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13867,7 +13847,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13910,7 +13890,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 64709-2023</t>
+          <t>A 6506-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13924,10 +13904,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45281</v>
+        <v>45699</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13940,7 +13920,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13983,7 +13963,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 64710-2023</t>
+          <t>A 12332-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13997,10 +13977,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45281</v>
+        <v>44999</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14013,7 +13993,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14056,7 +14036,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 28908-2026</t>
+          <t>A 36075-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14070,10 +14050,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46199</v>
+        <v>45149</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14086,7 +14066,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14129,7 +14109,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 36730-2023</t>
+          <t>A 16341-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14143,10 +14123,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45153</v>
+        <v>46111</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14158,8 +14138,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14202,7 +14187,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 12872-2026</t>
+          <t>A 16402-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14216,10 +14201,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46092</v>
+        <v>46111</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14231,8 +14216,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14275,7 +14265,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 12859-2026</t>
+          <t>A 16414-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14289,10 +14279,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46092</v>
+        <v>46111</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14304,8 +14294,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>0.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14348,7 +14343,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 16168-2023</t>
+          <t>A 16370-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14362,10 +14357,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45027</v>
+        <v>46111</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14383,7 +14378,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14426,7 +14421,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 21770-2023</t>
+          <t>A 15198-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14440,10 +14435,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45065</v>
+        <v>44658</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14456,7 +14451,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14499,7 +14494,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 36099-2024</t>
+          <t>A 6456-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14513,10 +14508,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45533</v>
+        <v>45699</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14529,7 +14524,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14572,7 +14567,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 38718-2023</t>
+          <t>A 21855-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14586,10 +14581,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45163</v>
+        <v>44709</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14602,7 +14597,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14645,7 +14640,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 14617-2026</t>
+          <t>A 72603-2021</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14659,10 +14654,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46101</v>
+        <v>44546</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14675,7 +14670,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14718,7 +14713,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 16370-2026</t>
+          <t>A 9448-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14732,10 +14727,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46111</v>
+        <v>44981</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14747,13 +14742,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>6.9</v>
+        <v>1.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14796,7 +14786,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 16414-2026</t>
+          <t>A 64709-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14810,10 +14800,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46111</v>
+        <v>45281</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14825,13 +14815,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>8.199999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14874,7 +14859,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 15906-2024</t>
+          <t>A 64710-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14884,14 +14869,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45405</v>
+        <v>45281</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14904,7 +14889,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14947,7 +14932,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 16402-2026</t>
+          <t>A 35097-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14961,10 +14946,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46111</v>
+        <v>45145</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14976,13 +14961,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15025,7 +15005,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 16341-2026</t>
+          <t>A 35411-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15039,10 +15019,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46111</v>
+        <v>45146</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15054,13 +15034,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15103,7 +15078,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 35097-2023</t>
+          <t>A 16259-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15117,10 +15092,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45145</v>
+        <v>46109</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15133,7 +15108,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15176,7 +15151,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 30945-2023</t>
+          <t>A 16262-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15190,10 +15165,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45113</v>
+        <v>46109</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15206,7 +15181,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15249,7 +15224,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 30964-2023</t>
+          <t>A 36730-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15263,10 +15238,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45113</v>
+        <v>45153</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15279,7 +15254,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15322,7 +15297,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 16259-2026</t>
+          <t>A 17950-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15336,10 +15311,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46109</v>
+        <v>46122</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15352,7 +15327,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15395,7 +15370,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 16262-2026</t>
+          <t>A 25729-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15409,10 +15384,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46109</v>
+        <v>45084</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15425,7 +15400,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15468,7 +15443,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 17950-2026</t>
+          <t>A 11699-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15482,10 +15457,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46122</v>
+        <v>45373</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15498,7 +15473,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15541,7 +15516,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 48325-2022</t>
+          <t>A 11704-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15551,14 +15526,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44858</v>
+        <v>45373</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15570,13 +15545,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15619,7 +15589,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 30155-2026</t>
+          <t>A 54590-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15633,10 +15603,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46206</v>
+        <v>45617</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15648,13 +15618,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15697,7 +15662,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 11699-2024</t>
+          <t>A 39027-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15711,10 +15676,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45373</v>
+        <v>45163</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15726,8 +15691,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15770,7 +15740,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 11704-2024</t>
+          <t>A 10335-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15784,10 +15754,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45373</v>
+        <v>44623</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15800,7 +15770,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15843,7 +15813,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 11193-2023</t>
+          <t>A 39024-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15853,14 +15823,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44992</v>
+        <v>45163</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15872,8 +15842,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15916,7 +15891,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 8049-2025</t>
+          <t>A 33375-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15930,10 +15905,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45707</v>
+        <v>45519</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15945,8 +15920,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15989,7 +15969,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 30389-2024</t>
+          <t>A 5513-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16003,10 +15983,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45491</v>
+        <v>45693</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16019,7 +15999,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16062,7 +16042,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 35380-2023</t>
+          <t>A 15813-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16072,14 +16052,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45146</v>
+        <v>44664</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16091,8 +16071,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16135,7 +16120,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 54419-2024</t>
+          <t>A 6368-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16149,10 +16134,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45617</v>
+        <v>45699</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16164,13 +16149,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>22.7</v>
+        <v>1.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16213,7 +16193,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 50358-2025</t>
+          <t>A 63074-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16227,10 +16207,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45944</v>
+        <v>46009</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16242,8 +16222,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>4.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16286,7 +16271,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 34961-2022</t>
+          <t>A 44069-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16300,10 +16285,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44796</v>
+        <v>45188</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16316,7 +16301,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16359,7 +16344,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 14185-2023</t>
+          <t>A 165-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16373,10 +16358,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45009</v>
+        <v>46024</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16389,7 +16374,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16432,7 +16417,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 27087-2024</t>
+          <t>A 3198-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16446,10 +16431,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45471</v>
+        <v>45316</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16462,7 +16447,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16505,7 +16490,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 6368-2025</t>
+          <t>A 5350-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16519,10 +16504,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45699</v>
+        <v>45692</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16535,7 +16520,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16578,7 +16563,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 39190-2023</t>
+          <t>A 16270-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16588,14 +16573,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45166</v>
+        <v>45407</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16651,7 +16636,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 31447-2026</t>
+          <t>A 51041-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16665,10 +16650,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46220</v>
+        <v>45603</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16681,7 +16666,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16724,7 +16709,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 54590-2024</t>
+          <t>A 6557-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16738,10 +16723,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45617</v>
+        <v>45699</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16754,7 +16739,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16797,7 +16782,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 14993-2023</t>
+          <t>A 15344-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16811,10 +16796,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45015</v>
+        <v>45747</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16827,7 +16812,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16870,7 +16855,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 36824-2026</t>
+          <t>A 50387-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16884,10 +16869,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46272</v>
+        <v>45600</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16899,13 +16884,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16948,7 +16928,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 52469-2023</t>
+          <t>A 32715-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16962,10 +16942,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45225</v>
+        <v>45516</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16978,7 +16958,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17021,7 +17001,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 19350-2023</t>
+          <t>A 38259-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17035,10 +17015,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45049</v>
+        <v>45161</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17051,7 +17031,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17094,7 +17074,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 51041-2024</t>
+          <t>A 21530-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17108,10 +17088,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45603</v>
+        <v>45782</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17124,7 +17104,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17167,7 +17147,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 37482-2026</t>
+          <t>A 21357-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17181,10 +17161,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46275</v>
+        <v>45782</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17196,13 +17176,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>16.5</v>
+        <v>1.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17245,7 +17220,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 37473-2026</t>
+          <t>A 63115-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17259,10 +17234,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46275</v>
+        <v>46009</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17275,7 +17250,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17318,7 +17293,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 37469-2026</t>
+          <t>A 61011-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17328,14 +17303,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46275</v>
+        <v>45645</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17348,7 +17323,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17391,7 +17366,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 11972-2023</t>
+          <t>A 1337-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17405,10 +17380,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44994</v>
+        <v>46031</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17421,7 +17396,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17464,7 +17439,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 12332-2023</t>
+          <t>A 8067-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17478,10 +17453,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44999</v>
+        <v>45707</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17494,7 +17469,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17537,7 +17512,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 37991-2026</t>
+          <t>A 32464-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17551,10 +17526,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46280</v>
+        <v>45838</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17567,7 +17542,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17610,7 +17585,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 38266-2022</t>
+          <t>A 25895-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17624,10 +17599,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44812</v>
+        <v>46178</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17640,7 +17615,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17683,7 +17658,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 1323-2023</t>
+          <t>A 25816-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17697,10 +17672,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44936</v>
+        <v>46178</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17713,7 +17688,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17756,7 +17731,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 37494-2026</t>
+          <t>A 25863-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17770,10 +17745,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46275</v>
+        <v>46178</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17786,7 +17761,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17829,7 +17804,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 14736-2024</t>
+          <t>A 25975-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17839,14 +17814,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45397</v>
+        <v>46181</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17859,7 +17834,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17902,7 +17877,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 25729-2023</t>
+          <t>A 27274-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17916,10 +17891,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45084</v>
+        <v>46184</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17932,7 +17907,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17975,7 +17950,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 30388-2024</t>
+          <t>A 27292-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17989,10 +17964,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45491</v>
+        <v>46184</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18005,7 +17980,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18048,7 +18023,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 21855-2022</t>
+          <t>A 28908-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18062,10 +18037,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44709</v>
+        <v>46199</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18078,7 +18053,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18121,7 +18096,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 72603-2021</t>
+          <t>A 28704-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18135,10 +18110,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44546</v>
+        <v>46198</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18150,8 +18125,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I231" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18194,7 +18174,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 14750-2023</t>
+          <t>A 28718-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18208,10 +18188,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45014</v>
+        <v>46198</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18223,8 +18203,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I232" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18267,7 +18252,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 47600-2023</t>
+          <t>A 30155-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18281,10 +18266,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45203</v>
+        <v>46206</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18296,8 +18281,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I233" t="n">
-        <v>0.6</v>
+        <v>5.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18340,7 +18330,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 21357-2025</t>
+          <t>A 50358-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18354,10 +18344,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45782</v>
+        <v>45944</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18370,7 +18360,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18413,7 +18403,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 21530-2025</t>
+          <t>A 31447-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18427,10 +18417,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45782</v>
+        <v>46220</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18443,7 +18433,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18486,7 +18476,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 3554-2025</t>
+          <t>A 36824-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18500,10 +18490,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45680</v>
+        <v>46272</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18515,8 +18505,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I236" t="n">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18559,7 +18554,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 50818-2023</t>
+          <t>A 37473-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18573,10 +18568,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45217</v>
+        <v>46275</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18589,7 +18584,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18632,7 +18627,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 21336-2025</t>
+          <t>A 37482-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18646,10 +18641,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45782</v>
+        <v>46275</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18661,8 +18656,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I238" t="n">
-        <v>1.9</v>
+        <v>16.5</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18705,7 +18705,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 30600-2025</t>
+          <t>A 37469-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18719,10 +18719,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45831</v>
+        <v>46275</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18778,7 +18778,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 32466-2025</t>
+          <t>A 37991-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18792,10 +18792,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45838</v>
+        <v>46280</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18851,24 +18851,24 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 32476-2025</t>
+          <t>S 899-2024</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45838</v>
+        <v>45376</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>0.7</v>
+        <v>18</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18921,10 +18921,10 @@
       </c>
       <c r="V241" s="2" t="inlineStr"/>
     </row>
-    <row r="242" ht="15" customHeight="1">
+    <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>S 899-2024</t>
+          <t>S 6457-2022</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -18938,10 +18938,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45376</v>
+        <v>44879</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -18953,8 +18953,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I242" t="n">
-        <v>18</v>
+        <v>101.8</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -18993,84 +18998,6 @@
         <v>0</v>
       </c>
       <c r="V242" s="2" t="inlineStr"/>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>S 6457-2022</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D243" s="1" t="n">
-        <v>44879</v>
-      </c>
-      <c r="E243" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I243" t="n">
-        <v>101.8</v>
-      </c>
-      <c r="J243" t="n">
-        <v>0</v>
-      </c>
-      <c r="K243" t="n">
-        <v>0</v>
-      </c>
-      <c r="L243" t="n">
-        <v>0</v>
-      </c>
-      <c r="M243" t="n">
-        <v>0</v>
-      </c>
-      <c r="N243" t="n">
-        <v>0</v>
-      </c>
-      <c r="O243" t="n">
-        <v>0</v>
-      </c>
-      <c r="P243" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
-      <c r="R243" t="n">
-        <v>0</v>
-      </c>
-      <c r="S243" t="n">
-        <v>0</v>
-      </c>
-      <c r="T243" t="n">
-        <v>0</v>
-      </c>
-      <c r="U243" t="n">
-        <v>0</v>
-      </c>
-      <c r="V243" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÖDESHÖG.xlsx
+++ b/Översikt ÖDESHÖG.xlsx
@@ -601,7 +601,7 @@
         <v>45805</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45723</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44698</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>44664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 35443-2022</t>
+          <t>A 56797-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1058,14 +1058,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44798</v>
+        <v>45244</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1118,149 +1118,149 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Jungfrulin
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 56797-2023 artfynd.xlsx", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 56797-2023 karta.png", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 56797-2023 georefererad karta.tif", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 56797-2023 FSC-klagomål.docx", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 56797-2023 FSC-klagomål mail.docx", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 56797-2023 tillsynsbegäran.docx", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 56797-2023 tillsynsbegäran mail.docx", "A 56797-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 35443-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44798</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Axveronika
 Bivråk</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 35443-2022 artfynd.xlsx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 35443-2022 karta.png", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 35443-2022 georefererad karta.tif", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 35443-2022 FSC-klagomål.docx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 35443-2022 FSC-klagomål mail.docx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 35443-2022 tillsynsbegäran.docx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 35443-2022 tillsynsbegäran mail.docx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/fåglar/A 35443-2022 prioriterade fågelarter.docx", "A 35443-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 56797-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45244</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 56797-2023 artfynd.xlsx", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 56797-2023 karta.png", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 56797-2023 georefererad karta.tif", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 56797-2023 FSC-klagomål.docx", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 56797-2023 FSC-klagomål mail.docx", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 56797-2023 tillsynsbegäran.docx", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 56797-2023 tillsynsbegäran mail.docx", "A 56797-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>44538</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 62988-2023</t>
+          <t>A 58551-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45272</v>
+        <v>45251</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1503,16 +1503,11 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1524,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1533,10 +1528,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1549,476 +1544,476 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58551-2023 artfynd.xlsx", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58551-2023 karta.png", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58551-2023 georefererad karta.tif", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58551-2023 FSC-klagomål.docx", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58551-2023 FSC-klagomål mail.docx", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58551-2023 tillsynsbegäran.docx", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58551-2023 tillsynsbegäran mail.docx", "A 58551-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 50774-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Mörk dunört</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 50774-2023 artfynd.xlsx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 50774-2023 karta.png", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 50774-2023 georefererad karta.tif", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 50774-2023 FSC-klagomål.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 50774-2023 FSC-klagomål mail.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 50774-2023 tillsynsbegäran.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 50774-2023 tillsynsbegäran mail.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 15437-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 15437-2025 artfynd.xlsx", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 15437-2025 karta.png", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 15437-2025 georefererad karta.tif", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/knärot/A 15437-2025 karta knärot.png", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 15437-2025 FSC-klagomål.docx", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 15437-2025 FSC-klagomål mail.docx", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 15437-2025 tillsynsbegäran.docx", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 15437-2025 tillsynsbegäran mail.docx", "A 15437-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 32713-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45516</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Kristinspindling</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32713-2024 artfynd.xlsx", "A 32713-2024")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32713-2024 karta.png", "A 32713-2024")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32713-2024 georefererad karta.tif", "A 32713-2024")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32713-2024 FSC-klagomål.docx", "A 32713-2024")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32713-2024 FSC-klagomål mail.docx", "A 32713-2024")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32713-2024 tillsynsbegäran.docx", "A 32713-2024")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32713-2024 tillsynsbegäran mail.docx", "A 32713-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 62988-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45272</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>19</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>Skogsalm</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 62988-2023 artfynd.xlsx", "A 62988-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 62988-2023 karta.png", "A 62988-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 62988-2023 georefererad karta.tif", "A 62988-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 62988-2023 FSC-klagomål.docx", "A 62988-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 62988-2023 FSC-klagomål mail.docx", "A 62988-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 62988-2023 tillsynsbegäran.docx", "A 62988-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 62988-2023 tillsynsbegäran mail.docx", "A 62988-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 15437-2025</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45747</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 15437-2025 artfynd.xlsx", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 15437-2025 karta.png", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 15437-2025 georefererad karta.tif", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="Z11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/knärot/A 15437-2025 karta knärot.png", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 15437-2025 FSC-klagomål.docx", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 15437-2025 FSC-klagomål mail.docx", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 15437-2025 tillsynsbegäran.docx", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 15437-2025 tillsynsbegäran mail.docx", "A 15437-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 4772-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44592</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 4772-2022 artfynd.xlsx", "A 4772-2022")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 4772-2022 karta.png", "A 4772-2022")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 4772-2022 georefererad karta.tif", "A 4772-2022")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 4772-2022 FSC-klagomål.docx", "A 4772-2022")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 4772-2022 FSC-klagomål mail.docx", "A 4772-2022")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 4772-2022 tillsynsbegäran.docx", "A 4772-2022")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 4772-2022 tillsynsbegäran mail.docx", "A 4772-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 58052-2021</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>44487</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Granbarkgnagare</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58052-2021 artfynd.xlsx", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58052-2021 karta.png", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58052-2021 georefererad karta.tif", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58052-2021 FSC-klagomål.docx", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58052-2021 FSC-klagomål mail.docx", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58052-2021 tillsynsbegäran.docx", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58052-2021 tillsynsbegäran mail.docx", "A 58052-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 58551-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45251</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58551-2023 artfynd.xlsx", "A 58551-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58551-2023 karta.png", "A 58551-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58551-2023 georefererad karta.tif", "A 58551-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58551-2023 FSC-klagomål.docx", "A 58551-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58551-2023 FSC-klagomål mail.docx", "A 58551-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58551-2023 tillsynsbegäran.docx", "A 58551-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58551-2023 tillsynsbegäran mail.docx", "A 58551-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32776-2025</t>
+          <t>A 38720-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2028,14 +2023,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45839</v>
+        <v>45163</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2048,19 +2043,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2072,10 +2067,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2088,35 +2083,35 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Hässleklocka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32776-2025 artfynd.xlsx", "A 32776-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 38720-2023 artfynd.xlsx", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32776-2025 karta.png", "A 32776-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 38720-2023 karta.png", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32776-2025 georefererad karta.tif", "A 32776-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 38720-2023 georefererad karta.tif", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32776-2025 FSC-klagomål.docx", "A 32776-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 38720-2023 FSC-klagomål.docx", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32776-2025 FSC-klagomål mail.docx", "A 32776-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 38720-2023 FSC-klagomål mail.docx", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32776-2025 tillsynsbegäran.docx", "A 32776-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 38720-2023 tillsynsbegäran.docx", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32776-2025 tillsynsbegäran mail.docx", "A 32776-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 38720-2023 tillsynsbegäran mail.docx", "A 38720-2023")</f>
         <v/>
       </c>
     </row>
@@ -2140,7 +2135,7 @@
         <v>45243</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2228,7 +2223,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 50774-2023</t>
+          <t>A 58052-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2242,10 +2237,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45210</v>
+        <v>44487</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2257,17 +2252,22 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>9.5</v>
+        <v>4.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2298,42 +2298,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Mörk dunört</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 50774-2023 artfynd.xlsx", "A 50774-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58052-2021 artfynd.xlsx", "A 58052-2021")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 50774-2023 karta.png", "A 50774-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58052-2021 karta.png", "A 58052-2021")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 50774-2023 georefererad karta.tif", "A 50774-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58052-2021 georefererad karta.tif", "A 58052-2021")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 50774-2023 FSC-klagomål.docx", "A 50774-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58052-2021 FSC-klagomål.docx", "A 58052-2021")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 50774-2023 FSC-klagomål mail.docx", "A 50774-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58052-2021 FSC-klagomål mail.docx", "A 58052-2021")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 50774-2023 tillsynsbegäran.docx", "A 50774-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58052-2021 tillsynsbegäran.docx", "A 58052-2021")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 50774-2023 tillsynsbegäran mail.docx", "A 50774-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58052-2021 tillsynsbegäran mail.docx", "A 58052-2021")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 38720-2023</t>
+          <t>A 4772-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45163</v>
+        <v>44592</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2363,23 +2363,23 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
@@ -2387,10 +2387,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2399,46 +2399,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Hässleklocka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 38720-2023 artfynd.xlsx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 4772-2022 artfynd.xlsx", "A 4772-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 38720-2023 karta.png", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 4772-2022 karta.png", "A 4772-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 38720-2023 georefererad karta.tif", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 4772-2022 georefererad karta.tif", "A 4772-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 38720-2023 FSC-klagomål.docx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 4772-2022 FSC-klagomål.docx", "A 4772-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 38720-2023 FSC-klagomål mail.docx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 4772-2022 FSC-klagomål mail.docx", "A 4772-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 38720-2023 tillsynsbegäran.docx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 4772-2022 tillsynsbegäran.docx", "A 4772-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 38720-2023 tillsynsbegäran mail.docx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 4772-2022 tillsynsbegäran mail.docx", "A 4772-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32713-2024</t>
+          <t>A 32776-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2448,14 +2448,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45516</v>
+        <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6.1</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2504,39 +2504,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Kristinspindling</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32713-2024 artfynd.xlsx", "A 32713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32776-2025 artfynd.xlsx", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32713-2024 karta.png", "A 32713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32776-2025 karta.png", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32713-2024 georefererad karta.tif", "A 32713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32776-2025 georefererad karta.tif", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32713-2024 FSC-klagomål.docx", "A 32713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32776-2025 FSC-klagomål.docx", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32713-2024 FSC-klagomål mail.docx", "A 32713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32776-2025 FSC-klagomål mail.docx", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32713-2024 tillsynsbegäran.docx", "A 32713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32776-2025 tillsynsbegäran.docx", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32713-2024 tillsynsbegäran mail.docx", "A 32713-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32776-2025 tillsynsbegäran mail.docx", "A 32776-2025")</f>
         <v/>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
         <v>44509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44538</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>44614</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>44803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>44510</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44504</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44517</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>44666</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3554-2025</t>
+          <t>A 29967-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45680</v>
+        <v>44756</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>44796</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 29967-2022</t>
+          <t>A 6705-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44756</v>
+        <v>45342</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3526,8 +3526,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3570,7 +3575,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 39032-2023</t>
+          <t>A 36114-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3584,10 +3589,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45163</v>
+        <v>44803</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3599,13 +3604,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 14993-2023</t>
+          <t>A 35661-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3662,10 +3662,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45015</v>
+        <v>45532</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11280-2025</t>
+          <t>A 5819-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3731,14 +3731,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45726</v>
+        <v>45335</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3750,8 +3750,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3794,7 +3799,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8049-2025</t>
+          <t>A 3198-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3808,10 +3813,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45707</v>
+        <v>45316</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3824,7 +3829,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3867,7 +3872,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 38152-2023</t>
+          <t>A 22088-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3881,10 +3886,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45161</v>
+        <v>45069</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3897,7 +3902,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3940,7 +3945,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8515-2022</t>
+          <t>A 8256-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3950,14 +3955,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44613</v>
+        <v>44974</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3970,7 +3975,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4013,7 +4018,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 36114-2022</t>
+          <t>A 15790-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4027,10 +4032,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44803</v>
+        <v>45748</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4043,7 +4048,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4086,7 +4091,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 47600-2023</t>
+          <t>A 26949-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4100,10 +4105,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45203</v>
+        <v>45093</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4116,7 +4121,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4159,7 +4164,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38723-2023</t>
+          <t>A 15813-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4169,14 +4174,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45163</v>
+        <v>44664</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4188,8 +4193,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4232,7 +4242,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3130-2025</t>
+          <t>A 38152-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4246,10 +4256,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45678</v>
+        <v>45161</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4261,13 +4271,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>18.6</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4310,7 +4315,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 50818-2023</t>
+          <t>A 56841-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4324,10 +4329,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45217</v>
+        <v>44894</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4340,7 +4345,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4383,7 +4388,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 16128-2025</t>
+          <t>A 44069-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4397,10 +4402,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45750</v>
+        <v>45188</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4412,13 +4417,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 55971-2023</t>
+          <t>A 1578-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45240</v>
+        <v>44937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4534,7 +4534,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 30945-2023</t>
+          <t>A 11280-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45113</v>
+        <v>45726</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4607,7 +4607,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 15906-2024</t>
+          <t>A 15909-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4624,7 +4624,7 @@
         <v>45405</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4680,7 +4680,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 16164-2023</t>
+          <t>A 39032-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4694,10 +4694,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45027</v>
+        <v>45163</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4758,7 +4758,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 30964-2023</t>
+          <t>A 45973-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4772,10 +4772,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45113</v>
+        <v>45580</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4831,7 +4831,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 21770-2023</t>
+          <t>A 9448-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45065</v>
+        <v>44981</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4904,7 +4904,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 19351-2023</t>
+          <t>A 39920-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45049</v>
+        <v>45553</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.8</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4977,7 +4977,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 21336-2025</t>
+          <t>A 54226-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45782</v>
+        <v>44470</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5050,7 +5050,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 38266-2022</t>
+          <t>A 46528-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44812</v>
+        <v>45582</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 21771-2023</t>
+          <t>A 36075-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45065</v>
+        <v>45149</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5196,7 +5196,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 41730-2025</t>
+          <t>A 1674-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5210,10 +5210,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45902</v>
+        <v>44938</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5286,7 +5286,7 @@
         <v>45145</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 45973-2024</t>
+          <t>A 6421-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5356,10 +5356,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45580</v>
+        <v>45699</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30389-2024</t>
+          <t>A 6456-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45491</v>
+        <v>45699</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5488,7 +5488,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35229-2023</t>
+          <t>A 17618-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45145</v>
+        <v>45416</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5561,7 +5561,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 1578-2023</t>
+          <t>A 47993-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5575,10 +5575,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44937</v>
+        <v>45589</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 5819-2024</t>
+          <t>A 5513-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5644,14 +5644,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45335</v>
+        <v>45693</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5663,13 +5663,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5712,7 +5707,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 54226-2021</t>
+          <t>A 38259-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5726,10 +5721,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44470</v>
+        <v>45161</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5742,7 +5737,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5785,7 +5780,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 48325-2022</t>
+          <t>A 13129-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5795,14 +5790,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44858</v>
+        <v>45002</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5814,13 +5809,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5863,7 +5853,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 47993-2024</t>
+          <t>A 6164-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5877,10 +5867,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45589</v>
+        <v>45337</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5893,7 +5883,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5936,7 +5926,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 64802-2021</t>
+          <t>A 14156-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5946,14 +5936,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44512</v>
+        <v>45009</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5966,7 +5956,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6009,7 +5999,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 61880-2021</t>
+          <t>A 16270-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6023,10 +6013,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44502</v>
+        <v>45407</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6039,7 +6029,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6082,7 +6072,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6164-2024</t>
+          <t>A 35411-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6096,10 +6086,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45337</v>
+        <v>45146</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6112,7 +6102,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6155,7 +6145,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6705-2024</t>
+          <t>A 20244-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6169,10 +6159,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45342</v>
+        <v>44698</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6190,7 +6180,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>8.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6233,7 +6223,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 35661-2024</t>
+          <t>A 6557-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6247,10 +6237,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45532</v>
+        <v>45699</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6263,7 +6253,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6306,7 +6296,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 56841-2022</t>
+          <t>A 32378-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6320,10 +6310,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44894</v>
+        <v>45512</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6336,7 +6326,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6379,7 +6369,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 1323-2023</t>
+          <t>A 19351-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6393,10 +6383,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44936</v>
+        <v>45049</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6409,7 +6399,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6469,7 +6459,7 @@
         <v>45512</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6525,7 +6515,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 38212-2023</t>
+          <t>A 8515-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6539,10 +6529,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45161</v>
+        <v>44613</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6555,7 +6545,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6598,7 +6588,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 27087-2024</t>
+          <t>A 61880-2021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6612,10 +6602,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45471</v>
+        <v>44502</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6628,7 +6618,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6671,7 +6661,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 46059-2025</t>
+          <t>A 33375-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6685,10 +6675,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45924</v>
+        <v>45519</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6700,8 +6690,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6744,7 +6739,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 39920-2024</t>
+          <t>A 41730-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6758,10 +6753,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45553</v>
+        <v>45902</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6774,7 +6769,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6817,7 +6812,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30388-2024</t>
+          <t>A 43263-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6827,14 +6822,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45491</v>
+        <v>45183</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6847,7 +6842,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6907,7 +6902,7 @@
         <v>45582</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6963,7 +6958,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 3149-2024</t>
+          <t>A 39024-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6977,10 +6972,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45316</v>
+        <v>45163</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6992,8 +6987,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>4.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 46788-2025</t>
+          <t>A 38212-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45926</v>
+        <v>45161</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7109,7 +7109,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 46778-2025</t>
+          <t>A 3130-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7123,10 +7123,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45926</v>
+        <v>45678</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7138,8 +7138,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>1.2</v>
+        <v>18.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7182,7 +7187,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 47597-2023</t>
+          <t>A 39027-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7196,10 +7201,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45203</v>
+        <v>45163</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7211,8 +7216,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7255,7 +7265,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 4678-2024</t>
+          <t>A 15907-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7265,14 +7275,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45328</v>
+        <v>45405</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7285,7 +7295,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7328,7 +7338,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 35095-2023</t>
+          <t>A 15915-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7338,14 +7348,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45145</v>
+        <v>45405</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7358,7 +7368,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7401,7 +7411,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 46999-2025</t>
+          <t>A 20232-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7415,10 +7425,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45929</v>
+        <v>44698</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7430,8 +7440,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7474,7 +7489,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 15907-2024</t>
+          <t>A 46059-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7484,14 +7499,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45405</v>
+        <v>45924</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7504,7 +7519,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7547,7 +7562,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 15915-2024</t>
+          <t>A 46778-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7557,14 +7572,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45405</v>
+        <v>45926</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7577,7 +7592,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7620,7 +7635,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 1749-2025</t>
+          <t>A 46999-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7634,10 +7649,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45671</v>
+        <v>45929</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7650,7 +7665,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7693,7 +7708,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 48063-2025</t>
+          <t>A 46788-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7707,10 +7722,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45932</v>
+        <v>45926</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7723,7 +7738,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7783,7 +7798,7 @@
         <v>45931</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7839,7 +7854,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 15909-2024</t>
+          <t>A 48063-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7849,14 +7864,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45405</v>
+        <v>45932</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7869,7 +7884,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.1</v>
+        <v>5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7912,7 +7927,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 48575-2025</t>
+          <t>A 8063-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7926,10 +7941,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45936</v>
+        <v>45707</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7942,7 +7957,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7985,7 +8000,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 6375-2025</t>
+          <t>A 5350-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7999,10 +8014,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45699</v>
+        <v>45692</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8015,7 +8030,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8058,7 +8073,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 17618-2024</t>
+          <t>A 32715-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8072,10 +8087,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45416</v>
+        <v>45516</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8088,7 +8103,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8148,7 +8163,7 @@
         <v>45936</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8221,7 +8236,7 @@
         <v>45936</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8277,7 +8292,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 13129-2023</t>
+          <t>A 48575-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8291,10 +8306,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45002</v>
+        <v>45936</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8307,7 +8322,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8350,7 +8365,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 5283-2024</t>
+          <t>A 6465-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8364,10 +8379,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45331</v>
+        <v>45699</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8380,7 +8395,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8423,7 +8438,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 14750-2023</t>
+          <t>A 1749-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8437,10 +8452,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45014</v>
+        <v>45671</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8453,7 +8468,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8496,7 +8511,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 32378-2024</t>
+          <t>A 50416-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8510,10 +8525,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45512</v>
+        <v>45944</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8526,7 +8541,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8569,7 +8584,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 50416-2025</t>
+          <t>A 51171-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8583,10 +8598,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45944</v>
+        <v>45947</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8599,7 +8614,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8642,7 +8657,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 14156-2023</t>
+          <t>A 51328-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8656,10 +8671,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45009</v>
+        <v>45950</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8672,7 +8687,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8715,7 +8730,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 51171-2025</t>
+          <t>A 17126-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8729,10 +8744,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45947</v>
+        <v>45412</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8745,7 +8760,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8788,7 +8803,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 51328-2025</t>
+          <t>A 4678-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8802,10 +8817,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45950</v>
+        <v>45328</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8818,7 +8833,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>6</v>
+        <v>0.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8861,7 +8876,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 46528-2024</t>
+          <t>A 21771-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8875,10 +8890,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45582</v>
+        <v>45065</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8891,7 +8906,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>5.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8934,7 +8949,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 8256-2023</t>
+          <t>A 64802-2021</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8948,10 +8963,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44974</v>
+        <v>44512</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8964,7 +8979,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9007,7 +9022,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 51180-2024</t>
+          <t>A 20720-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9021,10 +9036,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45603</v>
+        <v>45776</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9080,7 +9095,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 22088-2023</t>
+          <t>A 55901-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9094,10 +9109,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45069</v>
+        <v>45973</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9110,7 +9125,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9153,7 +9168,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 36099-2024</t>
+          <t>A 55906-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9167,10 +9182,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45533</v>
+        <v>45973</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9183,7 +9198,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9226,7 +9241,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 39190-2023</t>
+          <t>A 16128-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9236,14 +9251,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45166</v>
+        <v>45750</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9255,8 +9270,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9299,7 +9319,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 14736-2024</t>
+          <t>A 55908-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9309,14 +9329,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45397</v>
+        <v>45973</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9329,7 +9349,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9372,7 +9392,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 16168-2023</t>
+          <t>A 3149-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9386,10 +9406,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45027</v>
+        <v>45316</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9401,13 +9421,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9450,7 +9465,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 38718-2023</t>
+          <t>A 165-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9464,10 +9479,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45163</v>
+        <v>46024</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9480,7 +9495,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9523,7 +9538,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 2512-2024</t>
+          <t>A 51180-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9537,10 +9552,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45313</v>
+        <v>45603</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9553,7 +9568,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9596,7 +9611,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 20232-2022</t>
+          <t>A 35229-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9610,10 +9625,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44698</v>
+        <v>45145</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9625,13 +9640,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9674,7 +9684,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 14185-2023</t>
+          <t>A 63074-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9688,10 +9698,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45009</v>
+        <v>46009</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9703,8 +9713,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9764,7 +9779,7 @@
         <v>45603</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9820,7 +9835,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 20720-2025</t>
+          <t>A 19157-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9834,10 +9849,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45776</v>
+        <v>45048</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9850,7 +9865,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9893,7 +9908,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 14166-2023</t>
+          <t>A 55971-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9907,10 +9922,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45009</v>
+        <v>45240</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9923,7 +9938,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9966,7 +9981,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 19350-2023</t>
+          <t>A 63115-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9980,10 +9995,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45049</v>
+        <v>46009</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9996,7 +10011,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10039,7 +10054,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 55908-2025</t>
+          <t>A 16164-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10053,10 +10068,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45973</v>
+        <v>45027</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10068,8 +10083,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10112,7 +10132,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 35380-2023</t>
+          <t>A 39024-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10126,10 +10146,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45146</v>
+        <v>45163</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10141,8 +10161,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10185,7 +10210,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 55901-2025</t>
+          <t>A 61786-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10199,10 +10224,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45973</v>
+        <v>46002</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10215,7 +10240,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10258,7 +10283,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 55906-2025</t>
+          <t>A 61798-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10272,10 +10297,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45973</v>
+        <v>46002</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10287,8 +10312,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10331,7 +10361,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 6592-2025</t>
+          <t>A 61800-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10345,10 +10375,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45700</v>
+        <v>46002</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10361,7 +10391,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10404,7 +10434,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 11972-2023</t>
+          <t>A 61801-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10418,10 +10448,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44994</v>
+        <v>46002</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10434,7 +10464,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10477,7 +10507,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 43263-2023</t>
+          <t>A 61972-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10487,14 +10517,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45183</v>
+        <v>46003</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10506,8 +10536,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10550,7 +10585,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 20244-2022</t>
+          <t>A 61470-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10564,10 +10599,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44698</v>
+        <v>46001</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10585,7 +10620,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10628,7 +10663,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 20612-2022</t>
+          <t>A 61629-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10642,10 +10677,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44700</v>
+        <v>46002</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10657,13 +10692,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>8.9</v>
+        <v>1.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10706,7 +10736,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 54419-2024</t>
+          <t>A 47597-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10720,10 +10750,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45617</v>
+        <v>45203</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10735,13 +10765,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>22.7</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10784,7 +10809,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 6421-2025</t>
+          <t>A 62482-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10798,10 +10823,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45699</v>
+        <v>46007</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10814,7 +10839,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>6.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10857,7 +10882,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 52469-2023</t>
+          <t>A 62202-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10871,10 +10896,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45225</v>
+        <v>46006</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10887,7 +10912,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10930,7 +10955,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 8063-2025</t>
+          <t>A 62801-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10944,10 +10969,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45707</v>
+        <v>46008</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10960,7 +10985,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.1</v>
+        <v>6.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11003,7 +11028,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 30600-2025</t>
+          <t>A 14166-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11017,10 +11042,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45831</v>
+        <v>45009</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11033,7 +11058,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11076,7 +11101,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 15790-2025</t>
+          <t>A 15344-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11090,10 +11115,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45748</v>
+        <v>45747</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11149,7 +11174,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 602-2026</t>
+          <t>A 10335-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11163,10 +11188,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46029</v>
+        <v>44623</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11179,7 +11204,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11222,7 +11247,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 1589-2026</t>
+          <t>A 35095-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11236,10 +11261,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46034</v>
+        <v>45145</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11251,13 +11276,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11300,7 +11320,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 61801-2025</t>
+          <t>A 20612-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11314,10 +11334,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46002</v>
+        <v>44700</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11329,8 +11349,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>3.6</v>
+        <v>8.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11373,7 +11398,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 61470-2025</t>
+          <t>A 64010-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11387,10 +11412,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46001</v>
+        <v>46021</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11408,7 +11433,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>8</v>
+        <v>15.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11451,7 +11476,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 1279-2026</t>
+          <t>A 64015-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11465,10 +11490,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46031</v>
+        <v>46021</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11480,8 +11505,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11524,7 +11554,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 1264-2026</t>
+          <t>A 15198-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11538,10 +11568,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46031</v>
+        <v>44658</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11554,7 +11584,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11597,7 +11627,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 61798-2025</t>
+          <t>A 602-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11611,10 +11641,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46002</v>
+        <v>46029</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11626,13 +11656,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11675,7 +11700,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 61800-2025</t>
+          <t>A 6375-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11689,10 +11714,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46002</v>
+        <v>45699</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11705,7 +11730,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11748,7 +11773,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 61629-2025</t>
+          <t>A 6592-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11762,10 +11787,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46002</v>
+        <v>45700</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11778,7 +11803,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11838,7 +11863,7 @@
         <v>45160</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11894,7 +11919,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 1585-2026</t>
+          <t>A 1279-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11908,10 +11933,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46034</v>
+        <v>46031</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11923,13 +11948,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11972,7 +11992,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 61786-2025</t>
+          <t>A 1261-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11986,10 +12006,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46002</v>
+        <v>46031</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12002,7 +12022,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12045,7 +12065,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 1273-2026</t>
+          <t>A 1268-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12062,7 +12082,7 @@
         <v>46031</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12075,7 +12095,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12118,7 +12138,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 32476-2025</t>
+          <t>A 1264-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12132,10 +12152,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45838</v>
+        <v>46031</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12148,7 +12168,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12191,7 +12211,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 1261-2026</t>
+          <t>A 1273-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12208,7 +12228,7 @@
         <v>46031</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12221,7 +12241,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12264,7 +12284,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 1268-2026</t>
+          <t>A 1585-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12278,10 +12298,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12293,8 +12313,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12337,7 +12362,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 62202-2025</t>
+          <t>A 1589-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12351,10 +12376,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46006</v>
+        <v>46034</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12366,8 +12391,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12410,7 +12440,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 6465-2025</t>
+          <t>A 6506-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12427,7 +12457,7 @@
         <v>45699</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12440,7 +12470,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12483,7 +12513,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 61972-2025</t>
+          <t>A 61011-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12493,14 +12523,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46003</v>
+        <v>45645</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12512,13 +12542,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12561,7 +12586,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 32466-2025</t>
+          <t>A 1337-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12575,10 +12600,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45838</v>
+        <v>46031</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12591,7 +12616,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12634,7 +12659,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 62801-2025</t>
+          <t>A 32464-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12648,10 +12673,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46008</v>
+        <v>45838</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12664,7 +12689,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>6.6</v>
+        <v>1.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12707,7 +12732,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 62482-2025</t>
+          <t>A 8067-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12721,10 +12746,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46007</v>
+        <v>45707</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12737,7 +12762,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>6.7</v>
+        <v>0.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12780,7 +12805,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 1674-2023</t>
+          <t>A 5283-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12794,10 +12819,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44938</v>
+        <v>45331</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12810,7 +12835,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12853,7 +12878,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 34961-2022</t>
+          <t>A 7375-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12867,10 +12892,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44796</v>
+        <v>46059</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12883,7 +12908,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12926,7 +12951,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 19157-2023</t>
+          <t>A 38723-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12940,10 +12965,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45048</v>
+        <v>45163</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12999,7 +13024,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 64015-2025</t>
+          <t>A 50387-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13013,10 +13038,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46021</v>
+        <v>45600</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13028,13 +13053,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>0.9</v>
+        <v>8.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13077,7 +13097,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 64010-2025</t>
+          <t>A 2512-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13091,10 +13111,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46021</v>
+        <v>45313</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13106,13 +13126,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>15.4</v>
+        <v>5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13155,7 +13170,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 39024-2023</t>
+          <t>A 8118-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13169,10 +13184,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45163</v>
+        <v>46062</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13184,13 +13199,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>4.7</v>
+        <v>13.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13233,7 +13243,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 7375-2026</t>
+          <t>A 64709-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13247,10 +13257,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46059</v>
+        <v>45281</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13263,7 +13273,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13306,7 +13316,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 37494-2026</t>
+          <t>A 64710-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13320,10 +13330,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46275</v>
+        <v>45281</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13336,7 +13346,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13379,7 +13389,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 8118-2026</t>
+          <t>A 36730-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13393,10 +13403,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46062</v>
+        <v>45153</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13409,7 +13419,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>13.4</v>
+        <v>3.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13452,7 +13462,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 17126-2024</t>
+          <t>A 16168-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13466,10 +13476,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45412</v>
+        <v>45027</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13481,8 +13491,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13525,7 +13540,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 11193-2023</t>
+          <t>A 21770-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13535,14 +13550,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44992</v>
+        <v>45065</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13555,7 +13570,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13598,7 +13613,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 12859-2026</t>
+          <t>A 36099-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13612,10 +13627,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46092</v>
+        <v>45533</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13628,7 +13643,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13688,7 +13703,7 @@
         <v>46092</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13744,7 +13759,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 26949-2023</t>
+          <t>A 12859-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13758,10 +13773,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45093</v>
+        <v>46092</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13774,7 +13789,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13817,7 +13832,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 14617-2026</t>
+          <t>A 38718-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13831,10 +13846,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46101</v>
+        <v>45163</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13847,7 +13862,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13890,7 +13905,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 6506-2025</t>
+          <t>A 25895-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13904,10 +13919,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45699</v>
+        <v>46178</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13920,7 +13935,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13963,7 +13978,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 12332-2023</t>
+          <t>A 15906-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13973,14 +13988,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44999</v>
+        <v>45405</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13993,7 +14008,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14036,7 +14051,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 36075-2023</t>
+          <t>A 25863-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14050,10 +14065,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45149</v>
+        <v>46178</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14066,7 +14081,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14109,7 +14124,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 16341-2026</t>
+          <t>A 25816-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14123,10 +14138,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46111</v>
+        <v>46178</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14136,11 +14151,6 @@
       <c r="G177" t="inlineStr">
         <is>
           <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I177" t="n">
@@ -14187,7 +14197,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 16402-2026</t>
+          <t>A 25975-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14201,10 +14211,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46111</v>
+        <v>46181</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14216,13 +14226,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14265,7 +14270,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 16414-2026</t>
+          <t>A 14617-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14279,10 +14284,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46111</v>
+        <v>46101</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14294,13 +14299,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>8.199999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14343,7 +14343,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 16370-2026</t>
+          <t>A 27274-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14357,10 +14357,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46111</v>
+        <v>46184</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14372,13 +14372,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>6.9</v>
+        <v>2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14421,7 +14416,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 15198-2022</t>
+          <t>A 27292-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14435,10 +14430,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44658</v>
+        <v>46184</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14451,7 +14446,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14494,7 +14489,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 6456-2025</t>
+          <t>A 35097-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14508,10 +14503,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45699</v>
+        <v>45145</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14524,7 +14519,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14567,7 +14562,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 21855-2022</t>
+          <t>A 16370-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14581,10 +14576,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44709</v>
+        <v>46111</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14596,8 +14591,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>1.5</v>
+        <v>6.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14640,7 +14640,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 72603-2021</t>
+          <t>A 16414-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14654,10 +14654,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44546</v>
+        <v>46111</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14669,8 +14669,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>1.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14713,7 +14718,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 9448-2023</t>
+          <t>A 30945-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14727,10 +14732,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44981</v>
+        <v>45113</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14743,7 +14748,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14786,7 +14791,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 64709-2023</t>
+          <t>A 30964-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14800,10 +14805,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45281</v>
+        <v>45113</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14816,7 +14821,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14859,7 +14864,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 64710-2023</t>
+          <t>A 16402-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14873,10 +14878,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45281</v>
+        <v>46111</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14888,8 +14893,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>0.1</v>
+        <v>2.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14932,7 +14942,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 35097-2023</t>
+          <t>A 16341-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14946,10 +14956,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45145</v>
+        <v>46111</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14961,8 +14971,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15005,7 +15020,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 35411-2023</t>
+          <t>A 16259-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15019,10 +15034,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45146</v>
+        <v>46109</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15078,7 +15093,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 16259-2026</t>
+          <t>A 16262-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15095,7 +15110,7 @@
         <v>46109</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15108,7 +15123,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15151,7 +15166,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 16262-2026</t>
+          <t>A 17950-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15165,10 +15180,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46109</v>
+        <v>46122</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15181,7 +15196,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15224,7 +15239,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 36730-2023</t>
+          <t>A 48325-2022</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15234,14 +15249,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45153</v>
+        <v>44858</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15253,8 +15268,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15297,7 +15317,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 17950-2026</t>
+          <t>A 11699-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15311,10 +15331,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46122</v>
+        <v>45373</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15327,7 +15347,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15370,7 +15390,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 25729-2023</t>
+          <t>A 11704-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15384,10 +15404,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45084</v>
+        <v>45373</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15400,7 +15420,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15443,7 +15463,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 11699-2024</t>
+          <t>A 28718-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15457,10 +15477,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45373</v>
+        <v>46198</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15472,8 +15492,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15516,7 +15541,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 11704-2024</t>
+          <t>A 28704-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15530,10 +15555,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45373</v>
+        <v>46198</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15545,8 +15570,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15589,7 +15619,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 54590-2024</t>
+          <t>A 11193-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15599,14 +15629,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45617</v>
+        <v>44992</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15619,7 +15649,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15662,7 +15692,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 39027-2023</t>
+          <t>A 8049-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15676,10 +15706,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45163</v>
+        <v>45707</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15691,13 +15721,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15740,7 +15765,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 10335-2022</t>
+          <t>A 28908-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15754,10 +15779,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44623</v>
+        <v>46199</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15770,7 +15795,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15813,7 +15838,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 39024-2023</t>
+          <t>A 30389-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15827,10 +15852,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45163</v>
+        <v>45491</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15842,13 +15867,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15891,7 +15911,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 33375-2024</t>
+          <t>A 35380-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15905,10 +15925,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45519</v>
+        <v>45146</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15920,13 +15940,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>3.7</v>
+        <v>0.9</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15969,7 +15984,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 5513-2025</t>
+          <t>A 54419-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15983,10 +15998,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45693</v>
+        <v>45617</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -15998,8 +16013,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>0.7</v>
+        <v>22.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16042,7 +16062,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 15813-2022</t>
+          <t>A 34961-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16052,14 +16072,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44664</v>
+        <v>44796</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16071,13 +16091,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16120,7 +16135,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 6368-2025</t>
+          <t>A 14185-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16134,10 +16149,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45699</v>
+        <v>45009</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16150,7 +16165,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16193,7 +16208,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 63074-2025</t>
+          <t>A 27087-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16207,10 +16222,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46009</v>
+        <v>45471</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16222,13 +16237,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>8.699999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16271,7 +16281,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 44069-2023</t>
+          <t>A 30155-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16285,10 +16295,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45188</v>
+        <v>46206</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16300,8 +16310,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>2.3</v>
+        <v>5.8</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16344,7 +16359,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 165-2026</t>
+          <t>A 6368-2025</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16358,10 +16373,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46024</v>
+        <v>45699</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16374,7 +16389,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16417,7 +16432,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 3198-2024</t>
+          <t>A 39190-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16427,14 +16442,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45316</v>
+        <v>45166</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16447,7 +16462,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16490,7 +16505,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 5350-2025</t>
+          <t>A 54590-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16504,10 +16519,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45692</v>
+        <v>45617</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16520,7 +16535,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16563,7 +16578,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 16270-2024</t>
+          <t>A 50358-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16577,10 +16592,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45407</v>
+        <v>45944</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16593,7 +16608,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16636,7 +16651,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 51041-2024</t>
+          <t>A 14993-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16650,10 +16665,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45603</v>
+        <v>45015</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16666,7 +16681,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16709,7 +16724,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 6557-2025</t>
+          <t>A 52469-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16723,10 +16738,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45699</v>
+        <v>45225</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16739,7 +16754,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16782,7 +16797,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 15344-2025</t>
+          <t>A 19350-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16796,10 +16811,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45747</v>
+        <v>45049</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16812,7 +16827,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16855,7 +16870,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 50387-2024</t>
+          <t>A 51041-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16869,10 +16884,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45600</v>
+        <v>45603</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16885,7 +16900,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>8.5</v>
+        <v>0.4</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16928,7 +16943,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 32715-2024</t>
+          <t>A 31447-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16942,10 +16957,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45516</v>
+        <v>46220</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16958,7 +16973,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17001,7 +17016,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 38259-2023</t>
+          <t>A 11972-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17015,10 +17030,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45161</v>
+        <v>44994</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17031,7 +17046,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17074,7 +17089,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 21530-2025</t>
+          <t>A 12332-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17088,10 +17103,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45782</v>
+        <v>44999</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17104,7 +17119,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17147,7 +17162,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 21357-2025</t>
+          <t>A 38266-2022</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17161,10 +17176,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45782</v>
+        <v>44812</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17177,7 +17192,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17220,7 +17235,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 63115-2025</t>
+          <t>A 36824-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17234,10 +17249,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46009</v>
+        <v>46272</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17249,8 +17264,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17293,7 +17313,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 61011-2024</t>
+          <t>A 1323-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17303,14 +17323,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45645</v>
+        <v>44936</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17323,7 +17343,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17366,7 +17386,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 1337-2026</t>
+          <t>A 14736-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17376,14 +17396,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46031</v>
+        <v>45397</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17396,7 +17416,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17439,7 +17459,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 8067-2025</t>
+          <t>A 25729-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17453,10 +17473,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45707</v>
+        <v>45084</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17469,7 +17489,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17512,7 +17532,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 32464-2025</t>
+          <t>A 37482-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17526,10 +17546,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45838</v>
+        <v>46275</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17541,8 +17561,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I223" t="n">
-        <v>1.4</v>
+        <v>16.5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17585,7 +17610,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 25895-2026</t>
+          <t>A 37473-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17599,10 +17624,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46178</v>
+        <v>46275</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17615,7 +17640,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17658,7 +17683,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 25816-2026</t>
+          <t>A 37469-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17672,10 +17697,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46178</v>
+        <v>46275</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17688,7 +17713,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17731,7 +17756,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 25863-2026</t>
+          <t>A 30388-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17745,10 +17770,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46178</v>
+        <v>45491</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17761,7 +17786,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17804,7 +17829,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 25975-2026</t>
+          <t>A 21855-2022</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17818,10 +17843,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46181</v>
+        <v>44709</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17834,7 +17859,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17877,7 +17902,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 27274-2026</t>
+          <t>A 72603-2021</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17891,10 +17916,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46184</v>
+        <v>44546</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17907,7 +17932,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17950,7 +17975,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 27292-2026</t>
+          <t>A 37991-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17964,10 +17989,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46184</v>
+        <v>46280</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -17980,7 +18005,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18023,7 +18048,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 28908-2026</t>
+          <t>A 14750-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18037,10 +18062,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46199</v>
+        <v>45014</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18053,7 +18078,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18096,7 +18121,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 28704-2026</t>
+          <t>A 47600-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18110,10 +18135,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46198</v>
+        <v>45203</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18125,13 +18150,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I231" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18174,7 +18194,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 28718-2026</t>
+          <t>A 21357-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18188,10 +18208,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46198</v>
+        <v>45782</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18203,13 +18223,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I232" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18252,7 +18267,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 30155-2026</t>
+          <t>A 21530-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18266,10 +18281,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46206</v>
+        <v>45782</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18281,13 +18296,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I233" t="n">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18330,7 +18340,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 50358-2025</t>
+          <t>A 3554-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18344,10 +18354,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45944</v>
+        <v>45680</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18360,7 +18370,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18403,7 +18413,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 31447-2026</t>
+          <t>A 50818-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18417,10 +18427,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46220</v>
+        <v>45217</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18433,7 +18443,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18476,7 +18486,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 36824-2026</t>
+          <t>A 21336-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18490,10 +18500,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46272</v>
+        <v>45782</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18505,13 +18515,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I236" t="n">
-        <v>8</v>
+        <v>1.9</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18554,7 +18559,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 37473-2026</t>
+          <t>A 37494-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18571,7 +18576,7 @@
         <v>46275</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18584,7 +18589,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18627,7 +18632,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 37482-2026</t>
+          <t>A 30600-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18641,10 +18646,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46275</v>
+        <v>45831</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18656,13 +18661,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I238" t="n">
-        <v>16.5</v>
+        <v>4.8</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18705,7 +18705,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 37469-2026</t>
+          <t>A 32466-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18719,10 +18719,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46275</v>
+        <v>45838</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18778,7 +18778,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 37991-2026</t>
+          <t>A 32476-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18792,10 +18792,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>46280</v>
+        <v>45838</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18868,7 +18868,7 @@
         <v>45376</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>44879</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>

--- a/Översikt ÖDESHÖG.xlsx
+++ b/Översikt ÖDESHÖG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE242"/>
+  <dimension ref="A1:AE240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45805</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45723</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44698</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>44664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 56797-2023</t>
+          <t>A 35443-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1058,14 +1058,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45244</v>
+        <v>44798</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1118,149 +1118,149 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Axveronika
+Bivråk</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 35443-2022 artfynd.xlsx", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 35443-2022 karta.png", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 35443-2022 georefererad karta.tif", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 35443-2022 FSC-klagomål.docx", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 35443-2022 FSC-klagomål mail.docx", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 35443-2022 tillsynsbegäran.docx", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 35443-2022 tillsynsbegäran mail.docx", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/fåglar/A 35443-2022 prioriterade fågelarter.docx", "A 35443-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 56797-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45244</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Jungfrulin
 Svinrot</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 56797-2023 artfynd.xlsx", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 56797-2023 karta.png", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 56797-2023 georefererad karta.tif", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 56797-2023 FSC-klagomål.docx", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 56797-2023 FSC-klagomål mail.docx", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 56797-2023 tillsynsbegäran.docx", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 56797-2023 tillsynsbegäran mail.docx", "A 56797-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 35443-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44798</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Axveronika
-Bivråk</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 35443-2022 artfynd.xlsx", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 35443-2022 karta.png", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 35443-2022 georefererad karta.tif", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 35443-2022 FSC-klagomål.docx", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 35443-2022 FSC-klagomål mail.docx", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 35443-2022 tillsynsbegäran.docx", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 35443-2022 tillsynsbegäran mail.docx", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/fåglar/A 35443-2022 prioriterade fågelarter.docx", "A 35443-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>44538</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 58551-2023</t>
+          <t>A 15437-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45251</v>
+        <v>45747</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1503,8 +1503,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>11.9</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1516,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1528,10 +1533,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1544,362 +1549,362 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 15437-2025 artfynd.xlsx", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 15437-2025 karta.png", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 15437-2025 georefererad karta.tif", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/knärot/A 15437-2025 karta knärot.png", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 15437-2025 FSC-klagomål.docx", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 15437-2025 FSC-klagomål mail.docx", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 15437-2025 tillsynsbegäran.docx", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 15437-2025 tillsynsbegäran mail.docx", "A 15437-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 4772-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44592</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 4772-2022 artfynd.xlsx", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 4772-2022 karta.png", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 4772-2022 georefererad karta.tif", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 4772-2022 FSC-klagomål.docx", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 4772-2022 FSC-klagomål mail.docx", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 4772-2022 tillsynsbegäran.docx", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 4772-2022 tillsynsbegäran mail.docx", "A 4772-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 58052-2021</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44487</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58052-2021 artfynd.xlsx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58052-2021 karta.png", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58052-2021 georefererad karta.tif", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58052-2021 FSC-klagomål.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58052-2021 FSC-klagomål mail.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58052-2021 tillsynsbegäran.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58052-2021 tillsynsbegäran mail.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 58551-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45251</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58551-2023 artfynd.xlsx", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58551-2023 karta.png", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58551-2023 georefererad karta.tif", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58551-2023 FSC-klagomål.docx", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58551-2023 FSC-klagomål mail.docx", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58551-2023 tillsynsbegäran.docx", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58551-2023 tillsynsbegäran mail.docx", "A 58551-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 50774-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Mörk dunört</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 50774-2023 artfynd.xlsx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 50774-2023 karta.png", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 50774-2023 georefererad karta.tif", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 50774-2023 FSC-klagomål.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 50774-2023 FSC-klagomål mail.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 50774-2023 tillsynsbegäran.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 50774-2023 tillsynsbegäran mail.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 15437-2025</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45747</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 15437-2025 artfynd.xlsx", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 15437-2025 karta.png", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 15437-2025 georefererad karta.tif", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/knärot/A 15437-2025 karta knärot.png", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 15437-2025 FSC-klagomål.docx", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 15437-2025 FSC-klagomål mail.docx", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 15437-2025 tillsynsbegäran.docx", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 15437-2025 tillsynsbegäran mail.docx", "A 15437-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 32713-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45516</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Kristinspindling</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32713-2024 artfynd.xlsx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32713-2024 karta.png", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32713-2024 georefererad karta.tif", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32713-2024 FSC-klagomål.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32713-2024 FSC-klagomål mail.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32713-2024 tillsynsbegäran.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32713-2024 tillsynsbegäran mail.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1920,7 +1925,7 @@
         <v>45272</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2013,7 +2018,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 38720-2023</t>
+          <t>A 32776-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2023,14 +2028,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45163</v>
+        <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2043,20 +2048,20 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
@@ -2067,10 +2072,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2083,35 +2088,35 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Hässleklocka</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 38720-2023 artfynd.xlsx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32776-2025 artfynd.xlsx", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 38720-2023 karta.png", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32776-2025 karta.png", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 38720-2023 georefererad karta.tif", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32776-2025 georefererad karta.tif", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 38720-2023 FSC-klagomål.docx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32776-2025 FSC-klagomål.docx", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 38720-2023 FSC-klagomål mail.docx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32776-2025 FSC-klagomål mail.docx", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 38720-2023 tillsynsbegäran.docx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32776-2025 tillsynsbegäran.docx", "A 32776-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 38720-2023 tillsynsbegäran mail.docx", "A 38720-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32776-2025 tillsynsbegäran mail.docx", "A 32776-2025")</f>
         <v/>
       </c>
     </row>
@@ -2135,7 +2140,7 @@
         <v>45243</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2223,7 +2228,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 58052-2021</t>
+          <t>A 50774-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2237,10 +2242,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44487</v>
+        <v>45210</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2252,23 +2257,18 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>4.3</v>
+        <v>9.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2298,42 +2298,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mörk dunört</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58052-2021 artfynd.xlsx", "A 58052-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 50774-2023 artfynd.xlsx", "A 50774-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58052-2021 karta.png", "A 58052-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 50774-2023 karta.png", "A 50774-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58052-2021 georefererad karta.tif", "A 58052-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 50774-2023 georefererad karta.tif", "A 50774-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58052-2021 FSC-klagomål.docx", "A 58052-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 50774-2023 FSC-klagomål.docx", "A 50774-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58052-2021 FSC-klagomål mail.docx", "A 58052-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 50774-2023 FSC-klagomål mail.docx", "A 50774-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58052-2021 tillsynsbegäran.docx", "A 58052-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 50774-2023 tillsynsbegäran.docx", "A 50774-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58052-2021 tillsynsbegäran mail.docx", "A 58052-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 50774-2023 tillsynsbegäran mail.docx", "A 50774-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 4772-2022</t>
+          <t>A 38720-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44592</v>
+        <v>45163</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2363,13 +2363,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2378,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2387,10 +2387,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2399,46 +2399,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Hässleklocka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 4772-2022 artfynd.xlsx", "A 4772-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 38720-2023 artfynd.xlsx", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 4772-2022 karta.png", "A 4772-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 38720-2023 karta.png", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 4772-2022 georefererad karta.tif", "A 4772-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 38720-2023 georefererad karta.tif", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 4772-2022 FSC-klagomål.docx", "A 4772-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 38720-2023 FSC-klagomål.docx", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 4772-2022 FSC-klagomål mail.docx", "A 4772-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 38720-2023 FSC-klagomål mail.docx", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 4772-2022 tillsynsbegäran.docx", "A 4772-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 38720-2023 tillsynsbegäran.docx", "A 38720-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 4772-2022 tillsynsbegäran mail.docx", "A 4772-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 38720-2023 tillsynsbegäran mail.docx", "A 38720-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32776-2025</t>
+          <t>A 32713-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2448,14 +2448,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45839</v>
+        <v>45516</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>6.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2504,39 +2504,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Kristinspindling</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32776-2025 artfynd.xlsx", "A 32776-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32713-2024 artfynd.xlsx", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32776-2025 karta.png", "A 32776-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32713-2024 karta.png", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32776-2025 georefererad karta.tif", "A 32776-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32713-2024 georefererad karta.tif", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32776-2025 FSC-klagomål.docx", "A 32776-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32713-2024 FSC-klagomål.docx", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32776-2025 FSC-klagomål mail.docx", "A 32776-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32713-2024 FSC-klagomål mail.docx", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32776-2025 tillsynsbegäran.docx", "A 32776-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32713-2024 tillsynsbegäran.docx", "A 32713-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32776-2025 tillsynsbegäran mail.docx", "A 32776-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32713-2024 tillsynsbegäran mail.docx", "A 32713-2024")</f>
         <v/>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
         <v>44509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44538</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>44614</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>44803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>44510</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44504</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44517</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>44666</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>44756</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>44796</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 6705-2024</t>
+          <t>A 36114-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45342</v>
+        <v>44803</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3526,13 +3526,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>8.300000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3575,7 +3570,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 36114-2022</t>
+          <t>A 47600-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3589,10 +3584,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44803</v>
+        <v>45203</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3605,7 +3600,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3648,7 +3643,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 35661-2024</t>
+          <t>A 15906-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3658,14 +3653,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45532</v>
+        <v>45405</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3678,7 +3673,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3721,7 +3716,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 5819-2024</t>
+          <t>A 64015-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3731,14 +3726,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45335</v>
+        <v>46021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3756,7 +3751,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3799,7 +3794,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3198-2024</t>
+          <t>A 64010-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3813,10 +3808,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45316</v>
+        <v>46021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3828,8 +3823,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>15.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3872,7 +3872,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 22088-2023</t>
+          <t>A 602-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45069</v>
+        <v>46029</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3945,7 +3945,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8256-2023</t>
+          <t>A 21336-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3955,14 +3955,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44974</v>
+        <v>45782</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4018,7 +4018,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 15790-2025</t>
+          <t>A 30389-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45748</v>
+        <v>45491</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4091,7 +4091,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 26949-2023</t>
+          <t>A 1578-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45093</v>
+        <v>44937</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 15813-2022</t>
+          <t>A 1589-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4174,14 +4174,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44664</v>
+        <v>46034</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4195,11 +4195,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4242,7 +4242,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38152-2023</t>
+          <t>A 1279-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4256,10 +4256,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45161</v>
+        <v>46031</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 56841-2022</t>
+          <t>A 1264-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44894</v>
+        <v>46031</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4388,7 +4388,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 44069-2023</t>
+          <t>A 54226-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45188</v>
+        <v>44470</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1578-2023</t>
+          <t>A 48325-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4471,14 +4471,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44937</v>
+        <v>44858</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4490,8 +4490,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4534,7 +4539,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11280-2025</t>
+          <t>A 47993-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4548,10 +4553,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45726</v>
+        <v>45589</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4564,7 +4569,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4607,7 +4612,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 15909-2024</t>
+          <t>A 1585-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4617,14 +4622,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45405</v>
+        <v>46034</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4636,8 +4641,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.1</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4680,7 +4690,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 39032-2023</t>
+          <t>A 1273-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4694,10 +4704,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45163</v>
+        <v>46031</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4709,13 +4719,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4758,7 +4763,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 45973-2024</t>
+          <t>A 64802-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4768,14 +4773,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45580</v>
+        <v>44512</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4788,7 +4793,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4831,7 +4836,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9448-2023</t>
+          <t>A 1261-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4845,10 +4850,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44981</v>
+        <v>46031</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4861,7 +4866,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4904,7 +4909,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 39920-2024</t>
+          <t>A 1268-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4918,10 +4923,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45553</v>
+        <v>46031</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4934,7 +4939,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4977,7 +4982,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 54226-2021</t>
+          <t>A 6164-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4991,10 +4996,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44470</v>
+        <v>45337</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5007,7 +5012,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5050,7 +5055,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 46528-2024</t>
+          <t>A 6705-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5064,10 +5069,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45582</v>
+        <v>45342</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5079,8 +5084,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5123,7 +5133,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 36075-2023</t>
+          <t>A 35661-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5137,10 +5147,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45149</v>
+        <v>45532</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5153,7 +5163,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5196,7 +5206,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 1674-2023</t>
+          <t>A 56841-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5210,10 +5220,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44938</v>
+        <v>44894</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5226,7 +5236,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5269,7 +5279,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 35079-2023</t>
+          <t>A 1323-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5283,10 +5293,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45145</v>
+        <v>44936</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5299,7 +5309,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5342,7 +5352,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 6421-2025</t>
+          <t>A 32335-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5356,10 +5366,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45699</v>
+        <v>45512</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5372,7 +5382,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5415,7 +5425,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 6456-2025</t>
+          <t>A 41730-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5429,10 +5439,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45699</v>
+        <v>45902</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5445,7 +5455,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5488,7 +5498,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17618-2024</t>
+          <t>A 30388-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5502,10 +5512,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45416</v>
+        <v>45491</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5518,7 +5528,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5561,7 +5571,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 47993-2024</t>
+          <t>A 3149-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5575,10 +5585,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45589</v>
+        <v>45316</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5591,7 +5601,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5634,7 +5644,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 5513-2025</t>
+          <t>A 47597-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5648,10 +5658,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45693</v>
+        <v>45203</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5664,7 +5674,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5707,7 +5717,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 38259-2023</t>
+          <t>A 15907-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5717,14 +5727,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45161</v>
+        <v>45405</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5737,7 +5747,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5780,7 +5790,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 13129-2023</t>
+          <t>A 15915-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5790,14 +5800,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45002</v>
+        <v>45405</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5810,7 +5820,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5853,7 +5863,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 6164-2024</t>
+          <t>A 7375-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5867,10 +5877,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45337</v>
+        <v>46059</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5883,7 +5893,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5926,7 +5936,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 14156-2023</t>
+          <t>A 17618-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5940,10 +5950,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45009</v>
+        <v>45416</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5956,7 +5966,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5999,7 +6009,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 16270-2024</t>
+          <t>A 8118-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6013,10 +6023,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45407</v>
+        <v>46062</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6029,7 +6039,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>13.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6072,7 +6082,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 35411-2023</t>
+          <t>A 13129-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6086,10 +6096,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45146</v>
+        <v>45002</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6102,7 +6112,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6145,7 +6155,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 20244-2022</t>
+          <t>A 5283-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6159,10 +6169,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44698</v>
+        <v>45331</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6174,13 +6184,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>9.5</v>
+        <v>3.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6223,7 +6228,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 6557-2025</t>
+          <t>A 14750-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6237,10 +6242,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45699</v>
+        <v>45014</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6253,7 +6258,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6296,7 +6301,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 32378-2024</t>
+          <t>A 46059-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6310,10 +6315,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45512</v>
+        <v>45924</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6326,7 +6331,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6369,7 +6374,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 19351-2023</t>
+          <t>A 46788-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6383,10 +6388,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45049</v>
+        <v>45926</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6399,7 +6404,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6442,7 +6447,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 32335-2024</t>
+          <t>A 14156-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6456,10 +6461,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45512</v>
+        <v>45009</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6472,7 +6477,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6515,7 +6520,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 8515-2022</t>
+          <t>A 46778-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6529,10 +6534,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44613</v>
+        <v>45926</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6545,7 +6550,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6588,7 +6593,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 61880-2021</t>
+          <t>A 46999-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6602,10 +6607,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44502</v>
+        <v>45929</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6618,7 +6623,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6661,7 +6666,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 33375-2024</t>
+          <t>A 48063-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6675,10 +6680,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45519</v>
+        <v>45932</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6690,13 +6695,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6739,7 +6739,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 41730-2025</t>
+          <t>A 47648-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45902</v>
+        <v>45931</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6812,7 +6812,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 43263-2023</t>
+          <t>A 46528-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6822,14 +6822,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45183</v>
+        <v>45582</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6885,7 +6885,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 46536-2024</t>
+          <t>A 48575-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45582</v>
+        <v>45936</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6958,7 +6958,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 39024-2023</t>
+          <t>A 48611-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45163</v>
+        <v>45936</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6987,13 +6987,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7036,7 +7031,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 38212-2023</t>
+          <t>A 48614-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7050,10 +7045,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45161</v>
+        <v>45936</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7066,7 +7061,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7109,7 +7104,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3130-2025</t>
+          <t>A 8256-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7119,14 +7114,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45678</v>
+        <v>44974</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7138,13 +7133,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>18.6</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7187,7 +7177,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 39027-2023</t>
+          <t>A 12859-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7201,10 +7191,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45163</v>
+        <v>46092</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7216,13 +7206,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7265,7 +7250,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 15907-2024</t>
+          <t>A 12872-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7275,14 +7260,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45405</v>
+        <v>46092</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7295,7 +7280,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7338,7 +7323,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 15915-2024</t>
+          <t>A 22088-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7348,14 +7333,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45405</v>
+        <v>45069</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7368,7 +7353,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7411,7 +7396,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 20232-2022</t>
+          <t>A 50416-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7425,10 +7410,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44698</v>
+        <v>45944</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7440,13 +7425,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7489,7 +7469,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 46059-2025</t>
+          <t>A 36099-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7503,10 +7483,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45924</v>
+        <v>45533</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7519,7 +7499,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7562,7 +7542,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 46778-2025</t>
+          <t>A 14736-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7572,14 +7552,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45926</v>
+        <v>45397</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7592,7 +7572,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7635,7 +7615,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 46999-2025</t>
+          <t>A 14617-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7649,10 +7629,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45929</v>
+        <v>46101</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7665,7 +7645,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7708,7 +7688,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 46788-2025</t>
+          <t>A 51171-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7722,10 +7702,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45926</v>
+        <v>45947</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7738,7 +7718,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7781,7 +7761,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 47648-2025</t>
+          <t>A 51328-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7795,10 +7775,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45931</v>
+        <v>45950</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7811,7 +7791,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7854,7 +7834,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 48063-2025</t>
+          <t>A 20232-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7868,10 +7848,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45932</v>
+        <v>44698</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7883,8 +7863,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7927,7 +7912,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 8063-2025</t>
+          <t>A 14185-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7941,10 +7926,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45707</v>
+        <v>45009</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7957,7 +7942,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8000,7 +7985,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 5350-2025</t>
+          <t>A 16341-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8014,10 +7999,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45692</v>
+        <v>46111</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8029,8 +8014,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8073,7 +8063,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 32715-2024</t>
+          <t>A 16402-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8087,10 +8077,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45516</v>
+        <v>46111</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8102,8 +8092,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8146,7 +8141,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 48611-2025</t>
+          <t>A 16414-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8160,10 +8155,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45936</v>
+        <v>46111</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8175,8 +8170,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8219,7 +8219,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48614-2025</t>
+          <t>A 16370-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8233,10 +8233,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45936</v>
+        <v>46111</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8248,8 +8248,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>6.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8292,7 +8297,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 48575-2025</t>
+          <t>A 14166-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8306,10 +8311,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45936</v>
+        <v>45009</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8322,7 +8327,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8365,7 +8370,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 6465-2025</t>
+          <t>A 19350-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8379,10 +8384,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45699</v>
+        <v>45049</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8395,7 +8400,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8438,7 +8443,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 1749-2025</t>
+          <t>A 11972-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8452,10 +8457,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45671</v>
+        <v>44994</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8468,7 +8473,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8511,7 +8516,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 50416-2025</t>
+          <t>A 20720-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8525,10 +8530,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45944</v>
+        <v>45776</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8541,7 +8546,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8584,7 +8589,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 51171-2025</t>
+          <t>A 55908-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8598,10 +8603,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45947</v>
+        <v>45973</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8614,7 +8619,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8657,7 +8662,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 51328-2025</t>
+          <t>A 55901-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8671,10 +8676,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45950</v>
+        <v>45973</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8687,7 +8692,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>6</v>
+        <v>0.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8730,7 +8735,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 17126-2024</t>
+          <t>A 55906-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8744,10 +8749,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45412</v>
+        <v>45973</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8760,7 +8765,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8803,7 +8808,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 4678-2024</t>
+          <t>A 16259-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8817,10 +8822,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45328</v>
+        <v>46109</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8833,7 +8838,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8876,7 +8881,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 21771-2023</t>
+          <t>A 16262-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8890,10 +8895,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45065</v>
+        <v>46109</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8906,7 +8911,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8949,7 +8954,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 64802-2021</t>
+          <t>A 54419-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8959,14 +8964,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44512</v>
+        <v>45617</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8978,8 +8983,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>2.5</v>
+        <v>22.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9022,7 +9032,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 20720-2025</t>
+          <t>A 17950-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9036,10 +9046,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45776</v>
+        <v>46122</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9052,7 +9062,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9095,7 +9105,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 55901-2025</t>
+          <t>A 39032-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9109,10 +9119,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45973</v>
+        <v>45163</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9124,8 +9134,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9168,7 +9183,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 55906-2025</t>
+          <t>A 14993-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9182,10 +9197,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45973</v>
+        <v>45015</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9198,7 +9213,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9241,7 +9256,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 16128-2025</t>
+          <t>A 39027-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9255,10 +9270,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45750</v>
+        <v>45163</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9276,7 +9291,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9319,7 +9334,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 55908-2025</t>
+          <t>A 11280-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9333,10 +9348,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45973</v>
+        <v>45726</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9349,7 +9364,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9392,7 +9407,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 3149-2024</t>
+          <t>A 8049-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9406,10 +9421,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45316</v>
+        <v>45707</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9422,7 +9437,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9465,7 +9480,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 165-2026</t>
+          <t>A 61801-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9479,10 +9494,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46024</v>
+        <v>46002</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9495,7 +9510,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9538,7 +9553,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 51180-2024</t>
+          <t>A 61470-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9552,10 +9567,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45603</v>
+        <v>46001</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9567,8 +9582,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>1.3</v>
+        <v>8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9611,7 +9631,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 35229-2023</t>
+          <t>A 61798-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9625,10 +9645,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45145</v>
+        <v>46002</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9640,8 +9660,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9684,7 +9709,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 63074-2025</t>
+          <t>A 61629-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9698,10 +9723,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9713,13 +9738,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>8.699999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9762,7 +9782,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 51178-2024</t>
+          <t>A 38152-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9776,10 +9796,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45603</v>
+        <v>45161</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9792,7 +9812,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9835,7 +9855,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 19157-2023</t>
+          <t>A 62202-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9849,10 +9869,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45048</v>
+        <v>46006</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9865,7 +9885,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9908,7 +9928,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 55971-2023</t>
+          <t>A 61972-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9922,10 +9942,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45240</v>
+        <v>46003</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9937,8 +9957,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9981,7 +10006,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 63115-2025</t>
+          <t>A 8515-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9995,10 +10020,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46009</v>
+        <v>44613</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10011,7 +10036,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10054,7 +10079,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 16164-2023</t>
+          <t>A 62801-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10068,10 +10093,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45027</v>
+        <v>46008</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10083,13 +10108,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>6.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10132,7 +10152,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 39024-2023</t>
+          <t>A 62482-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10146,10 +10166,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45163</v>
+        <v>46007</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10161,13 +10181,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>4.7</v>
+        <v>6.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10210,7 +10225,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 61786-2025</t>
+          <t>A 38723-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10224,10 +10239,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46002</v>
+        <v>45163</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10240,7 +10255,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10283,7 +10298,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 61798-2025</t>
+          <t>A 3130-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10297,10 +10312,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46002</v>
+        <v>45678</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10318,7 +10333,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.2</v>
+        <v>18.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10361,7 +10376,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 61800-2025</t>
+          <t>A 63074-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10375,10 +10390,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46002</v>
+        <v>46009</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10390,8 +10405,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>2.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10434,7 +10454,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 61801-2025</t>
+          <t>A 16128-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10448,10 +10468,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46002</v>
+        <v>45750</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10463,8 +10483,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10507,7 +10532,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 61972-2025</t>
+          <t>A 165-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10521,10 +10546,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46003</v>
+        <v>46024</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10536,13 +10561,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10585,7 +10605,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 61470-2025</t>
+          <t>A 55971-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10599,10 +10619,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46001</v>
+        <v>45240</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10614,13 +10634,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>8</v>
+        <v>0.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10663,7 +10678,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 61629-2025</t>
+          <t>A 30945-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10677,10 +10692,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46002</v>
+        <v>45113</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10693,7 +10708,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10736,7 +10751,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 47597-2023</t>
+          <t>A 16164-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10750,10 +10765,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45203</v>
+        <v>45027</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10763,6 +10778,11 @@
       <c r="G131" t="inlineStr">
         <is>
           <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I131" t="n">
@@ -10809,7 +10829,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 62482-2025</t>
+          <t>A 5350-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10823,10 +10843,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46007</v>
+        <v>45692</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10839,7 +10859,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>6.7</v>
+        <v>2.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10882,7 +10902,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 62202-2025</t>
+          <t>A 30964-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10896,10 +10916,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46006</v>
+        <v>45113</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10912,7 +10932,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10955,7 +10975,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 62801-2025</t>
+          <t>A 30600-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10969,10 +10989,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46008</v>
+        <v>45831</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10985,7 +11005,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11028,7 +11048,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 14166-2023</t>
+          <t>A 21770-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11042,10 +11062,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45009</v>
+        <v>45065</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11058,7 +11078,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11101,7 +11121,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 15344-2025</t>
+          <t>A 19351-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11115,10 +11135,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45747</v>
+        <v>45049</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11131,7 +11151,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11174,7 +11194,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 10335-2022</t>
+          <t>A 38266-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11188,10 +11208,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44623</v>
+        <v>44812</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11204,7 +11224,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11247,7 +11267,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 35095-2023</t>
+          <t>A 32476-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11261,10 +11281,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45145</v>
+        <v>45838</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11277,7 +11297,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11320,7 +11340,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 20612-2022</t>
+          <t>A 63115-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11334,10 +11354,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44700</v>
+        <v>46009</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11349,13 +11369,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>8.9</v>
+        <v>3.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11398,7 +11413,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 64010-2025</t>
+          <t>A 32466-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11412,10 +11427,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46021</v>
+        <v>45838</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11427,13 +11442,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>15.4</v>
+        <v>0.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11476,7 +11486,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 64015-2025</t>
+          <t>A 21771-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11490,10 +11500,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46021</v>
+        <v>45065</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11505,13 +11515,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11554,7 +11559,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 15198-2022</t>
+          <t>A 61011-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11564,14 +11569,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44658</v>
+        <v>45645</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11584,7 +11589,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11627,7 +11632,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 602-2026</t>
+          <t>A 1337-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11641,10 +11646,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11657,7 +11662,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11700,7 +11705,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 6375-2025</t>
+          <t>A 8067-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11714,10 +11719,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45699</v>
+        <v>45707</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11730,7 +11735,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11773,7 +11778,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 6592-2025</t>
+          <t>A 32464-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11787,10 +11792,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45700</v>
+        <v>45838</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11803,7 +11808,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11846,7 +11851,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 37843-2023</t>
+          <t>A 35079-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11860,10 +11865,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45160</v>
+        <v>45145</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11876,7 +11881,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11919,7 +11924,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 1279-2026</t>
+          <t>A 45973-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11933,10 +11938,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46031</v>
+        <v>45580</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11949,7 +11954,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11992,7 +11997,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 1261-2026</t>
+          <t>A 35229-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12006,10 +12011,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46031</v>
+        <v>45145</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12022,7 +12027,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12065,7 +12070,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 1268-2026</t>
+          <t>A 5819-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12075,14 +12080,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46031</v>
+        <v>45335</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12094,8 +12099,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12138,7 +12148,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 1264-2026</t>
+          <t>A 61880-2021</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12152,10 +12162,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46031</v>
+        <v>44502</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12168,7 +12178,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12211,7 +12221,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 1273-2026</t>
+          <t>A 38212-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12225,10 +12235,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46031</v>
+        <v>45161</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12241,7 +12251,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12284,7 +12294,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 1585-2026</t>
+          <t>A 25895-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12298,10 +12308,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46034</v>
+        <v>46178</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12313,13 +12323,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12362,7 +12367,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 1589-2026</t>
+          <t>A 25816-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12376,10 +12381,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46034</v>
+        <v>46178</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12391,13 +12396,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12440,7 +12440,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 6506-2025</t>
+          <t>A 27087-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12454,10 +12454,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45699</v>
+        <v>45471</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12513,7 +12513,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 61011-2024</t>
+          <t>A 25863-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12523,14 +12523,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45645</v>
+        <v>46178</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12586,7 +12586,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 1337-2026</t>
+          <t>A 25975-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12600,10 +12600,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46031</v>
+        <v>46181</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12659,7 +12659,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 32464-2025</t>
+          <t>A 39920-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12673,10 +12673,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45838</v>
+        <v>45553</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12732,7 +12732,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 8067-2025</t>
+          <t>A 46536-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12746,10 +12746,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45707</v>
+        <v>45582</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12805,7 +12805,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 5283-2024</t>
+          <t>A 27292-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12819,10 +12819,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45331</v>
+        <v>46184</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12835,7 +12835,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12878,7 +12878,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 7375-2026</t>
+          <t>A 4678-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12892,10 +12892,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46059</v>
+        <v>45328</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12951,7 +12951,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 38723-2023</t>
+          <t>A 35095-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12965,10 +12965,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45163</v>
+        <v>45145</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 50387-2024</t>
+          <t>A 1749-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13038,10 +13038,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45600</v>
+        <v>45671</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>8.5</v>
+        <v>1.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13097,7 +13097,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 2512-2024</t>
+          <t>A 15909-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13107,14 +13107,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45313</v>
+        <v>45405</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13170,7 +13170,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 8118-2026</t>
+          <t>A 6375-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13184,10 +13184,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46062</v>
+        <v>45699</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>13.4</v>
+        <v>1.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13243,7 +13243,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 64709-2023</t>
+          <t>A 32378-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13257,10 +13257,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45281</v>
+        <v>45512</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13316,7 +13316,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 64710-2023</t>
+          <t>A 28908-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13330,10 +13330,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45281</v>
+        <v>46199</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.1</v>
+        <v>5.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13389,7 +13389,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 36730-2023</t>
+          <t>A 28704-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13403,10 +13403,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45153</v>
+        <v>46198</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13418,8 +13418,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13462,7 +13467,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 16168-2023</t>
+          <t>A 28718-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13476,10 +13481,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45027</v>
+        <v>46198</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13497,7 +13502,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13540,7 +13545,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 21770-2023</t>
+          <t>A 51180-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13554,10 +13559,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45065</v>
+        <v>45603</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13570,7 +13575,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13613,7 +13618,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 36099-2024</t>
+          <t>A 39024-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13627,10 +13632,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45533</v>
+        <v>45163</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13642,8 +13647,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13686,7 +13696,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 12872-2026</t>
+          <t>A 39190-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13696,14 +13706,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46092</v>
+        <v>45166</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13716,7 +13726,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13759,7 +13769,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 12859-2026</t>
+          <t>A 30155-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13773,10 +13783,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46092</v>
+        <v>46206</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13788,8 +13798,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13832,7 +13847,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 38718-2023</t>
+          <t>A 16168-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13846,10 +13861,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45163</v>
+        <v>45027</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13861,8 +13876,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13905,7 +13925,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 25895-2026</t>
+          <t>A 38718-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13919,10 +13939,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46178</v>
+        <v>45163</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13935,7 +13955,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13978,7 +13998,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 15906-2024</t>
+          <t>A 2512-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13988,14 +14008,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45405</v>
+        <v>45313</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14008,7 +14028,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.2</v>
+        <v>5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14051,7 +14071,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 25863-2026</t>
+          <t>A 51178-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14065,10 +14085,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46178</v>
+        <v>45603</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14124,7 +14144,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 25816-2026</t>
+          <t>A 35380-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14138,10 +14158,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46178</v>
+        <v>45146</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14154,7 +14174,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14197,7 +14217,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 25975-2026</t>
+          <t>A 6592-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14211,10 +14231,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46181</v>
+        <v>45700</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14227,7 +14247,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14270,7 +14290,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 14617-2026</t>
+          <t>A 43263-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14280,14 +14300,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46101</v>
+        <v>45183</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14300,7 +14320,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14343,7 +14363,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 27274-2026</t>
+          <t>A 20244-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14357,10 +14377,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46184</v>
+        <v>44698</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14372,8 +14392,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14416,7 +14441,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 27292-2026</t>
+          <t>A 50358-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14430,10 +14455,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46184</v>
+        <v>45944</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14446,7 +14471,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14489,7 +14514,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 35097-2023</t>
+          <t>A 20612-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14503,10 +14528,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45145</v>
+        <v>44700</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14518,8 +14543,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>1</v>
+        <v>8.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14562,7 +14592,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 16370-2026</t>
+          <t>A 6421-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14576,10 +14606,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46111</v>
+        <v>45699</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14591,13 +14621,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>6.9</v>
+        <v>1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14640,7 +14665,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 16414-2026</t>
+          <t>A 52469-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14654,10 +14679,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46111</v>
+        <v>45225</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14669,13 +14694,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>8.199999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14718,7 +14738,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 30945-2023</t>
+          <t>A 8063-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14732,10 +14752,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45113</v>
+        <v>45707</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14748,7 +14768,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14791,7 +14811,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 30964-2023</t>
+          <t>A 15790-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14805,10 +14825,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45113</v>
+        <v>45748</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14821,7 +14841,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14864,7 +14884,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 16402-2026</t>
+          <t>A 31447-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14878,10 +14898,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46111</v>
+        <v>46220</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14893,13 +14913,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14942,7 +14957,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 16341-2026</t>
+          <t>A 37843-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14956,10 +14971,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46111</v>
+        <v>45160</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14971,13 +14986,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15020,7 +15030,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 16259-2026</t>
+          <t>A 6465-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15034,10 +15044,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46109</v>
+        <v>45699</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15050,7 +15060,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15093,7 +15103,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 16262-2026</t>
+          <t>A 1674-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15107,10 +15117,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46109</v>
+        <v>44938</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15123,7 +15133,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15166,7 +15176,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 17950-2026</t>
+          <t>A 34961-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15180,10 +15190,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46122</v>
+        <v>44796</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15196,7 +15206,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15239,7 +15249,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 48325-2022</t>
+          <t>A 19157-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15249,14 +15259,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44858</v>
+        <v>45048</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15268,13 +15278,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15317,7 +15322,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 11699-2024</t>
+          <t>A 36824-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15331,10 +15336,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45373</v>
+        <v>46272</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15346,8 +15351,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>2.4</v>
+        <v>8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15390,7 +15400,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 11704-2024</t>
+          <t>A 37473-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15404,10 +15414,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45373</v>
+        <v>46275</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15420,7 +15430,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15463,7 +15473,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 28718-2026</t>
+          <t>A 37482-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15477,10 +15487,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46198</v>
+        <v>46275</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15498,7 +15508,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2</v>
+        <v>16.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15541,7 +15551,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 28704-2026</t>
+          <t>A 37469-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15555,10 +15565,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46198</v>
+        <v>46275</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15570,13 +15580,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15619,7 +15624,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 11193-2023</t>
+          <t>A 37991-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15629,14 +15634,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44992</v>
+        <v>46280</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15649,7 +15654,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15692,7 +15697,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 8049-2025</t>
+          <t>A 39024-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15706,10 +15711,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45707</v>
+        <v>45163</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15721,8 +15726,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15765,7 +15775,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 28908-2026</t>
+          <t>A 17126-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15779,10 +15789,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46199</v>
+        <v>45412</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15795,7 +15805,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15838,7 +15848,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 30389-2024</t>
+          <t>A 11193-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15848,14 +15858,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45491</v>
+        <v>44992</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15868,7 +15878,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>5.6</v>
+        <v>2.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15911,7 +15921,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 35380-2023</t>
+          <t>A 26949-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15925,10 +15935,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45146</v>
+        <v>45093</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15941,7 +15951,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15984,7 +15994,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 54419-2024</t>
+          <t>A 39658-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -15998,10 +16008,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45617</v>
+        <v>46289</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16013,13 +16023,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>22.7</v>
+        <v>1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16062,7 +16067,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 34961-2022</t>
+          <t>A 37494-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16076,10 +16081,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44796</v>
+        <v>46275</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16092,7 +16097,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16135,7 +16140,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 14185-2023</t>
+          <t>A 6506-2025</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16149,10 +16154,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45009</v>
+        <v>45699</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16165,7 +16170,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16208,7 +16213,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 27087-2024</t>
+          <t>A 12332-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16222,10 +16227,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45471</v>
+        <v>44999</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16238,7 +16243,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16281,7 +16286,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 30155-2026</t>
+          <t>A 36075-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16295,10 +16300,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46206</v>
+        <v>45149</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16310,13 +16315,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16359,7 +16359,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 6368-2025</t>
+          <t>A 15198-2022</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16373,10 +16373,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45699</v>
+        <v>44658</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16432,7 +16432,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 39190-2023</t>
+          <t>A 6456-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16442,14 +16442,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45166</v>
+        <v>45699</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16505,7 +16505,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 54590-2024</t>
+          <t>A 21855-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16519,10 +16519,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45617</v>
+        <v>44709</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16578,7 +16578,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 50358-2025</t>
+          <t>A 72603-2021</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16592,10 +16592,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45944</v>
+        <v>44546</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16651,7 +16651,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 14993-2023</t>
+          <t>A 9448-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16665,10 +16665,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45015</v>
+        <v>44981</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16724,7 +16724,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 52469-2023</t>
+          <t>A 64709-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16738,10 +16738,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45225</v>
+        <v>45281</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 19350-2023</t>
+          <t>A 64710-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16811,10 +16811,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45049</v>
+        <v>45281</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16870,7 +16870,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 51041-2024</t>
+          <t>A 35097-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16884,10 +16884,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45603</v>
+        <v>45145</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 31447-2026</t>
+          <t>A 35411-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16957,10 +16957,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46220</v>
+        <v>45146</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17016,7 +17016,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 11972-2023</t>
+          <t>A 36730-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17030,10 +17030,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44994</v>
+        <v>45153</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17089,7 +17089,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 12332-2023</t>
+          <t>A 25729-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17103,10 +17103,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44999</v>
+        <v>45084</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17162,7 +17162,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 38266-2022</t>
+          <t>A 11699-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17176,10 +17176,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44812</v>
+        <v>45373</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 36824-2026</t>
+          <t>A 11704-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17249,10 +17249,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46272</v>
+        <v>45373</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17264,13 +17264,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17313,7 +17308,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 1323-2023</t>
+          <t>A 54590-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17327,10 +17322,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44936</v>
+        <v>45617</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17343,7 +17338,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17386,7 +17381,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 14736-2024</t>
+          <t>A 10335-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17396,14 +17391,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45397</v>
+        <v>44623</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17416,7 +17411,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17459,7 +17454,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 25729-2023</t>
+          <t>A 33375-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17473,10 +17468,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45084</v>
+        <v>45519</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17488,8 +17483,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 37482-2026</t>
+          <t>A 5513-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17546,10 +17546,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46275</v>
+        <v>45693</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17561,13 +17561,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>16.5</v>
+        <v>0.7</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17610,7 +17605,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 37473-2026</t>
+          <t>A 15813-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17620,14 +17615,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46275</v>
+        <v>44664</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17639,8 +17634,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17683,7 +17683,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 37469-2026</t>
+          <t>A 6368-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17697,10 +17697,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46275</v>
+        <v>45699</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17756,7 +17756,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 30388-2024</t>
+          <t>A 44069-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17770,10 +17770,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45491</v>
+        <v>45188</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17829,7 +17829,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 21855-2022</t>
+          <t>A 3198-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17843,10 +17843,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44709</v>
+        <v>45316</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17902,7 +17902,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 72603-2021</t>
+          <t>A 16270-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17916,10 +17916,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44546</v>
+        <v>45407</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17975,7 +17975,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 37991-2026</t>
+          <t>A 51041-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17989,10 +17989,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46280</v>
+        <v>45603</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>4.9</v>
+        <v>0.4</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18048,7 +18048,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 14750-2023</t>
+          <t>A 6557-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18062,10 +18062,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45014</v>
+        <v>45699</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18121,7 +18121,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 47600-2023</t>
+          <t>A 15344-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18135,10 +18135,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45203</v>
+        <v>45747</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18194,7 +18194,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 21357-2025</t>
+          <t>A 50387-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18208,10 +18208,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45782</v>
+        <v>45600</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.9</v>
+        <v>8.5</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18267,7 +18267,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 21530-2025</t>
+          <t>A 32715-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18281,10 +18281,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45782</v>
+        <v>45516</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18340,7 +18340,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 3554-2025</t>
+          <t>A 38259-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18354,10 +18354,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45680</v>
+        <v>45161</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18413,7 +18413,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 50818-2023</t>
+          <t>A 21530-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18427,10 +18427,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45217</v>
+        <v>45782</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18486,7 +18486,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 21336-2025</t>
+          <t>A 21357-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18503,7 +18503,7 @@
         <v>45782</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 37494-2026</t>
+          <t>A 3554-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18573,10 +18573,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>46275</v>
+        <v>45680</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18632,7 +18632,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 30600-2025</t>
+          <t>A 50818-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18646,10 +18646,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45831</v>
+        <v>45217</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18705,24 +18705,24 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 32466-2025</t>
+          <t>S 899-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45838</v>
+        <v>45376</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>0.5</v>
+        <v>18</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18775,27 +18775,27 @@
       </c>
       <c r="V239" s="2" t="inlineStr"/>
     </row>
-    <row r="240" ht="15" customHeight="1">
+    <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 32476-2025</t>
+          <t>S 6457-2022</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45838</v>
+        <v>44879</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18807,8 +18807,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I240" t="n">
-        <v>0.7</v>
+        <v>101.8</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18847,157 +18852,6 @@
         <v>0</v>
       </c>
       <c r="V240" s="2" t="inlineStr"/>
-    </row>
-    <row r="241" ht="15" customHeight="1">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>S 899-2024</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D241" s="1" t="n">
-        <v>45376</v>
-      </c>
-      <c r="E241" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I241" t="n">
-        <v>18</v>
-      </c>
-      <c r="J241" t="n">
-        <v>0</v>
-      </c>
-      <c r="K241" t="n">
-        <v>0</v>
-      </c>
-      <c r="L241" t="n">
-        <v>0</v>
-      </c>
-      <c r="M241" t="n">
-        <v>0</v>
-      </c>
-      <c r="N241" t="n">
-        <v>0</v>
-      </c>
-      <c r="O241" t="n">
-        <v>0</v>
-      </c>
-      <c r="P241" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
-      <c r="R241" t="n">
-        <v>0</v>
-      </c>
-      <c r="S241" t="n">
-        <v>0</v>
-      </c>
-      <c r="T241" t="n">
-        <v>0</v>
-      </c>
-      <c r="U241" t="n">
-        <v>0</v>
-      </c>
-      <c r="V241" s="2" t="inlineStr"/>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>S 6457-2022</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D242" s="1" t="n">
-        <v>44879</v>
-      </c>
-      <c r="E242" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I242" t="n">
-        <v>101.8</v>
-      </c>
-      <c r="J242" t="n">
-        <v>0</v>
-      </c>
-      <c r="K242" t="n">
-        <v>0</v>
-      </c>
-      <c r="L242" t="n">
-        <v>0</v>
-      </c>
-      <c r="M242" t="n">
-        <v>0</v>
-      </c>
-      <c r="N242" t="n">
-        <v>0</v>
-      </c>
-      <c r="O242" t="n">
-        <v>0</v>
-      </c>
-      <c r="P242" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
-      <c r="R242" t="n">
-        <v>0</v>
-      </c>
-      <c r="S242" t="n">
-        <v>0</v>
-      </c>
-      <c r="T242" t="n">
-        <v>0</v>
-      </c>
-      <c r="U242" t="n">
-        <v>0</v>
-      </c>
-      <c r="V242" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÖDESHÖG.xlsx
+++ b/Översikt ÖDESHÖG.xlsx
@@ -601,7 +601,7 @@
         <v>45805</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45723</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44698</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>44664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>44798</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>45244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>44538</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>45747</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>44592</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>44487</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>45251</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>45272</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45243</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45210</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>45163</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>45516</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44538</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>44614</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>44803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>44510</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44504</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44517</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>44666</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>44756</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>44796</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44803</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>45203</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>45405</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>46021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>46021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>46029</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45782</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>45491</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>44937</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>46034</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46031</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>46031</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>44470</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44858</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>45589</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>46034</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>46031</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>44512</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>46031</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>46031</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>45337</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>45342</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>45532</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>44894</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>44936</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>45512</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>45902</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>45491</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         <v>45316</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>45203</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>45405</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>45405</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>46059</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>45416</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>46062</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>45002</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45331</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>45014</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>45924</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>45926</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>45009</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>45926</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>45929</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>45932</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>45931</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>45582</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>45936</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>45936</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>45936</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>44974</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>46092</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>46092</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>45069</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>45944</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>45533</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>45397</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>46101</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>45947</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>45950</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>44698</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>45009</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>46111</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>46111</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>46111</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>46111</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45009</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45049</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44994</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>45776</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>45973</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>45973</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>45973</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>46109</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>46109</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45617</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>46122</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>45163</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>45015</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         <v>45163</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>45726</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>45707</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>46002</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>46001</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>46002</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>46002</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>45161</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>46006</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>46003</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>44613</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>46008</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         <v>46007</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>45163</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>45678</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>46009</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>45750</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>46024</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>45240</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>45113</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>45027</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>45692</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>45113</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>45831</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>45065</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>45049</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>44812</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>45838</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>46009</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         <v>45838</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         <v>45065</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>45645</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>46031</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>45707</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>45838</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>45145</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>45580</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>45145</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>45335</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>44502</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>45161</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>46178</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         <v>46178</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>45471</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>46178</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>46181</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>45553</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>45582</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>46184</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>45328</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>45145</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         <v>45671</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>45405</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>45699</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>45512</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>46199</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>46198</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>46198</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>45603</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>45163</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>45166</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>46206</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13864,7 +13864,7 @@
         <v>45027</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>45163</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>45313</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>45603</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>45146</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>45700</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>45183</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>44698</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>45944</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>44700</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>45699</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>45225</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>45707</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>45748</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>46220</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>45160</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>45699</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>44938</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>44796</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>45048</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>46272</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>46275</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>46275</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>46275</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>46280</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>45163</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>45412</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15865,7 +15865,7 @@
         <v>44992</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>45093</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>46289</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>46275</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>45699</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>44999</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>45149</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>44658</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>45699</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>44709</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>44546</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>44981</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16741,7 +16741,7 @@
         <v>45281</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>45281</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>45145</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>45146</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>45153</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>45084</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>45373</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>45373</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45617</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>44623</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>45519</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>45693</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>44664</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>45699</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>45188</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>45316</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45407</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>45603</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>45699</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>45747</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45600</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45516</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>45161</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45782</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>45782</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>45680</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>45217</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>45376</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>44879</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>

--- a/Översikt ÖDESHÖG.xlsx
+++ b/Översikt ÖDESHÖG.xlsx
@@ -601,7 +601,7 @@
         <v>45805</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45723</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44698</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>44664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>44798</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>45244</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>44538</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>45747</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>44592</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>44487</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>45251</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>45272</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45243</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>45210</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>45163</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>45516</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44538</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>44614</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>44803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>44510</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>44466</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>44511</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>44504</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>44517</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3295,7 +3295,7 @@
         <v>44666</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>44756</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>44796</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44803</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>45203</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>45405</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>46021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>46021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
         <v>46029</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45782</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>45491</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>44937</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>46034</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46031</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>46031</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>44470</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44858</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>45589</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>46034</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>46031</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>44512</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>46031</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>46031</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>45337</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>45342</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5150,7 +5150,7 @@
         <v>45532</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>44894</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         <v>44936</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>45512</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>45902</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>45491</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         <v>45316</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>45203</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>45405</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>45405</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>46059</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>45416</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>46062</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>45002</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6172,7 +6172,7 @@
         <v>45331</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>45014</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>45924</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>45926</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>45009</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>45926</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>45929</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>45932</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6756,7 +6756,7 @@
         <v>45931</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>45582</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>45936</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>45936</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>45936</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>44974</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>46092</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>46092</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         <v>45069</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>45944</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>45533</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>45397</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>46101</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>45947</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>45950</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>44698</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         <v>45009</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>46111</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>46111</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>46111</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>46111</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45009</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45049</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44994</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>45776</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>45973</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>45973</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>45973</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>46109</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>46109</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>45617</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>46122</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>45163</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>45015</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         <v>45163</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>45726</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>45707</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>46002</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>46001</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>46002</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9726,7 +9726,7 @@
         <v>46002</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>45161</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>46006</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>46003</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         <v>44613</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>46008</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         <v>46007</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>45163</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>45678</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>46009</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>45750</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>46024</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>45240</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>45113</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>45027</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>45692</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>45113</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>45831</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>45065</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>45049</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>44812</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>45838</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>46009</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         <v>45838</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         <v>45065</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>45645</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>46031</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>45707</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>45838</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>45145</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>45580</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>45145</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>45335</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>44502</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>45161</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>46178</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         <v>46178</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>45471</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>46178</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>46181</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>45553</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>45582</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>46184</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>45328</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>45145</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         <v>45671</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>45405</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>45699</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>45512</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>46199</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>46198</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>46198</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>45603</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>45163</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>45166</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>46206</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13864,7 +13864,7 @@
         <v>45027</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>45163</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>45313</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>45603</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>45146</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>45700</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>45183</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>44698</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>45944</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>44700</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>45699</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>45225</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>45707</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>45748</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>46220</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>45160</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>45699</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>44938</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>44796</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>45048</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>46272</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>46275</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>46275</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>46275</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>46280</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>45163</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>45412</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15865,7 +15865,7 @@
         <v>44992</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>45093</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16011,7 +16011,7 @@
         <v>46289</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>46275</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>45699</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>44999</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>45149</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>44658</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>45699</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>44709</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>44546</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>44981</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16741,7 +16741,7 @@
         <v>45281</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>45281</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>45145</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>45146</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>45153</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>45084</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>45373</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17252,7 +17252,7 @@
         <v>45373</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45617</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17398,7 +17398,7 @@
         <v>44623</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>45519</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>45693</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>44664</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>45699</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>45188</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>45316</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45407</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>45603</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>45699</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>45747</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45600</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45516</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>45161</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45782</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>45782</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>45680</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>45217</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>45376</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>44879</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>

--- a/Översikt ÖDESHÖG.xlsx
+++ b/Översikt ÖDESHÖG.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE240"/>
+  <dimension ref="A1:AE239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45805</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45723</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44698</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>44664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 35443-2022</t>
+          <t>A 56797-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1058,14 +1058,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44798</v>
+        <v>45244</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1118,149 +1118,149 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Jungfrulin
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 56797-2023 artfynd.xlsx", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 56797-2023 karta.png", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 56797-2023 georefererad karta.tif", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 56797-2023 FSC-klagomål.docx", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 56797-2023 FSC-klagomål mail.docx", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 56797-2023 tillsynsbegäran.docx", "A 56797-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 56797-2023 tillsynsbegäran mail.docx", "A 56797-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 35443-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44798</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Axveronika
 Bivråk</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 35443-2022 artfynd.xlsx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 35443-2022 karta.png", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 35443-2022 georefererad karta.tif", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 35443-2022 FSC-klagomål.docx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 35443-2022 FSC-klagomål mail.docx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 35443-2022 tillsynsbegäran.docx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 35443-2022 tillsynsbegäran mail.docx", "A 35443-2022")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/fåglar/A 35443-2022 prioriterade fågelarter.docx", "A 35443-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 56797-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45244</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 56797-2023 artfynd.xlsx", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 56797-2023 karta.png", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 56797-2023 georefererad karta.tif", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 56797-2023 FSC-klagomål.docx", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 56797-2023 FSC-klagomål mail.docx", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 56797-2023 tillsynsbegäran.docx", "A 56797-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 56797-2023 tillsynsbegäran mail.docx", "A 56797-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>44538</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 15437-2025</t>
+          <t>A 32776-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45747</v>
+        <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1503,16 +1503,11 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>11.9</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1545,1001 +1540,1006 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
+          <t>Smalsprötad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32776-2025 artfynd.xlsx", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32776-2025 karta.png", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32776-2025 georefererad karta.tif", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32776-2025 FSC-klagomål.docx", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32776-2025 FSC-klagomål mail.docx", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32776-2025 tillsynsbegäran.docx", "A 32776-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32776-2025 tillsynsbegäran mail.docx", "A 32776-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 58551-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45251</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58551-2023 artfynd.xlsx", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58551-2023 karta.png", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58551-2023 georefererad karta.tif", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58551-2023 FSC-klagomål.docx", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58551-2023 FSC-klagomål mail.docx", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58551-2023 tillsynsbegäran.docx", "A 58551-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58551-2023 tillsynsbegäran mail.docx", "A 58551-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 50774-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Mörk dunört</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 50774-2023 artfynd.xlsx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 50774-2023 karta.png", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 50774-2023 georefererad karta.tif", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 50774-2023 FSC-klagomål.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 50774-2023 FSC-klagomål mail.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 50774-2023 tillsynsbegäran.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 50774-2023 tillsynsbegäran mail.docx", "A 50774-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 15437-2025</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>Knärot</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 15437-2025 artfynd.xlsx", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 15437-2025 karta.png", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 15437-2025 georefererad karta.tif", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="Z10">
+      <c r="Z13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/knärot/A 15437-2025 karta knärot.png", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 15437-2025 FSC-klagomål.docx", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 15437-2025 FSC-klagomål mail.docx", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 15437-2025 tillsynsbegäran.docx", "A 15437-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 15437-2025 tillsynsbegäran mail.docx", "A 15437-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 32713-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45516</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Kristinspindling</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32713-2024 artfynd.xlsx", "A 32713-2024")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32713-2024 karta.png", "A 32713-2024")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32713-2024 georefererad karta.tif", "A 32713-2024")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32713-2024 FSC-klagomål.docx", "A 32713-2024")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32713-2024 FSC-klagomål mail.docx", "A 32713-2024")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32713-2024 tillsynsbegäran.docx", "A 32713-2024")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32713-2024 tillsynsbegäran mail.docx", "A 32713-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 62988-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45272</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>19</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 62988-2023 artfynd.xlsx", "A 62988-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 62988-2023 karta.png", "A 62988-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 62988-2023 georefererad karta.tif", "A 62988-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 62988-2023 FSC-klagomål.docx", "A 62988-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 62988-2023 FSC-klagomål mail.docx", "A 62988-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 62988-2023 tillsynsbegäran.docx", "A 62988-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 62988-2023 tillsynsbegäran mail.docx", "A 62988-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 38720-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Hässleklocka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 38720-2023 artfynd.xlsx", "A 38720-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 38720-2023 karta.png", "A 38720-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 38720-2023 georefererad karta.tif", "A 38720-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 38720-2023 FSC-klagomål.docx", "A 38720-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 38720-2023 FSC-klagomål mail.docx", "A 38720-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 38720-2023 tillsynsbegäran.docx", "A 38720-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 38720-2023 tillsynsbegäran mail.docx", "A 38720-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 56637-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45243</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 56637-2023 artfynd.xlsx", "A 56637-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 56637-2023 karta.png", "A 56637-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 56637-2023 georefererad karta.tif", "A 56637-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 56637-2023 FSC-klagomål.docx", "A 56637-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 56637-2023 FSC-klagomål mail.docx", "A 56637-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 56637-2023 tillsynsbegäran.docx", "A 56637-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 56637-2023 tillsynsbegäran mail.docx", "A 56637-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 58052-2021</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44487</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58052-2021 artfynd.xlsx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58052-2021 karta.png", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58052-2021 georefererad karta.tif", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58052-2021 FSC-klagomål.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58052-2021 FSC-klagomål mail.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58052-2021 tillsynsbegäran.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58052-2021 tillsynsbegäran mail.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 4772-2022</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>44592</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>1.2</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>1</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R19" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S19" t="n">
         <v>1</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T19" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 4772-2022 artfynd.xlsx", "A 4772-2022")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 4772-2022 karta.png", "A 4772-2022")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 4772-2022 georefererad karta.tif", "A 4772-2022")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 4772-2022 FSC-klagomål.docx", "A 4772-2022")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 4772-2022 FSC-klagomål mail.docx", "A 4772-2022")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 4772-2022 tillsynsbegäran.docx", "A 4772-2022")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 4772-2022 tillsynsbegäran mail.docx", "A 4772-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 58052-2021</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44487</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Granbarkgnagare</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58052-2021 artfynd.xlsx", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58052-2021 karta.png", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58052-2021 georefererad karta.tif", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58052-2021 FSC-klagomål.docx", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58052-2021 FSC-klagomål mail.docx", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58052-2021 tillsynsbegäran.docx", "A 58052-2021")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58052-2021 tillsynsbegäran mail.docx", "A 58052-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 58551-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45251</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58551-2023 artfynd.xlsx", "A 58551-2023")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58551-2023 karta.png", "A 58551-2023")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58551-2023 georefererad karta.tif", "A 58551-2023")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58551-2023 FSC-klagomål.docx", "A 58551-2023")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58551-2023 FSC-klagomål mail.docx", "A 58551-2023")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58551-2023 tillsynsbegäran.docx", "A 58551-2023")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58551-2023 tillsynsbegäran mail.docx", "A 58551-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 62988-2023</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45272</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>19</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 62988-2023 artfynd.xlsx", "A 62988-2023")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 62988-2023 karta.png", "A 62988-2023")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 62988-2023 georefererad karta.tif", "A 62988-2023")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 62988-2023 FSC-klagomål.docx", "A 62988-2023")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 62988-2023 FSC-klagomål mail.docx", "A 62988-2023")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 62988-2023 tillsynsbegäran.docx", "A 62988-2023")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 62988-2023 tillsynsbegäran mail.docx", "A 62988-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 32776-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45839</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Smalsprötad bastardsvärmare</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32776-2025 artfynd.xlsx", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32776-2025 karta.png", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32776-2025 georefererad karta.tif", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32776-2025 FSC-klagomål.docx", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32776-2025 FSC-klagomål mail.docx", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32776-2025 tillsynsbegäran.docx", "A 32776-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32776-2025 tillsynsbegäran mail.docx", "A 32776-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 56637-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45243</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 56637-2023 artfynd.xlsx", "A 56637-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 56637-2023 karta.png", "A 56637-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 56637-2023 georefererad karta.tif", "A 56637-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 56637-2023 FSC-klagomål.docx", "A 56637-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 56637-2023 FSC-klagomål mail.docx", "A 56637-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 56637-2023 tillsynsbegäran.docx", "A 56637-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 56637-2023 tillsynsbegäran mail.docx", "A 56637-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 50774-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Mörk dunört</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 50774-2023 artfynd.xlsx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 50774-2023 karta.png", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 50774-2023 georefererad karta.tif", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 50774-2023 FSC-klagomål.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 50774-2023 FSC-klagomål mail.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 50774-2023 tillsynsbegäran.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 50774-2023 tillsynsbegäran mail.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 38720-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45163</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Hässleklocka</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 38720-2023 artfynd.xlsx", "A 38720-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 38720-2023 karta.png", "A 38720-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 38720-2023 georefererad karta.tif", "A 38720-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 38720-2023 FSC-klagomål.docx", "A 38720-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 38720-2023 FSC-klagomål mail.docx", "A 38720-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 38720-2023 tillsynsbegäran.docx", "A 38720-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 38720-2023 tillsynsbegäran mail.docx", "A 38720-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 32713-2024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45516</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Kristinspindling</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32713-2024 artfynd.xlsx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32713-2024 karta.png", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32713-2024 georefererad karta.tif", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32713-2024 FSC-klagomål.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32713-2024 FSC-klagomål mail.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32713-2024 tillsynsbegäran.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32713-2024 tillsynsbegäran mail.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         <v>44509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>44538</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>44614</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>44582</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>44803</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>44510</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 52476-2021</t>
+          <t>A 64622-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2991,14 +2991,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44466</v>
+        <v>44511</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3010,13 +3010,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3059,7 +3054,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 64622-2021</t>
+          <t>A 62919-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3069,14 +3064,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44511</v>
+        <v>44504</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3089,7 +3084,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3132,7 +3127,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 62919-2021</t>
+          <t>A 65821-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3146,10 +3141,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44504</v>
+        <v>44517</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3162,7 +3157,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3205,7 +3200,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 65821-2021</t>
+          <t>A 16152-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3219,10 +3214,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44517</v>
+        <v>44666</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3235,7 +3230,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3278,7 +3273,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16152-2022</t>
+          <t>A 29967-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3292,10 +3287,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44666</v>
+        <v>44756</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3308,7 +3303,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3351,7 +3346,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 29967-2022</t>
+          <t>A 34979-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3365,10 +3360,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44756</v>
+        <v>44796</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3381,7 +3376,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3424,7 +3419,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 34979-2022</t>
+          <t>A 15790-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3438,10 +3433,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44796</v>
+        <v>45748</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3454,7 +3449,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3497,7 +3492,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 36114-2022</t>
+          <t>A 6705-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3511,10 +3506,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44803</v>
+        <v>45342</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3526,8 +3521,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3570,7 +3570,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 47600-2023</t>
+          <t>A 35661-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45203</v>
+        <v>45532</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3643,7 +3643,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 15906-2024</t>
+          <t>A 5819-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45405</v>
+        <v>45335</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3672,8 +3672,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3716,7 +3721,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 64015-2025</t>
+          <t>A 22088-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3730,10 +3735,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46021</v>
+        <v>45069</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3745,13 +3750,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3794,7 +3794,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 64010-2025</t>
+          <t>A 26949-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46021</v>
+        <v>45093</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3823,13 +3823,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>15.4</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3872,7 +3867,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 602-2026</t>
+          <t>A 36114-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3886,10 +3881,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46029</v>
+        <v>44803</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3902,7 +3897,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3945,7 +3940,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 21336-2025</t>
+          <t>A 15813-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3955,14 +3950,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45782</v>
+        <v>44664</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3974,8 +3969,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4018,7 +4018,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30389-2024</t>
+          <t>A 38152-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45491</v>
+        <v>45161</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.6</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4091,7 +4091,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 1578-2023</t>
+          <t>A 44069-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44937</v>
+        <v>45188</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4164,7 +4164,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 1589-2026</t>
+          <t>A 1578-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46034</v>
+        <v>44937</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4193,13 +4193,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4242,7 +4237,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 1279-2026</t>
+          <t>A 56841-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4256,10 +4251,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46031</v>
+        <v>44894</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4272,7 +4267,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4315,7 +4310,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 1264-2026</t>
+          <t>A 11280-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4329,10 +4324,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46031</v>
+        <v>45726</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4345,7 +4340,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4388,7 +4383,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 54226-2021</t>
+          <t>A 3198-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4402,10 +4397,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44470</v>
+        <v>45316</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4461,7 +4456,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 48325-2022</t>
+          <t>A 15909-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4475,10 +4470,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44858</v>
+        <v>45405</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4490,13 +4485,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4539,7 +4529,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 47993-2024</t>
+          <t>A 3554-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4553,10 +4543,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45589</v>
+        <v>45680</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4569,7 +4559,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4612,7 +4602,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 1585-2026</t>
+          <t>A 8256-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4622,14 +4612,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46034</v>
+        <v>44974</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4641,13 +4631,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4690,7 +4675,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 1273-2026</t>
+          <t>A 61798-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4704,10 +4689,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46031</v>
+        <v>46002</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4719,8 +4704,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4763,7 +4753,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 64802-2021</t>
+          <t>A 61801-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4773,14 +4763,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44512</v>
+        <v>46002</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4793,7 +4783,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4836,7 +4826,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 1261-2026</t>
+          <t>A 61972-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4850,10 +4840,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46031</v>
+        <v>46003</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4865,8 +4855,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4909,7 +4904,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 1268-2026</t>
+          <t>A 61470-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4923,10 +4918,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46031</v>
+        <v>46001</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4938,8 +4933,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4982,7 +4982,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 6164-2024</t>
+          <t>A 61629-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4996,10 +4996,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45337</v>
+        <v>46002</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5055,7 +5055,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 6705-2024</t>
+          <t>A 50818-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45342</v>
+        <v>45217</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5084,13 +5084,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>8.300000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5133,7 +5128,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 35661-2024</t>
+          <t>A 38259-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5147,10 +5142,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45532</v>
+        <v>45161</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5163,7 +5158,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5206,7 +5201,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 56841-2022</t>
+          <t>A 62482-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5220,10 +5215,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44894</v>
+        <v>46007</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5236,7 +5231,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>6.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5279,7 +5274,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 1323-2023</t>
+          <t>A 62202-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5293,10 +5288,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44936</v>
+        <v>46006</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5309,7 +5304,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>5.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5352,7 +5347,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 32335-2024</t>
+          <t>A 62801-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5366,10 +5361,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45512</v>
+        <v>46008</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5382,7 +5377,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.2</v>
+        <v>6.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5425,7 +5420,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 41730-2025</t>
+          <t>A 21336-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5439,10 +5434,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45902</v>
+        <v>45782</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5498,7 +5493,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30388-2024</t>
+          <t>A 39032-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5512,10 +5507,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45491</v>
+        <v>45163</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5527,8 +5522,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.9</v>
+        <v>5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5571,7 +5571,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 3149-2024</t>
+          <t>A 41730-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45316</v>
+        <v>45902</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5644,7 +5644,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 47597-2023</t>
+          <t>A 39920-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5658,10 +5658,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45203</v>
+        <v>45553</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5717,7 +5717,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 15907-2024</t>
+          <t>A 45973-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5727,14 +5727,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45405</v>
+        <v>45580</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5790,7 +5790,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 15915-2024</t>
+          <t>A 9448-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5800,14 +5800,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45405</v>
+        <v>44981</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5863,7 +5863,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 7375-2026</t>
+          <t>A 54226-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46059</v>
+        <v>44470</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5936,7 +5936,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17618-2024</t>
+          <t>A 46528-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5950,10 +5950,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45416</v>
+        <v>45582</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6009,7 +6009,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 8118-2026</t>
+          <t>A 36075-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6023,10 +6023,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46062</v>
+        <v>45149</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>13.4</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13129-2023</t>
+          <t>A 1674-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6096,10 +6096,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45002</v>
+        <v>44938</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6155,7 +6155,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 5283-2024</t>
+          <t>A 46059-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6169,10 +6169,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45331</v>
+        <v>45924</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6228,7 +6228,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 14750-2023</t>
+          <t>A 46778-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6242,10 +6242,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45014</v>
+        <v>45926</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6301,7 +6301,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 46059-2025</t>
+          <t>A 35079-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45924</v>
+        <v>45145</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6374,7 +6374,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 46788-2025</t>
+          <t>A 30600-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45926</v>
+        <v>45831</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6447,7 +6447,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 14156-2023</t>
+          <t>A 46999-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6461,10 +6461,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45009</v>
+        <v>45929</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6477,7 +6477,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6520,7 +6520,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 46778-2025</t>
+          <t>A 46788-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6537,7 +6537,7 @@
         <v>45926</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6593,7 +6593,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 46999-2025</t>
+          <t>A 47648-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6607,10 +6607,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6683,7 +6683,7 @@
         <v>45932</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 47648-2025</t>
+          <t>A 6421-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45931</v>
+        <v>45699</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6812,7 +6812,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 46528-2024</t>
+          <t>A 6456-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6826,10 +6826,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45582</v>
+        <v>45699</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 48575-2025</t>
+          <t>A 17618-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45936</v>
+        <v>45416</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6975,7 +6975,7 @@
         <v>45936</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>45936</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 8256-2023</t>
+          <t>A 32466-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7114,14 +7114,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44974</v>
+        <v>45838</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7177,7 +7177,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 12859-2026</t>
+          <t>A 48575-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7191,10 +7191,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46092</v>
+        <v>45936</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7250,7 +7250,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 12872-2026</t>
+          <t>A 32476-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7264,10 +7264,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46092</v>
+        <v>45838</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7323,7 +7323,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 22088-2023</t>
+          <t>A 47993-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7337,10 +7337,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45069</v>
+        <v>45589</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7396,7 +7396,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 50416-2025</t>
+          <t>A 64010-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7410,10 +7410,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45944</v>
+        <v>46021</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7425,8 +7425,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>3.4</v>
+        <v>15.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7469,7 +7474,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 36099-2024</t>
+          <t>A 5513-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7483,10 +7488,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45533</v>
+        <v>45693</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7499,7 +7504,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7542,7 +7547,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 14736-2024</t>
+          <t>A 6164-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7552,14 +7557,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45397</v>
+        <v>45337</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7572,7 +7577,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7615,7 +7620,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 14617-2026</t>
+          <t>A 14156-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7629,10 +7634,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46101</v>
+        <v>45009</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7645,7 +7650,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7688,7 +7693,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 51171-2025</t>
+          <t>A 50416-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7702,10 +7707,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45947</v>
+        <v>45944</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7718,7 +7723,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7761,7 +7766,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 51328-2025</t>
+          <t>A 64015-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7775,10 +7780,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45950</v>
+        <v>46021</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7790,8 +7795,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7834,7 +7844,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 20232-2022</t>
+          <t>A 51171-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7848,10 +7858,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44698</v>
+        <v>45947</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7863,13 +7873,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7912,7 +7917,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 14185-2023</t>
+          <t>A 13129-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7926,10 +7931,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45009</v>
+        <v>45002</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7985,7 +7990,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 16341-2026</t>
+          <t>A 51328-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7999,10 +8004,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46111</v>
+        <v>45950</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8014,13 +8019,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8063,7 +8063,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 16402-2026</t>
+          <t>A 35411-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8077,10 +8077,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46111</v>
+        <v>45146</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8092,13 +8092,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8141,7 +8136,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 16414-2026</t>
+          <t>A 16270-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8155,10 +8150,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46111</v>
+        <v>45407</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8170,13 +8165,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>8.199999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8219,7 +8209,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 16370-2026</t>
+          <t>A 602-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8233,10 +8223,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46111</v>
+        <v>46029</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8248,13 +8238,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>6.9</v>
+        <v>1.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8297,7 +8282,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 14166-2023</t>
+          <t>A 1279-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8311,10 +8296,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45009</v>
+        <v>46031</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8327,7 +8312,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8370,7 +8355,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 19350-2023</t>
+          <t>A 1261-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8384,10 +8369,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45049</v>
+        <v>46031</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8400,7 +8385,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8443,7 +8428,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 11972-2023</t>
+          <t>A 1268-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8457,10 +8442,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44994</v>
+        <v>46031</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8473,7 +8458,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8516,7 +8501,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 20720-2025</t>
+          <t>A 1264-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8530,10 +8515,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45776</v>
+        <v>46031</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8546,7 +8531,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8589,7 +8574,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 55908-2025</t>
+          <t>A 1273-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8603,10 +8588,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45973</v>
+        <v>46031</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8619,7 +8604,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8662,7 +8647,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 55901-2025</t>
+          <t>A 20244-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8676,10 +8661,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45973</v>
+        <v>44698</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8691,8 +8676,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>9.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8735,7 +8725,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 55906-2025</t>
+          <t>A 6557-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8749,10 +8739,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45973</v>
+        <v>45699</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8765,7 +8755,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8808,7 +8798,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 16259-2026</t>
+          <t>A 32378-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8822,10 +8812,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46109</v>
+        <v>45512</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8838,7 +8828,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8881,7 +8871,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 16262-2026</t>
+          <t>A 1585-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8895,10 +8885,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46109</v>
+        <v>46034</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8910,8 +8900,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8954,7 +8949,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 54419-2024</t>
+          <t>A 1589-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8968,10 +8963,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45617</v>
+        <v>46034</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8989,7 +8984,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>22.7</v>
+        <v>3.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9032,7 +9027,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 17950-2026</t>
+          <t>A 20720-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9046,10 +9041,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46122</v>
+        <v>45776</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9062,7 +9057,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9105,7 +9100,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 39032-2023</t>
+          <t>A 55901-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9119,10 +9114,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45163</v>
+        <v>45973</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9134,13 +9129,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9183,7 +9173,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 14993-2023</t>
+          <t>A 55906-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9197,10 +9187,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45015</v>
+        <v>45973</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9213,7 +9203,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9256,7 +9246,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 39027-2023</t>
+          <t>A 55908-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9270,10 +9260,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45163</v>
+        <v>45973</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9285,13 +9275,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9334,7 +9319,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 11280-2025</t>
+          <t>A 19351-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9348,10 +9333,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45726</v>
+        <v>45049</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9364,7 +9349,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.4</v>
+        <v>5.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9407,7 +9392,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 8049-2025</t>
+          <t>A 39024-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9421,10 +9406,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45707</v>
+        <v>45163</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9436,8 +9421,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9480,7 +9470,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 61801-2025</t>
+          <t>A 32335-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9494,10 +9484,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46002</v>
+        <v>45512</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9510,7 +9500,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9553,7 +9543,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 61470-2025</t>
+          <t>A 8515-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9567,10 +9557,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46001</v>
+        <v>44613</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9582,13 +9572,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>8</v>
+        <v>2.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9631,7 +9616,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 61798-2025</t>
+          <t>A 61880-2021</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9645,10 +9630,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46002</v>
+        <v>44502</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9660,13 +9645,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>1.2</v>
+        <v>4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9709,7 +9689,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 61629-2025</t>
+          <t>A 33375-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9723,10 +9703,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46002</v>
+        <v>45519</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9738,8 +9718,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9782,7 +9767,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 38152-2023</t>
+          <t>A 43263-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9792,14 +9777,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45161</v>
+        <v>45183</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9812,7 +9797,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9855,7 +9840,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 62202-2025</t>
+          <t>A 46536-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9869,10 +9854,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46006</v>
+        <v>45582</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9885,7 +9870,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9928,7 +9913,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 61972-2025</t>
+          <t>A 7375-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9942,10 +9927,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46003</v>
+        <v>46059</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9957,13 +9942,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10006,7 +9986,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 8515-2022</t>
+          <t>A 38212-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10020,10 +10000,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44613</v>
+        <v>45161</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10036,7 +10016,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10079,7 +10059,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 62801-2025</t>
+          <t>A 8118-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10093,10 +10073,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46008</v>
+        <v>46062</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10109,7 +10089,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>6.6</v>
+        <v>13.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10152,7 +10132,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 62482-2025</t>
+          <t>A 3130-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10166,10 +10146,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46007</v>
+        <v>45678</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10181,8 +10161,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>6.7</v>
+        <v>18.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10225,7 +10210,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 38723-2023</t>
+          <t>A 15907-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10235,14 +10220,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45163</v>
+        <v>45405</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10298,7 +10283,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 3130-2025</t>
+          <t>A 15915-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10308,14 +10293,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45678</v>
+        <v>45405</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10327,13 +10312,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>18.6</v>
+        <v>0.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10376,7 +10356,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 63074-2025</t>
+          <t>A 20232-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10390,10 +10370,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46009</v>
+        <v>44698</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10411,7 +10391,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>8.699999999999999</v>
+        <v>2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10454,7 +10434,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 16128-2025</t>
+          <t>A 8063-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10468,10 +10448,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45750</v>
+        <v>45707</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10483,13 +10463,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10532,7 +10507,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 165-2026</t>
+          <t>A 32715-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10546,10 +10521,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46024</v>
+        <v>45516</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10562,7 +10537,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10605,7 +10580,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 55971-2023</t>
+          <t>A 6465-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10619,10 +10594,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45240</v>
+        <v>45699</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10635,7 +10610,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10678,7 +10653,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 30945-2023</t>
+          <t>A 1749-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10692,10 +10667,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45113</v>
+        <v>45671</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10708,7 +10683,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10751,7 +10726,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 16164-2023</t>
+          <t>A 12872-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10765,10 +10740,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45027</v>
+        <v>46092</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10780,13 +10755,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10829,7 +10799,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 5350-2025</t>
+          <t>A 12859-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10843,10 +10813,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45692</v>
+        <v>46092</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10859,7 +10829,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10902,7 +10872,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 30964-2023</t>
+          <t>A 14617-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10916,10 +10886,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45113</v>
+        <v>46101</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10932,7 +10902,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10975,7 +10945,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 30600-2025</t>
+          <t>A 17126-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10989,10 +10959,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45831</v>
+        <v>45412</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11005,7 +10975,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11048,7 +11018,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 21770-2023</t>
+          <t>A 4678-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11062,10 +11032,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45065</v>
+        <v>45328</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11078,7 +11048,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11121,7 +11091,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 19351-2023</t>
+          <t>A 16370-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11135,10 +11105,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45049</v>
+        <v>46111</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11150,8 +11120,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>5.8</v>
+        <v>6.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11194,7 +11169,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 38266-2022</t>
+          <t>A 16414-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11208,10 +11183,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44812</v>
+        <v>46111</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11223,8 +11198,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>2.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11267,7 +11247,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 32476-2025</t>
+          <t>A 16402-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11281,10 +11261,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45838</v>
+        <v>46111</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11296,8 +11276,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11340,7 +11325,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 63115-2025</t>
+          <t>A 16341-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11354,10 +11339,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46009</v>
+        <v>46111</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11369,8 +11354,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>3.8</v>
+        <v>1.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11413,7 +11403,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 32466-2025</t>
+          <t>A 21771-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11427,10 +11417,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45838</v>
+        <v>45065</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11443,7 +11433,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11486,7 +11476,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 21771-2023</t>
+          <t>A 64802-2021</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11496,14 +11486,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45065</v>
+        <v>44512</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11516,7 +11506,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11559,7 +11549,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 61011-2024</t>
+          <t>A 16128-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11569,14 +11559,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45645</v>
+        <v>45750</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11588,8 +11578,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>4.7</v>
+        <v>1.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11632,7 +11627,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 1337-2026</t>
+          <t>A 3149-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11646,10 +11641,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46031</v>
+        <v>45316</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11662,7 +11657,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11705,7 +11700,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 8067-2025</t>
+          <t>A 16259-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11719,10 +11714,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45707</v>
+        <v>46109</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11735,7 +11730,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11778,7 +11773,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 32464-2025</t>
+          <t>A 16262-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11792,10 +11787,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45838</v>
+        <v>46109</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11808,7 +11803,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11851,7 +11846,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 35079-2023</t>
+          <t>A 17950-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11865,10 +11860,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45145</v>
+        <v>46122</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11881,7 +11876,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11924,7 +11919,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 45973-2024</t>
+          <t>A 51180-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11938,10 +11933,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45580</v>
+        <v>45603</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11954,7 +11949,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12014,7 +12009,7 @@
         <v>45145</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12070,7 +12065,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 5819-2024</t>
+          <t>A 51178-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12080,14 +12075,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45335</v>
+        <v>45603</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12099,13 +12094,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12148,7 +12138,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 61880-2021</t>
+          <t>A 19157-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12162,10 +12152,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44502</v>
+        <v>45048</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12178,7 +12168,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12221,7 +12211,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 38212-2023</t>
+          <t>A 55971-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12235,10 +12225,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45161</v>
+        <v>45240</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12251,7 +12241,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12294,7 +12284,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 25895-2026</t>
+          <t>A 16164-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12308,10 +12298,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46178</v>
+        <v>45027</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12323,8 +12313,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12367,7 +12362,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 25816-2026</t>
+          <t>A 39024-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12381,10 +12376,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46178</v>
+        <v>45163</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12396,8 +12391,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12440,7 +12440,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 27087-2024</t>
+          <t>A 39027-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12454,10 +12454,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45471</v>
+        <v>45163</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12469,8 +12469,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12513,7 +12518,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 25863-2026</t>
+          <t>A 47597-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12527,10 +12532,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46178</v>
+        <v>45203</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12543,7 +12548,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12586,7 +12591,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 25975-2026</t>
+          <t>A 14166-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12600,10 +12605,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46181</v>
+        <v>45009</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12616,7 +12621,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12659,7 +12664,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 39920-2024</t>
+          <t>A 5350-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12673,10 +12678,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45553</v>
+        <v>45692</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12689,7 +12694,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12732,7 +12737,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 46536-2024</t>
+          <t>A 15344-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12746,10 +12751,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45582</v>
+        <v>45747</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12762,7 +12767,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12805,7 +12810,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 27292-2026</t>
+          <t>A 10335-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12819,10 +12824,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46184</v>
+        <v>44623</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12835,7 +12840,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12878,7 +12883,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 4678-2024</t>
+          <t>A 35095-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12892,10 +12897,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45328</v>
+        <v>45145</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12908,7 +12913,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12951,7 +12956,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 35095-2023</t>
+          <t>A 20612-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12965,10 +12970,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45145</v>
+        <v>44700</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12980,8 +12985,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>0.5</v>
+        <v>8.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13024,7 +13034,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 1749-2025</t>
+          <t>A 15198-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13038,10 +13048,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45671</v>
+        <v>44658</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13054,7 +13064,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13097,7 +13107,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 15909-2024</t>
+          <t>A 6375-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13107,14 +13117,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45405</v>
+        <v>45699</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13127,7 +13137,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13170,7 +13180,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 6375-2025</t>
+          <t>A 6592-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13184,10 +13194,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45699</v>
+        <v>45700</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13243,7 +13253,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 32378-2024</t>
+          <t>A 37843-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13257,10 +13267,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45512</v>
+        <v>45160</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13273,7 +13283,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13316,7 +13326,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 28908-2026</t>
+          <t>A 6506-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13330,10 +13340,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46199</v>
+        <v>45699</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13346,7 +13356,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13389,7 +13399,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 28704-2026</t>
+          <t>A 165-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13403,10 +13413,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46198</v>
+        <v>46024</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13418,13 +13428,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13467,7 +13472,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 28718-2026</t>
+          <t>A 63074-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13481,10 +13486,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46198</v>
+        <v>46009</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13502,7 +13507,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13545,7 +13550,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 51180-2024</t>
+          <t>A 5283-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13559,10 +13564,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45603</v>
+        <v>45331</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13575,7 +13580,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13618,7 +13623,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 39024-2023</t>
+          <t>A 38723-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13635,7 +13640,7 @@
         <v>45163</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13647,13 +13652,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13696,7 +13696,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 39190-2023</t>
+          <t>A 63115-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13706,14 +13706,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45166</v>
+        <v>46009</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13769,7 +13769,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 30155-2026</t>
+          <t>A 50387-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13783,10 +13783,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46206</v>
+        <v>45600</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13798,13 +13798,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>5.8</v>
+        <v>8.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13847,7 +13842,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 16168-2023</t>
+          <t>A 2512-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13861,10 +13856,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45027</v>
+        <v>45313</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13876,13 +13871,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13925,7 +13915,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 38718-2023</t>
+          <t>A 64709-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13939,10 +13929,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45163</v>
+        <v>45281</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13955,7 +13945,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13998,7 +13988,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 2512-2024</t>
+          <t>A 64710-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14012,10 +14002,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45313</v>
+        <v>45281</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14028,7 +14018,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14071,7 +14061,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 51178-2024</t>
+          <t>A 36730-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14085,10 +14075,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45603</v>
+        <v>45153</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14101,7 +14091,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14144,7 +14134,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 35380-2023</t>
+          <t>A 16168-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14158,10 +14148,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45146</v>
+        <v>45027</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14173,8 +14163,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14217,7 +14212,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 6592-2025</t>
+          <t>A 21770-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14231,10 +14226,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45700</v>
+        <v>45065</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14247,7 +14242,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14290,7 +14285,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 43263-2023</t>
+          <t>A 36099-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14300,14 +14295,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45183</v>
+        <v>45533</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14320,7 +14315,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14363,7 +14358,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 20244-2022</t>
+          <t>A 61011-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14373,14 +14368,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44698</v>
+        <v>45645</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14392,13 +14387,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>9.5</v>
+        <v>4.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14441,7 +14431,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 50358-2025</t>
+          <t>A 1337-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14455,10 +14445,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45944</v>
+        <v>46031</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14471,7 +14461,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14514,7 +14504,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 20612-2022</t>
+          <t>A 32464-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14528,10 +14518,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44700</v>
+        <v>45838</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14543,13 +14533,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>8.9</v>
+        <v>1.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14592,7 +14577,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 6421-2025</t>
+          <t>A 8067-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14606,10 +14591,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45699</v>
+        <v>45707</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14622,7 +14607,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14665,7 +14650,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 52469-2023</t>
+          <t>A 38718-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14679,10 +14664,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45225</v>
+        <v>45163</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14695,7 +14680,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14738,7 +14723,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 8063-2025</t>
+          <t>A 15906-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14748,14 +14733,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45707</v>
+        <v>45405</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14768,7 +14753,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.1</v>
+        <v>0.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14811,7 +14796,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 15790-2025</t>
+          <t>A 35097-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14825,10 +14810,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45748</v>
+        <v>45145</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14841,7 +14826,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14884,7 +14869,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 31447-2026</t>
+          <t>A 30945-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14898,10 +14883,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46220</v>
+        <v>45113</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14914,7 +14899,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14957,7 +14942,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 37843-2023</t>
+          <t>A 30964-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14971,10 +14956,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45160</v>
+        <v>45113</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14987,7 +14972,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15030,7 +15015,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 6465-2025</t>
+          <t>A 25895-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15044,10 +15029,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45699</v>
+        <v>46178</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15060,7 +15045,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15103,7 +15088,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 1674-2023</t>
+          <t>A 25863-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15117,10 +15102,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44938</v>
+        <v>46178</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15133,7 +15118,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15176,7 +15161,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 34961-2022</t>
+          <t>A 25816-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15190,10 +15175,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44796</v>
+        <v>46178</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15206,7 +15191,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15249,7 +15234,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 19157-2023</t>
+          <t>A 25975-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15263,10 +15248,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45048</v>
+        <v>46181</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15279,7 +15264,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15322,7 +15307,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 36824-2026</t>
+          <t>A 48325-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15332,14 +15317,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46272</v>
+        <v>44858</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15357,7 +15342,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>8</v>
+        <v>1.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15400,7 +15385,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 37473-2026</t>
+          <t>A 27292-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15414,10 +15399,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46275</v>
+        <v>46184</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15430,7 +15415,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15473,7 +15458,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 37482-2026</t>
+          <t>A 11699-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15487,10 +15472,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46275</v>
+        <v>45373</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15502,13 +15487,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>16.5</v>
+        <v>2.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15551,7 +15531,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 37469-2026</t>
+          <t>A 11704-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15565,10 +15545,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46275</v>
+        <v>45373</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15581,7 +15561,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15624,7 +15604,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 37991-2026</t>
+          <t>A 11193-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15634,14 +15614,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46280</v>
+        <v>44992</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15654,7 +15634,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15697,7 +15677,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 39024-2023</t>
+          <t>A 8049-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15711,10 +15691,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45163</v>
+        <v>45707</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15726,13 +15706,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15775,7 +15750,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 17126-2024</t>
+          <t>A 30389-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15789,10 +15764,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45412</v>
+        <v>45491</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15805,7 +15780,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.6</v>
+        <v>5.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15848,7 +15823,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 11193-2023</t>
+          <t>A 35380-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15858,14 +15833,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44992</v>
+        <v>45146</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15878,7 +15853,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15921,7 +15896,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 26949-2023</t>
+          <t>A 54419-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15935,10 +15910,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45093</v>
+        <v>45617</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -15950,8 +15925,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>1.3</v>
+        <v>22.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -15994,7 +15974,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 39658-2026</t>
+          <t>A 28718-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16008,10 +15988,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46289</v>
+        <v>46198</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16023,8 +16003,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16067,7 +16052,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 37494-2026</t>
+          <t>A 28704-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16081,10 +16066,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46275</v>
+        <v>46198</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16096,8 +16081,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16140,7 +16130,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 6506-2025</t>
+          <t>A 28908-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16154,10 +16144,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45699</v>
+        <v>46199</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16170,7 +16160,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16213,7 +16203,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 12332-2023</t>
+          <t>A 34961-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16227,10 +16217,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44999</v>
+        <v>44796</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16243,7 +16233,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16286,7 +16276,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 36075-2023</t>
+          <t>A 14185-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16300,10 +16290,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45149</v>
+        <v>45009</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16316,7 +16306,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16359,7 +16349,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 15198-2022</t>
+          <t>A 27087-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16373,10 +16363,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44658</v>
+        <v>45471</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16389,7 +16379,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16432,7 +16422,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 6456-2025</t>
+          <t>A 6368-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16449,7 +16439,7 @@
         <v>45699</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16462,7 +16452,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16505,7 +16495,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 21855-2022</t>
+          <t>A 39190-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16515,14 +16505,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44709</v>
+        <v>45166</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16535,7 +16525,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16578,7 +16568,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 72603-2021</t>
+          <t>A 30155-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16592,10 +16582,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44546</v>
+        <v>46206</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16607,8 +16597,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16651,7 +16646,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 9448-2023</t>
+          <t>A 54590-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16665,10 +16660,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44981</v>
+        <v>45617</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16724,7 +16719,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 64709-2023</t>
+          <t>A 14993-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16738,10 +16733,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45281</v>
+        <v>45015</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16754,7 +16749,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16797,7 +16792,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 64710-2023</t>
+          <t>A 52469-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16811,10 +16806,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45281</v>
+        <v>45225</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16827,7 +16822,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16870,7 +16865,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 35097-2023</t>
+          <t>A 50358-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16884,10 +16879,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45145</v>
+        <v>45944</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16900,7 +16895,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -16943,7 +16938,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 35411-2023</t>
+          <t>A 19350-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -16957,10 +16952,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45146</v>
+        <v>45049</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -16973,7 +16968,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17016,7 +17011,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 36730-2023</t>
+          <t>A 51041-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17030,10 +17025,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45153</v>
+        <v>45603</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17046,7 +17041,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17089,7 +17084,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 25729-2023</t>
+          <t>A 11972-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17103,10 +17098,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45084</v>
+        <v>44994</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17119,7 +17114,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17162,7 +17157,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 11699-2024</t>
+          <t>A 31447-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17176,10 +17171,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45373</v>
+        <v>46220</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17192,7 +17187,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17235,7 +17230,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 11704-2024</t>
+          <t>A 12332-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17249,10 +17244,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45373</v>
+        <v>44999</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17265,7 +17260,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17308,7 +17303,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 54590-2024</t>
+          <t>A 38266-2022</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17322,10 +17317,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45617</v>
+        <v>44812</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17338,7 +17333,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17381,7 +17376,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 10335-2022</t>
+          <t>A 1323-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17395,10 +17390,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44623</v>
+        <v>44936</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17411,7 +17406,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17454,7 +17449,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 33375-2024</t>
+          <t>A 14736-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17464,14 +17459,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45519</v>
+        <v>45397</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17483,13 +17478,8 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17532,7 +17522,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 5513-2025</t>
+          <t>A 25729-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17546,10 +17536,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45693</v>
+        <v>45084</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17562,7 +17552,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17605,7 +17595,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 15813-2022</t>
+          <t>A 36824-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17615,14 +17605,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44664</v>
+        <v>46272</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17636,11 +17626,11 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17683,7 +17673,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 6368-2025</t>
+          <t>A 30388-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17697,10 +17687,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45699</v>
+        <v>45491</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17713,7 +17703,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17756,7 +17746,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 44069-2023</t>
+          <t>A 37482-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17770,10 +17760,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45188</v>
+        <v>46275</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17785,8 +17775,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>2.3</v>
+        <v>16.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17829,7 +17824,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 3198-2024</t>
+          <t>A 37473-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17843,10 +17838,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45316</v>
+        <v>46275</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17859,7 +17854,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17902,7 +17897,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 16270-2024</t>
+          <t>A 37469-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17916,10 +17911,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45407</v>
+        <v>46275</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17932,7 +17927,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -17975,7 +17970,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 51041-2024</t>
+          <t>A 21855-2022</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -17989,10 +17984,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45603</v>
+        <v>44709</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18005,7 +18000,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18048,7 +18043,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 6557-2025</t>
+          <t>A 72603-2021</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18062,10 +18057,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45699</v>
+        <v>44546</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18078,7 +18073,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18121,7 +18116,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 15344-2025</t>
+          <t>A 14750-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18135,10 +18130,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45747</v>
+        <v>45014</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18151,7 +18146,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18194,7 +18189,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 50387-2024</t>
+          <t>A 47600-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18208,10 +18203,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45600</v>
+        <v>45203</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18224,7 +18219,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>8.5</v>
+        <v>0.6</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18267,7 +18262,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 32715-2024</t>
+          <t>A 37991-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18281,10 +18276,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45516</v>
+        <v>46280</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18297,7 +18292,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18340,7 +18335,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 38259-2023</t>
+          <t>A 21357-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18354,10 +18349,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45161</v>
+        <v>45782</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18370,7 +18365,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18430,7 +18425,7 @@
         <v>45782</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18486,7 +18481,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 21357-2025</t>
+          <t>A 37494-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18500,10 +18495,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45782</v>
+        <v>46275</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18516,7 +18511,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18559,7 +18554,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 3554-2025</t>
+          <t>A 39658-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18573,10 +18568,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45680</v>
+        <v>46289</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18589,7 +18584,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18632,24 +18627,24 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 50818-2023</t>
+          <t>S 899-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45217</v>
+        <v>45376</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18662,7 +18657,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>3.8</v>
+        <v>18</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18702,10 +18697,10 @@
       </c>
       <c r="V238" s="2" t="inlineStr"/>
     </row>
-    <row r="239" ht="15" customHeight="1">
+    <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>S 899-2024</t>
+          <t>S 6457-2022</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18719,10 +18714,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45376</v>
+        <v>44879</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18734,8 +18729,13 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I239" t="n">
-        <v>18</v>
+        <v>101.8</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18774,84 +18774,6 @@
         <v>0</v>
       </c>
       <c r="V239" s="2" t="inlineStr"/>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>S 6457-2022</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D240" s="1" t="n">
-        <v>44879</v>
-      </c>
-      <c r="E240" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I240" t="n">
-        <v>101.8</v>
-      </c>
-      <c r="J240" t="n">
-        <v>0</v>
-      </c>
-      <c r="K240" t="n">
-        <v>0</v>
-      </c>
-      <c r="L240" t="n">
-        <v>0</v>
-      </c>
-      <c r="M240" t="n">
-        <v>0</v>
-      </c>
-      <c r="N240" t="n">
-        <v>0</v>
-      </c>
-      <c r="O240" t="n">
-        <v>0</v>
-      </c>
-      <c r="P240" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
-      <c r="R240" t="n">
-        <v>0</v>
-      </c>
-      <c r="S240" t="n">
-        <v>0</v>
-      </c>
-      <c r="T240" t="n">
-        <v>0</v>
-      </c>
-      <c r="U240" t="n">
-        <v>0</v>
-      </c>
-      <c r="V240" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÖDESHÖG.xlsx
+++ b/Översikt ÖDESHÖG.xlsx
@@ -601,7 +601,7 @@
         <v>45805</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>45723</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         <v>44698</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>44664</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 56797-2023</t>
+          <t>A 35443-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1058,14 +1058,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45244</v>
+        <v>44798</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1118,149 +1118,149 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
+          <t>Axveronika
+Bivråk</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 35443-2022 artfynd.xlsx", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 35443-2022 karta.png", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 35443-2022 georefererad karta.tif", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 35443-2022 FSC-klagomål.docx", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 35443-2022 FSC-klagomål mail.docx", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 35443-2022 tillsynsbegäran.docx", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 35443-2022 tillsynsbegäran mail.docx", "A 35443-2022")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/fåglar/A 35443-2022 prioriterade fågelarter.docx", "A 35443-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 56797-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45244</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>Jungfrulin
 Svinrot</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 56797-2023 artfynd.xlsx", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 56797-2023 karta.png", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 56797-2023 georefererad karta.tif", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 56797-2023 FSC-klagomål.docx", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 56797-2023 FSC-klagomål mail.docx", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 56797-2023 tillsynsbegäran.docx", "A 56797-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 56797-2023 tillsynsbegäran mail.docx", "A 56797-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 35443-2022</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44798</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Axveronika
-Bivråk</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 35443-2022 artfynd.xlsx", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 35443-2022 karta.png", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 35443-2022 georefererad karta.tif", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 35443-2022 FSC-klagomål.docx", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 35443-2022 FSC-klagomål mail.docx", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 35443-2022 tillsynsbegäran.docx", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 35443-2022 tillsynsbegäran mail.docx", "A 35443-2022")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/fåglar/A 35443-2022 prioriterade fågelarter.docx", "A 35443-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>44538</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         <v>44538</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 32776-2025</t>
+          <t>A 15437-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45839</v>
+        <v>45747</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1503,11 +1503,16 @@
           <t>ÖDESHÖG</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>11.9</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1540,471 +1545,471 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 15437-2025 artfynd.xlsx", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 15437-2025 karta.png", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 15437-2025 georefererad karta.tif", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/knärot/A 15437-2025 karta knärot.png", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 15437-2025 FSC-klagomål.docx", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 15437-2025 FSC-klagomål mail.docx", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 15437-2025 tillsynsbegäran.docx", "A 15437-2025")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 15437-2025 tillsynsbegäran mail.docx", "A 15437-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 4772-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44592</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>1</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 4772-2022 artfynd.xlsx", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 4772-2022 karta.png", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 4772-2022 georefererad karta.tif", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 4772-2022 FSC-klagomål.docx", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 4772-2022 FSC-klagomål mail.docx", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 4772-2022 tillsynsbegäran.docx", "A 4772-2022")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 4772-2022 tillsynsbegäran mail.docx", "A 4772-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 32776-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32776-2025 artfynd.xlsx", "A 32776-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32776-2025 karta.png", "A 32776-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32776-2025 georefererad karta.tif", "A 32776-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32776-2025 FSC-klagomål.docx", "A 32776-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32776-2025 FSC-klagomål mail.docx", "A 32776-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32776-2025 tillsynsbegäran.docx", "A 32776-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32776-2025 tillsynsbegäran mail.docx", "A 32776-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 58052-2021</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>44487</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58052-2021 artfynd.xlsx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58052-2021 karta.png", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58052-2021 georefererad karta.tif", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58052-2021 FSC-klagomål.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58052-2021 FSC-klagomål mail.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58052-2021 tillsynsbegäran.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58052-2021 tillsynsbegäran mail.docx", "A 58052-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 58551-2023</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>45251</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E14" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ÖDESHÖG</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>0.8</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>1</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Blåsippa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 58551-2023 artfynd.xlsx", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 58551-2023 karta.png", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 58551-2023 georefererad karta.tif", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 58551-2023 FSC-klagomål.docx", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 58551-2023 FSC-klagomål mail.docx", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 58551-2023 tillsynsbegäran.docx", "A 58551-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 58551-2023 tillsynsbegäran mail.docx", "A 58551-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 50774-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Mörk dunört</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 50774-2023 artfynd.xlsx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 50774-2023 karta.png", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 50774-2023 georefererad karta.tif", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 50774-2023 FSC-klagomål.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 50774-2023 FSC-klagomål mail.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 50774-2023 tillsynsbegäran.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 50774-2023 tillsynsbegäran mail.docx", "A 50774-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 15437-2025</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45747</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 15437-2025 artfynd.xlsx", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 15437-2025 karta.png", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 15437-2025 georefererad karta.tif", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/knärot/A 15437-2025 karta knärot.png", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 15437-2025 FSC-klagomål.docx", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 15437-2025 FSC-klagomål mail.docx", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 15437-2025 tillsynsbegäran.docx", "A 15437-2025")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 15437-2025 tillsynsbegäran mail.docx", "A 15437-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 32713-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45516</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ÖDESHÖG</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Kristinspindling</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 32713-2024 artfynd.xlsx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 32713-2024 karta.png", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 32713-2024 georefererad karta.tif", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 32713-2024 FSC-klagomål.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 32713-2024 FSC-klagomål mail.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsyn/A 32713-2024 tillsynsbegäran.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0509/tillsynsmail/A 32713-2024 tillsynsbegäran mail.docx", "A 32713-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
@@ -2025,7 +2030,7 @@
         <v>45272</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2118,7 +2123,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 38720-2023</t>
+          <t>A 56637-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2128,14 +2133,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45163</v>
+        <v>45243</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2148,23 +2153,23 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
@@ -2172,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2184,261 +2189,256 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/artfynd/A 56637-2023 artfynd.xlsx", "A 56637-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor/A 56637-2023 karta.png", "A 56637-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/kartor_geotiff/A 56637-2023 georefererad karta.tif", "A 56637-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomål/A 56637-2023 FSC-klagomål.docx", "A 56637-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0509/klagomålsmail/A 56637-2023 FSC-klagomål mail.docx", "A 56637-2023")</f>
+        <v/>
+      </c>
+      <c r="A